--- a/research/traditional_assets/database/data/uruguay/uruguay_retail_general.xlsx
+++ b/research/traditional_assets/database/data/uruguay/uruguay_retail_general.xlsx
@@ -647,10 +647,10 @@
         <v>0.5242612185333819</v>
       </c>
       <c r="X2">
-        <v>0.1112812316607407</v>
+        <v>0.1112635149689779</v>
       </c>
       <c r="Y2">
-        <v>0.4129799868726412</v>
+        <v>0.412997703564404</v>
       </c>
       <c r="Z2">
         <v>3.222075759524397</v>
@@ -659,10 +659,10 @@
         <v>0.2807625253322066</v>
       </c>
       <c r="AB2">
-        <v>0.1076765390128246</v>
+        <v>0.1076600175231005</v>
       </c>
       <c r="AC2">
-        <v>0.1730859863193819</v>
+        <v>0.1731025078091061</v>
       </c>
       <c r="AD2">
         <v>5369</v>
@@ -781,10 +781,10 @@
         <v>0.5242612185333819</v>
       </c>
       <c r="X3">
-        <v>0.1112812316607407</v>
+        <v>0.1112635149689779</v>
       </c>
       <c r="Y3">
-        <v>0.4129799868726412</v>
+        <v>0.412997703564404</v>
       </c>
       <c r="Z3">
         <v>3.222075759524397</v>
@@ -793,10 +793,10 @@
         <v>0.2807625253322066</v>
       </c>
       <c r="AB3">
-        <v>0.1076765390128246</v>
+        <v>0.1076600175231005</v>
       </c>
       <c r="AC3">
-        <v>0.1730859863193819</v>
+        <v>0.1731025078091061</v>
       </c>
       <c r="AD3">
         <v>5369</v>
@@ -1133,7 +1133,7 @@
         <v>6.77352941176471</v>
       </c>
       <c r="F2">
-        <v>3.07164677696688</v>
+        <v>3.18392249523834</v>
       </c>
       <c r="G2">
         <v>2.14828376781942</v>
@@ -1151,13 +1151,13 @@
         <v>86207.8</v>
       </c>
       <c r="L2">
-        <v>82904.9921866573</v>
+        <v>83223.44443610081</v>
       </c>
       <c r="M2">
         <v>90282.2677779798</v>
       </c>
       <c r="N2">
-        <v>90911.8616422351</v>
+        <v>91230.3138916786</v>
       </c>
       <c r="O2">
         <v>6236.46777797978</v>
@@ -1166,16 +1166,16 @@
         <v>10168.8694555778</v>
       </c>
       <c r="Q2">
-        <v>0.107676539012825</v>
+        <v>0.107660017523101</v>
       </c>
       <c r="R2">
-        <v>0.107248024090788</v>
+        <v>0.107017181313244</v>
       </c>
       <c r="S2">
         <v>0.0578482333250682</v>
       </c>
       <c r="T2">
-        <v>0.0552982333250682</v>
+        <v>0.0533482333250682</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -1188,10 +1188,10 @@
         </is>
       </c>
       <c r="W2">
-        <v>0.111281231660741</v>
+        <v>0.111263514968978</v>
       </c>
       <c r="X2">
-        <v>0.113668784747225</v>
+        <v>0.113650422075828</v>
       </c>
       <c r="Y2">
         <v>1.01269975667748</v>
@@ -1230,7 +1230,7 @@
         <v>86207.8</v>
       </c>
       <c r="AK2">
-        <v>0.0646600645739018</v>
+        <v>0.06464257005823122</v>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
@@ -1418,13 +1418,13 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>0.1079112785861496</v>
+        <v>0.1078944736735083</v>
       </c>
       <c r="C2">
-        <v>92103.06048842739</v>
+        <v>92103.38022871723</v>
       </c>
       <c r="D2">
-        <v>89941.06048842739</v>
+        <v>89941.38022871723</v>
       </c>
       <c r="E2">
         <v>-6236.467777979779</v>
@@ -1469,19 +1469,19 @@
         <v>0</v>
       </c>
       <c r="S2">
-        <v>0.1079112785861496</v>
+        <v>0.1078944736735083</v>
       </c>
       <c r="T2">
         <v>0.960581759320096</v>
       </c>
       <c r="U2">
-        <v>0.06753097776675758</v>
+        <v>0.06613097776675758</v>
       </c>
       <c r="V2">
         <v>0.25</v>
       </c>
       <c r="W2">
-        <v>0.05064823332506818</v>
+        <v>0.04959823332506819</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
@@ -1500,13 +1500,13 @@
         <v>0.01</v>
       </c>
       <c r="B3">
-        <v>0.1078044827229349</v>
+        <v>0.1077772198225752</v>
       </c>
       <c r="C3">
-        <v>91333.53133901661</v>
+        <v>91349.09641285871</v>
       </c>
       <c r="D3">
-        <v>90095.9740167964</v>
+        <v>90111.5390906385</v>
       </c>
       <c r="E3">
         <v>-5312.025100199981</v>
@@ -1533,37 +1533,37 @@
         <v>2303</v>
       </c>
       <c r="M3">
-        <v>62.42851791978936</v>
+        <v>61.13429817089765</v>
       </c>
       <c r="N3">
-        <v>2240.57148208021</v>
+        <v>2241.865701829102</v>
       </c>
       <c r="O3">
-        <v>560.1428705200526</v>
+        <v>560.4664254572756</v>
       </c>
       <c r="P3">
-        <v>1680.428611560158</v>
+        <v>1681.399276371827</v>
       </c>
       <c r="Q3">
-        <v>2280.428611560158</v>
+        <v>2281.399276371827</v>
       </c>
       <c r="R3">
         <v>0.0101010101010101</v>
       </c>
       <c r="S3">
-        <v>0.1083818185754386</v>
+        <v>0.1083648863528531</v>
       </c>
       <c r="T3">
         <v>0.9678588938603998</v>
       </c>
       <c r="U3">
-        <v>0.06753097776675758</v>
+        <v>0.06613097776675758</v>
       </c>
       <c r="V3">
         <v>0.25</v>
       </c>
       <c r="W3">
-        <v>0.05064823332506818</v>
+        <v>0.04959823332506819</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>36.89019180239046</v>
+        <v>37.67116117963908</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1582,13 +1582,13 @@
         <v>0.02</v>
       </c>
       <c r="B4">
-        <v>0.1076976868597202</v>
+        <v>0.1076599659716421</v>
       </c>
       <c r="C4">
-        <v>90564.53675316791</v>
+        <v>90595.45765981317</v>
       </c>
       <c r="D4">
-        <v>90251.42210872751</v>
+        <v>90282.34301537277</v>
       </c>
       <c r="E4">
         <v>-4387.582422420184</v>
@@ -1615,37 +1615,37 @@
         <v>2303</v>
       </c>
       <c r="M4">
-        <v>124.8570358395787</v>
+        <v>122.2685963417953</v>
       </c>
       <c r="N4">
-        <v>2178.142964160421</v>
+        <v>2180.731403658205</v>
       </c>
       <c r="O4">
-        <v>544.5357410401053</v>
+        <v>545.1828509145512</v>
       </c>
       <c r="P4">
-        <v>1633.607223120316</v>
+        <v>1635.548552743654</v>
       </c>
       <c r="Q4">
-        <v>2233.607223120316</v>
+        <v>2235.548552743654</v>
       </c>
       <c r="R4">
         <v>0.02040816326530612</v>
       </c>
       <c r="S4">
-        <v>0.1088619614216519</v>
+        <v>0.10884489929096</v>
       </c>
       <c r="T4">
         <v>0.9752845413505058</v>
       </c>
       <c r="U4">
-        <v>0.06753097776675758</v>
+        <v>0.06613097776675758</v>
       </c>
       <c r="V4">
         <v>0.25</v>
       </c>
       <c r="W4">
-        <v>0.05064823332506818</v>
+        <v>0.04959823332506819</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>18.44509590119523</v>
+        <v>18.83558058981954</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1664,13 +1664,13 @@
         <v>0.03</v>
       </c>
       <c r="B5">
-        <v>0.1075908909965055</v>
+        <v>0.107542712120709</v>
       </c>
       <c r="C5">
-        <v>89796.07950260914</v>
+        <v>89842.4676446427</v>
       </c>
       <c r="D5">
-        <v>90407.40753594853</v>
+        <v>90453.7956779821</v>
       </c>
       <c r="E5">
         <v>-3463.139744640386</v>
@@ -1697,37 +1697,37 @@
         <v>2303</v>
       </c>
       <c r="M5">
-        <v>187.2855537593681</v>
+        <v>183.4028945126929</v>
       </c>
       <c r="N5">
-        <v>2115.714446240632</v>
+        <v>2119.597105487307</v>
       </c>
       <c r="O5">
-        <v>528.9286115601579</v>
+        <v>529.8992763718268</v>
       </c>
       <c r="P5">
-        <v>1586.785834680474</v>
+        <v>1589.69782911548</v>
       </c>
       <c r="Q5">
-        <v>2186.785834680474</v>
+        <v>2189.69782911548</v>
       </c>
       <c r="R5">
         <v>0.03092783505154639</v>
       </c>
       <c r="S5">
-        <v>0.1093520041203644</v>
+        <v>0.1093348094030484</v>
       </c>
       <c r="T5">
         <v>0.982863294974428</v>
       </c>
       <c r="U5">
-        <v>0.06753097776675758</v>
+        <v>0.06613097776675758</v>
       </c>
       <c r="V5">
         <v>0.25</v>
       </c>
       <c r="W5">
-        <v>0.05064823332506818</v>
+        <v>0.04959823332506819</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>12.29673060079682</v>
+        <v>12.55705372654636</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1746,13 +1746,13 @@
         <v>0.04</v>
       </c>
       <c r="B6">
-        <v>0.1074840951332909</v>
+        <v>0.107425458269776</v>
       </c>
       <c r="C6">
-        <v>89028.16237826315</v>
+        <v>89090.13007037916</v>
       </c>
       <c r="D6">
-        <v>90563.93308938234</v>
+        <v>90625.90078149835</v>
       </c>
       <c r="E6">
         <v>-2538.697066860588</v>
@@ -1779,37 +1779,37 @@
         <v>2303</v>
       </c>
       <c r="M6">
-        <v>249.7140716791575</v>
+        <v>244.5371926835906</v>
       </c>
       <c r="N6">
-        <v>2053.285928320843</v>
+        <v>2058.462807316409</v>
       </c>
       <c r="O6">
-        <v>513.3214820802107</v>
+        <v>514.6157018291024</v>
       </c>
       <c r="P6">
-        <v>1539.964446240632</v>
+        <v>1543.847105487307</v>
       </c>
       <c r="Q6">
-        <v>2139.964446240632</v>
+        <v>2143.847105487307</v>
       </c>
       <c r="R6">
         <v>0.04166666666666667</v>
       </c>
       <c r="S6">
-        <v>0.1098522560419668</v>
+        <v>0.1098349259758054</v>
       </c>
       <c r="T6">
         <v>0.990599939298849</v>
       </c>
       <c r="U6">
-        <v>0.06753097776675758</v>
+        <v>0.06613097776675758</v>
       </c>
       <c r="V6">
         <v>0.25</v>
       </c>
       <c r="W6">
-        <v>0.05064823332506818</v>
+        <v>0.04959823332506819</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>9.222547950597617</v>
+        <v>9.41779029490977</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1828,13 +1828,13 @@
         <v>0.05</v>
       </c>
       <c r="B7">
-        <v>0.1074185492700761</v>
+        <v>0.1073644544188429</v>
       </c>
       <c r="C7">
-        <v>88200.05580772347</v>
+        <v>88255.48805751454</v>
       </c>
       <c r="D7">
-        <v>90660.26919662247</v>
+        <v>90715.70144641353</v>
       </c>
       <c r="E7">
         <v>-1614.25438908079</v>
@@ -1861,37 +1861,37 @@
         <v>2303</v>
       </c>
       <c r="M7">
-        <v>317.2270243267358</v>
+        <v>312.6048109378368</v>
       </c>
       <c r="N7">
-        <v>1985.772975673264</v>
+        <v>1990.395189062163</v>
       </c>
       <c r="O7">
-        <v>496.4432439183161</v>
+        <v>497.5987972655408</v>
       </c>
       <c r="P7">
-        <v>1489.329731754948</v>
+        <v>1492.796391796623</v>
       </c>
       <c r="Q7">
-        <v>2089.329731754948</v>
+        <v>2092.796391796623</v>
       </c>
       <c r="R7">
         <v>0.05263157894736843</v>
       </c>
       <c r="S7">
-        <v>0.1103630395829713</v>
+        <v>0.1103455713185152</v>
       </c>
       <c r="T7">
         <v>0.9984994603458893</v>
       </c>
       <c r="U7">
-        <v>0.06863097776675758</v>
+        <v>0.06763097776675758</v>
       </c>
       <c r="V7">
         <v>0.25</v>
       </c>
       <c r="W7">
-        <v>0.05147323332506819</v>
+        <v>0.05072323332506819</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>7.25978502269078</v>
+        <v>7.367129101726988</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1910,13 +1910,13 @@
         <v>0.06</v>
       </c>
       <c r="B8">
-        <v>0.1074190034068615</v>
+        <v>0.1073349505679098</v>
       </c>
       <c r="C8">
-        <v>87274.94495680013</v>
+        <v>87374.54037742411</v>
       </c>
       <c r="D8">
-        <v>90659.60102347891</v>
+        <v>90759.1964441029</v>
       </c>
       <c r="E8">
         <v>-689.811711300993</v>
@@ -1943,37 +1943,37 @@
         <v>2303</v>
       </c>
       <c r="M8">
-        <v>392.8750725387762</v>
+        <v>384.555088438758</v>
       </c>
       <c r="N8">
-        <v>1910.124927461224</v>
+        <v>1918.444911561242</v>
       </c>
       <c r="O8">
-        <v>477.5312318653059</v>
+        <v>479.6112278903105</v>
       </c>
       <c r="P8">
-        <v>1432.593695595918</v>
+        <v>1438.833683670931</v>
       </c>
       <c r="Q8">
-        <v>2032.593695595918</v>
+        <v>2038.833683670931</v>
       </c>
       <c r="R8">
         <v>0.06382978723404255</v>
       </c>
       <c r="S8">
-        <v>0.1108846908588908</v>
+        <v>0.1108670814557507</v>
       </c>
       <c r="T8">
         <v>1.006567056308824</v>
       </c>
       <c r="U8">
-        <v>0.07083097776675758</v>
+        <v>0.06933097776675758</v>
       </c>
       <c r="V8">
         <v>0.25</v>
       </c>
       <c r="W8">
-        <v>0.05312323332506819</v>
+        <v>0.05199823332506819</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>5.861914285164268</v>
+        <v>5.988738854944998</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1992,13 +1992,13 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="B9">
-        <v>0.1074157075436467</v>
+        <v>0.1072836967169767</v>
       </c>
       <c r="C9">
-        <v>86355.35171848934</v>
+        <v>86525.75610298928</v>
       </c>
       <c r="D9">
-        <v>90664.45046294793</v>
+        <v>90834.85484744787</v>
       </c>
       <c r="E9">
         <v>234.6309664788059</v>
@@ -2025,37 +2025,37 @@
         <v>2303</v>
       </c>
       <c r="M9">
-        <v>468.0608994119268</v>
+        <v>453.824482174118</v>
       </c>
       <c r="N9">
-        <v>1834.939100588073</v>
+        <v>1849.175517825882</v>
       </c>
       <c r="O9">
-        <v>458.7347751470183</v>
+        <v>462.2938794564705</v>
       </c>
       <c r="P9">
-        <v>1376.204325441055</v>
+        <v>1386.881638369412</v>
       </c>
       <c r="Q9">
-        <v>1976.204325441055</v>
+        <v>1986.881638369412</v>
       </c>
       <c r="R9">
         <v>0.07526881720430109</v>
       </c>
       <c r="S9">
-        <v>0.1114175604418193</v>
+        <v>0.1113998068647547</v>
       </c>
       <c r="T9">
         <v>1.014808148959134</v>
       </c>
       <c r="U9">
-        <v>0.07233097776675758</v>
+        <v>0.07013097776675759</v>
       </c>
       <c r="V9">
         <v>0.25</v>
       </c>
       <c r="W9">
-        <v>0.05424823332506819</v>
+        <v>0.05259823332506819</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>4.920299907327223</v>
+        <v>5.074649099949641</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2074,13 +2074,13 @@
         <v>0.08</v>
       </c>
       <c r="B10">
-        <v>0.1073449116804321</v>
+        <v>0.1071964428660436</v>
       </c>
       <c r="C10">
-        <v>85535.2014648621</v>
+        <v>85730.40381733007</v>
       </c>
       <c r="D10">
-        <v>90768.74288710048</v>
+        <v>90963.94523956845</v>
       </c>
       <c r="E10">
         <v>1159.073644258603</v>
@@ -2107,37 +2107,37 @@
         <v>2303</v>
       </c>
       <c r="M10">
-        <v>534.9267421850592</v>
+        <v>518.6565510561347</v>
       </c>
       <c r="N10">
-        <v>1768.073257814941</v>
+        <v>1784.343448943865</v>
       </c>
       <c r="O10">
-        <v>442.0183144537352</v>
+        <v>446.0858622359663</v>
       </c>
       <c r="P10">
-        <v>1326.054943361206</v>
+        <v>1338.257586707899</v>
       </c>
       <c r="Q10">
-        <v>1926.054943361206</v>
+        <v>1938.257586707899</v>
       </c>
       <c r="R10">
         <v>0.08695652173913043</v>
       </c>
       <c r="S10">
-        <v>0.1119620141461159</v>
+        <v>0.111944113260911</v>
       </c>
       <c r="T10">
         <v>1.023228395797494</v>
       </c>
       <c r="U10">
-        <v>0.07233097776675758</v>
+        <v>0.07013097776675759</v>
       </c>
       <c r="V10">
         <v>0.25</v>
       </c>
       <c r="W10">
-        <v>0.05424823332506819</v>
+        <v>0.05259823332506819</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>4.305262418911321</v>
+        <v>4.440317962455937</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2156,13 +2156,13 @@
         <v>0.09</v>
       </c>
       <c r="B11">
-        <v>0.1073686158172174</v>
+        <v>0.1071766890151105</v>
       </c>
       <c r="C11">
-        <v>84575.81249718013</v>
+        <v>84835.23753492745</v>
       </c>
       <c r="D11">
-        <v>90733.79659719831</v>
+        <v>90993.22163494563</v>
       </c>
       <c r="E11">
         <v>2083.516322038401</v>
@@ -2189,37 +2189,37 @@
         <v>2303</v>
       </c>
       <c r="M11">
-        <v>613.440562698217</v>
+        <v>591.8086040381698</v>
       </c>
       <c r="N11">
-        <v>1689.559437301783</v>
+        <v>1711.19139596183</v>
       </c>
       <c r="O11">
-        <v>422.3898593254457</v>
+        <v>427.7978489904575</v>
       </c>
       <c r="P11">
-        <v>1267.169577976337</v>
+        <v>1283.393546971372</v>
       </c>
       <c r="Q11">
-        <v>1867.169577976337</v>
+        <v>1883.393546971372</v>
       </c>
       <c r="R11">
         <v>0.0989010989010989</v>
       </c>
       <c r="S11">
-        <v>0.1125184338658915</v>
+        <v>0.1125003824350048</v>
       </c>
       <c r="T11">
         <v>1.031833703005927</v>
       </c>
       <c r="U11">
-        <v>0.07373097776675758</v>
+        <v>0.07113097776675759</v>
       </c>
       <c r="V11">
         <v>0.25</v>
       </c>
       <c r="W11">
-        <v>0.05529823332506818</v>
+        <v>0.05334823332506819</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>3.754234949626186</v>
+        <v>3.891460827513524</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2238,13 +2238,13 @@
         <v>0.1</v>
       </c>
       <c r="B12">
-        <v>0.1073083199540027</v>
+        <v>0.1070969351641774</v>
       </c>
       <c r="C12">
-        <v>83740.31506441216</v>
+        <v>84029.18674435632</v>
       </c>
       <c r="D12">
-        <v>90822.74184221015</v>
+        <v>91111.61352215431</v>
       </c>
       <c r="E12">
         <v>3007.958999818199</v>
@@ -2271,37 +2271,37 @@
         <v>2303</v>
       </c>
       <c r="M12">
-        <v>681.6006252202411</v>
+        <v>657.5651155979665</v>
       </c>
       <c r="N12">
-        <v>1621.399374779759</v>
+        <v>1645.434884402034</v>
       </c>
       <c r="O12">
-        <v>405.3498436949398</v>
+        <v>411.3587211005084</v>
       </c>
       <c r="P12">
-        <v>1216.049531084819</v>
+        <v>1234.076163301525</v>
       </c>
       <c r="Q12">
-        <v>1816.049531084819</v>
+        <v>1834.076163301525</v>
       </c>
       <c r="R12">
         <v>0.1111111111111111</v>
       </c>
       <c r="S12">
-        <v>0.1130872184683287</v>
+        <v>0.1130690131463007</v>
       </c>
       <c r="T12">
         <v>1.040630239263437</v>
       </c>
       <c r="U12">
-        <v>0.07373097776675758</v>
+        <v>0.07113097776675759</v>
       </c>
       <c r="V12">
         <v>0.25</v>
       </c>
       <c r="W12">
-        <v>0.05529823332506818</v>
+        <v>0.05334823332506819</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>3.378811454663568</v>
+        <v>3.502314744762172</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2320,13 +2320,13 @@
         <v>0.11</v>
       </c>
       <c r="B13">
-        <v>0.107248024090788</v>
+        <v>0.1070171813132443</v>
       </c>
       <c r="C13">
-        <v>82904.99218665733</v>
+        <v>83223.44443610085</v>
       </c>
       <c r="D13">
-        <v>90911.8616422351</v>
+        <v>91230.31389167863</v>
       </c>
       <c r="E13">
         <v>3932.401677597997</v>
@@ -2353,37 +2353,37 @@
         <v>2303</v>
       </c>
       <c r="M13">
-        <v>749.7606877422653</v>
+        <v>723.3216271577631</v>
       </c>
       <c r="N13">
-        <v>1553.239312257735</v>
+        <v>1579.678372842237</v>
       </c>
       <c r="O13">
-        <v>388.3098280644336</v>
+        <v>394.9195932105592</v>
       </c>
       <c r="P13">
-        <v>1164.929484193301</v>
+        <v>1184.758779631678</v>
       </c>
       <c r="Q13">
-        <v>1764.929484193301</v>
+        <v>1784.758779631678</v>
       </c>
       <c r="R13">
         <v>0.1235955056179775</v>
       </c>
       <c r="S13">
-        <v>0.1136687847472253</v>
+        <v>0.1136504220758279</v>
       </c>
       <c r="T13">
         <v>1.049624450493026</v>
       </c>
       <c r="U13">
-        <v>0.07373097776675758</v>
+        <v>0.07113097776675759</v>
       </c>
       <c r="V13">
         <v>0.25</v>
       </c>
       <c r="W13">
-        <v>0.05529823332506818</v>
+        <v>0.05334823332506819</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>3.071646776966879</v>
+        <v>3.183922495238338</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2402,13 +2402,13 @@
         <v>0.12</v>
       </c>
       <c r="B14">
-        <v>0.1074217282275733</v>
+        <v>0.1071624274623112</v>
       </c>
       <c r="C14">
-        <v>81724.2800580794</v>
+        <v>82083.057697453</v>
       </c>
       <c r="D14">
-        <v>90655.59219143697</v>
+        <v>91014.36983081057</v>
       </c>
       <c r="E14">
         <v>4856.844355377793</v>
@@ -2435,37 +2435,37 @@
         <v>2303</v>
       </c>
       <c r="M14">
-        <v>846.7633618110189</v>
+        <v>816.8114190509534</v>
       </c>
       <c r="N14">
-        <v>1456.236638188981</v>
+        <v>1486.188580949047</v>
       </c>
       <c r="O14">
-        <v>364.0591595472453</v>
+        <v>371.5471452372616</v>
       </c>
       <c r="P14">
-        <v>1092.177478641736</v>
+        <v>1114.641435711785</v>
       </c>
       <c r="Q14">
-        <v>1692.177478641736</v>
+        <v>1714.641435711785</v>
       </c>
       <c r="R14">
         <v>0.1363636363636364</v>
       </c>
       <c r="S14">
-        <v>0.1142635684415513</v>
+        <v>0.1142450448446626</v>
       </c>
       <c r="T14">
         <v>1.058823075614197</v>
       </c>
       <c r="U14">
-        <v>0.07633097776675757</v>
+        <v>0.07363097776675757</v>
       </c>
       <c r="V14">
         <v>0.25</v>
       </c>
       <c r="W14">
-        <v>0.05724823332506818</v>
+        <v>0.05522323332506818</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>2.719768123970844</v>
+        <v>2.819500249734311</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2484,13 +2484,13 @@
         <v>0.13</v>
       </c>
       <c r="B15">
-        <v>0.1073809323643586</v>
+        <v>0.1071014236113782</v>
       </c>
       <c r="C15">
-        <v>80859.89449533008</v>
+        <v>81249.18758263887</v>
       </c>
       <c r="D15">
-        <v>90715.64930646746</v>
+        <v>91104.94239377625</v>
       </c>
       <c r="E15">
         <v>5781.287033157593</v>
@@ -2517,37 +2517,37 @@
         <v>2303</v>
       </c>
       <c r="M15">
-        <v>917.3269752952706</v>
+        <v>884.8790373051997</v>
       </c>
       <c r="N15">
-        <v>1385.673024704729</v>
+        <v>1418.1209626948</v>
       </c>
       <c r="O15">
-        <v>346.4182561761824</v>
+        <v>354.5302406737001</v>
       </c>
       <c r="P15">
-        <v>1039.254768528547</v>
+        <v>1063.5907220211</v>
       </c>
       <c r="Q15">
-        <v>1639.254768528547</v>
+        <v>1663.5907220211</v>
       </c>
       <c r="R15">
         <v>0.1494252873563219</v>
       </c>
       <c r="S15">
-        <v>0.1148720253242526</v>
+        <v>0.114853337102436</v>
       </c>
       <c r="T15">
         <v>1.068233163381831</v>
       </c>
       <c r="U15">
-        <v>0.07633097776675757</v>
+        <v>0.07363097776675757</v>
       </c>
       <c r="V15">
         <v>0.25</v>
       </c>
       <c r="W15">
-        <v>0.05724823332506818</v>
+        <v>0.05522323332506818</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>2.510555191357702</v>
+        <v>2.602615615139364</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2566,13 +2566,13 @@
         <v>0.14</v>
       </c>
       <c r="B16">
-        <v>0.1076236365011439</v>
+        <v>0.1074079197604451</v>
       </c>
       <c r="C16">
-        <v>79579.32486346152</v>
+        <v>79871.50262508025</v>
       </c>
       <c r="D16">
-        <v>90359.52235237868</v>
+        <v>90651.70011399742</v>
       </c>
       <c r="E16">
         <v>6705.729710937391</v>
@@ -2599,37 +2599,37 @@
         <v>2303</v>
       </c>
       <c r="M16">
-        <v>1022.834521999599</v>
+        <v>998.2443467706561</v>
       </c>
       <c r="N16">
-        <v>1280.165478000401</v>
+        <v>1304.755653229344</v>
       </c>
       <c r="O16">
-        <v>320.0413695001004</v>
+        <v>326.188913307336</v>
       </c>
       <c r="P16">
-        <v>960.1241085003011</v>
+        <v>978.5667399220079</v>
       </c>
       <c r="Q16">
-        <v>1560.124108500301</v>
+        <v>1578.566739922008</v>
       </c>
       <c r="R16">
         <v>0.1627906976744186</v>
       </c>
       <c r="S16">
-        <v>0.1154946323670167</v>
+        <v>0.1154757756917855</v>
       </c>
       <c r="T16">
         <v>1.077862090399875</v>
       </c>
       <c r="U16">
-        <v>0.07903097776675758</v>
+        <v>0.07713097776675758</v>
       </c>
       <c r="V16">
         <v>0.25</v>
       </c>
       <c r="W16">
-        <v>0.05927323332506818</v>
+        <v>0.05784823332506818</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>2.251586107494428</v>
+        <v>2.307050380450697</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2648,13 +2648,13 @@
         <v>0.15</v>
       </c>
       <c r="B17">
-        <v>0.1091780906379292</v>
+        <v>0.107688165909512</v>
       </c>
       <c r="C17">
-        <v>76438.66311210582</v>
+        <v>78536.5648309892</v>
       </c>
       <c r="D17">
-        <v>88143.30327880278</v>
+        <v>90241.20499768616</v>
       </c>
       <c r="E17">
         <v>7630.172388717187</v>
@@ -2681,45 +2681,45 @@
         <v>2303</v>
       </c>
       <c r="M17">
-        <v>1290.027093047613</v>
+        <v>1108.374106863883</v>
       </c>
       <c r="N17">
-        <v>1012.972906952387</v>
+        <v>1194.625893136117</v>
       </c>
       <c r="O17">
-        <v>253.2432267380967</v>
+        <v>298.6564732840292</v>
       </c>
       <c r="P17">
-        <v>759.7296802142902</v>
+        <v>895.9694198520876</v>
       </c>
       <c r="Q17">
-        <v>1359.72968021429</v>
+        <v>1495.969419852088</v>
       </c>
       <c r="R17">
         <v>0.1764705882352941</v>
       </c>
       <c r="S17">
-        <v>0.1161318889872577</v>
+        <v>0.1161128598950021</v>
       </c>
       <c r="T17">
         <v>1.087717580406579</v>
       </c>
       <c r="U17">
-        <v>0.09303097776675757</v>
+        <v>0.07993097776675759</v>
       </c>
       <c r="V17">
         <v>0.25</v>
       </c>
       <c r="W17">
-        <v>0.06977323332506818</v>
+        <v>0.05994823332506819</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y17">
-        <v>1.785233823701561</v>
+        <v>2.077818297755332</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2730,13 +2730,13 @@
         <v>0.16</v>
       </c>
       <c r="B18">
-        <v>0.1098265447747145</v>
+        <v>0.1086104120585789</v>
       </c>
       <c r="C18">
-        <v>74621.5142943621</v>
+        <v>76287.10929198733</v>
       </c>
       <c r="D18">
-        <v>87250.59713883887</v>
+        <v>88916.1921364641</v>
       </c>
       <c r="E18">
         <v>8554.615066496986</v>
@@ -2763,45 +2763,45 @@
         <v>2303</v>
       </c>
       <c r="M18">
-        <v>1445.546988619828</v>
+        <v>1297.636160175061</v>
       </c>
       <c r="N18">
-        <v>857.453011380172</v>
+        <v>1005.363839824939</v>
       </c>
       <c r="O18">
-        <v>214.363252845043</v>
+        <v>251.3409599562348</v>
       </c>
       <c r="P18">
-        <v>643.089758535129</v>
+        <v>754.0228798687044</v>
       </c>
       <c r="Q18">
-        <v>1243.089758535129</v>
+        <v>1354.022879868704</v>
       </c>
       <c r="R18">
         <v>0.1904761904761905</v>
       </c>
       <c r="S18">
-        <v>0.116784318384171</v>
+        <v>0.1167651127697238</v>
       </c>
       <c r="T18">
         <v>1.097807724937253</v>
       </c>
       <c r="U18">
-        <v>0.09773097776675757</v>
+        <v>0.08773097776675759</v>
       </c>
       <c r="V18">
         <v>0.25</v>
       </c>
       <c r="W18">
-        <v>0.07329823332506819</v>
+        <v>0.06579823332506819</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y18">
-        <v>1.593168550127068</v>
+        <v>1.774765585824387</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2812,13 +2812,13 @@
         <v>0.17</v>
       </c>
       <c r="B19">
-        <v>0.1120244989114998</v>
+        <v>0.1091524082076458</v>
       </c>
       <c r="C19">
-        <v>70801.27302134375</v>
+        <v>74601.96571757075</v>
       </c>
       <c r="D19">
-        <v>84354.79854360031</v>
+        <v>88155.49123982732</v>
       </c>
       <c r="E19">
         <v>9479.057744276786</v>
@@ -2845,45 +2845,45 @@
         <v>2303</v>
       </c>
       <c r="M19">
-        <v>1792.05674142135</v>
+        <v>1440.028969722802</v>
       </c>
       <c r="N19">
-        <v>510.9432585786503</v>
+        <v>862.9710302771975</v>
       </c>
       <c r="O19">
-        <v>127.7358146446626</v>
+        <v>215.7427575692994</v>
       </c>
       <c r="P19">
-        <v>383.2074439339877</v>
+        <v>647.2282727078982</v>
       </c>
       <c r="Q19">
-        <v>983.2074439339877</v>
+        <v>1247.228272707898</v>
       </c>
       <c r="R19">
         <v>0.2048192771084338</v>
       </c>
       <c r="S19">
-        <v>0.1174524689713714</v>
+        <v>0.1174330825811858</v>
       </c>
       <c r="T19">
         <v>1.108141005480713</v>
       </c>
       <c r="U19">
-        <v>0.1140309777667576</v>
+        <v>0.09163097776675758</v>
       </c>
       <c r="V19">
         <v>0.25</v>
       </c>
       <c r="W19">
-        <v>0.08552323332506818</v>
+        <v>0.06872323332506819</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y19">
-        <v>1.285115558435612</v>
+        <v>1.599273381592674</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2894,13 +2894,13 @@
         <v>0.18</v>
       </c>
       <c r="B20">
-        <v>0.1172144305020097</v>
+        <v>0.1092264043567127</v>
       </c>
       <c r="C20">
-        <v>63746.47782664227</v>
+        <v>73574.67680505622</v>
       </c>
       <c r="D20">
-        <v>78224.44602667863</v>
+        <v>88052.64500509259</v>
       </c>
       <c r="E20">
         <v>10403.50042205658</v>
@@ -2927,45 +2927,45 @@
         <v>2303</v>
       </c>
       <c r="M20">
-        <v>2441.598803999088</v>
+        <v>1524.736556177085</v>
       </c>
       <c r="N20">
-        <v>-138.5988039990884</v>
+        <v>778.2634438229152</v>
       </c>
       <c r="O20">
-        <v>-34.64970099977211</v>
+        <v>194.5658609557288</v>
       </c>
       <c r="P20">
-        <v>-103.9491029993163</v>
+        <v>583.6975828671864</v>
       </c>
       <c r="Q20">
-        <v>496.0508970006837</v>
+        <v>1183.697582867186</v>
       </c>
       <c r="R20">
         <v>0.2195121951219512</v>
       </c>
       <c r="S20">
-        <v>0.1183304040366341</v>
+        <v>0.1181173443392688</v>
       </c>
       <c r="T20">
-        <v>1.121718707127752</v>
+        <v>1.118726317256941</v>
       </c>
       <c r="U20">
-        <v>0.1467309777667576</v>
+        <v>0.09163097776675758</v>
       </c>
       <c r="V20">
-        <v>0.2358086017477485</v>
+        <v>0.25</v>
       </c>
       <c r="W20">
-        <v>0.1121305510664985</v>
+        <v>0.06872323332506819</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y20">
-        <v>0.9432344069909938</v>
+        <v>1.510424860393081</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2976,13 +2976,13 @@
         <v>0.19</v>
       </c>
       <c r="B21">
-        <v>0.1182237402796772</v>
+        <v>0.1156294966694496</v>
       </c>
       <c r="C21">
-        <v>61731.88573207639</v>
+        <v>64576.1502338016</v>
       </c>
       <c r="D21">
-        <v>77134.29660989255</v>
+        <v>79978.56111161776</v>
       </c>
       <c r="E21">
         <v>11327.94309983638</v>
@@ -3009,37 +3009,37 @@
         <v>2303</v>
       </c>
       <c r="M21">
-        <v>2577.243181999037</v>
+        <v>2361.200928201899</v>
       </c>
       <c r="N21">
-        <v>-274.2431819990375</v>
+        <v>-58.20092820189893</v>
       </c>
       <c r="O21">
-        <v>-68.56079549975937</v>
+        <v>-14.55023205047473</v>
       </c>
       <c r="P21">
-        <v>-205.6823864992781</v>
+        <v>-43.6506961514242</v>
       </c>
       <c r="Q21">
-        <v>394.3176135007219</v>
+        <v>556.3493038485758</v>
       </c>
       <c r="R21">
         <v>0.2345679012345679</v>
       </c>
       <c r="S21">
-        <v>0.1192258411235061</v>
+        <v>0.1189082564195213</v>
       </c>
       <c r="T21">
-        <v>1.135567086228094</v>
+        <v>1.130961475598264</v>
       </c>
       <c r="U21">
-        <v>0.1467309777667576</v>
+        <v>0.1344309777667576</v>
       </c>
       <c r="V21">
-        <v>0.2233976227083933</v>
+        <v>0.2438377831904568</v>
       </c>
       <c r="W21">
-        <v>0.1139516261559858</v>
+        <v>0.1016516261559858</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>0.8935904908335732</v>
+        <v>0.9753511327618273</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3058,13 +3058,13 @@
         <v>0.2</v>
       </c>
       <c r="B22">
-        <v>0.1192330500573448</v>
+        <v>0.1165158064471172</v>
       </c>
       <c r="C22">
-        <v>59747.2610286136</v>
+        <v>62649.30393116854</v>
       </c>
       <c r="D22">
-        <v>76074.11458420956</v>
+        <v>78976.1574867645</v>
       </c>
       <c r="E22">
         <v>12252.38577761618</v>
@@ -3091,37 +3091,37 @@
         <v>2303</v>
       </c>
       <c r="M22">
-        <v>2712.887559998987</v>
+        <v>2485.474661265157</v>
       </c>
       <c r="N22">
-        <v>-409.8875599989874</v>
+        <v>-182.474661265157</v>
       </c>
       <c r="O22">
-        <v>-102.4718899997468</v>
+        <v>-45.61866531628925</v>
       </c>
       <c r="P22">
-        <v>-307.4156699992405</v>
+        <v>-136.8559959488678</v>
       </c>
       <c r="Q22">
-        <v>292.5843300007595</v>
+        <v>463.1440040511322</v>
       </c>
       <c r="R22">
         <v>0.25</v>
       </c>
       <c r="S22">
-        <v>0.1201436641375499</v>
+        <v>0.1198221096247654</v>
       </c>
       <c r="T22">
-        <v>1.149761674805946</v>
+        <v>1.145098494043242</v>
       </c>
       <c r="U22">
-        <v>0.1467309777667576</v>
+        <v>0.1344309777667576</v>
       </c>
       <c r="V22">
-        <v>0.2122277415729736</v>
+        <v>0.2316458940309339</v>
       </c>
       <c r="W22">
-        <v>0.1155905937365244</v>
+        <v>0.1032905937365244</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>0.8489109662918943</v>
+        <v>0.9265835761237358</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3140,13 +3140,13 @@
         <v>0.21</v>
       </c>
       <c r="B23">
-        <v>0.1202423598350124</v>
+        <v>0.1174021162247847</v>
       </c>
       <c r="C23">
-        <v>57791.38479811705</v>
+        <v>60747.27365858378</v>
       </c>
       <c r="D23">
-        <v>75042.6810314928</v>
+        <v>77998.56989195953</v>
       </c>
       <c r="E23">
         <v>13176.82845539597</v>
@@ -3173,37 +3173,37 @@
         <v>2303</v>
       </c>
       <c r="M23">
-        <v>2848.531937998936</v>
+        <v>2609.748394328415</v>
       </c>
       <c r="N23">
-        <v>-545.5319379989364</v>
+        <v>-306.7483943284146</v>
       </c>
       <c r="O23">
-        <v>-136.3829844997341</v>
+        <v>-76.68709858210366</v>
       </c>
       <c r="P23">
-        <v>-409.1489534992023</v>
+        <v>-230.061295746311</v>
       </c>
       <c r="Q23">
-        <v>190.8510465007977</v>
+        <v>369.938704253689</v>
       </c>
       <c r="R23">
         <v>0.2658227848101266</v>
       </c>
       <c r="S23">
-        <v>0.1210847231772658</v>
+        <v>0.1207590983541928</v>
       </c>
       <c r="T23">
-        <v>1.164315620056654</v>
+        <v>1.159593411689359</v>
       </c>
       <c r="U23">
-        <v>0.1467309777667576</v>
+        <v>0.1344309777667576</v>
       </c>
       <c r="V23">
-        <v>0.2021216586409273</v>
+        <v>0.2206151371723181</v>
       </c>
       <c r="W23">
-        <v>0.1170734691665355</v>
+        <v>0.1047734691665355</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>0.8084866345637091</v>
+        <v>0.8824605486892723</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3222,13 +3222,13 @@
         <v>0.22</v>
       </c>
       <c r="B24">
-        <v>0.1408959733683335</v>
+        <v>0.1182884260024523</v>
       </c>
       <c r="C24">
-        <v>40568.64391032232</v>
+        <v>58869.14914562393</v>
       </c>
       <c r="D24">
-        <v>58744.38282147788</v>
+        <v>77044.88805677948</v>
       </c>
       <c r="E24">
         <v>14101.27113317577</v>
@@ -3255,45 +3255,45 @@
         <v>2303</v>
       </c>
       <c r="M24">
-        <v>4710.850349555993</v>
+        <v>2734.022127391673</v>
       </c>
       <c r="N24">
-        <v>-2407.850349555993</v>
+        <v>-431.0221273916727</v>
       </c>
       <c r="O24">
-        <v>-601.9625873889981</v>
+        <v>-107.7555318479182</v>
       </c>
       <c r="P24">
-        <v>-1805.887762166994</v>
+        <v>-323.2665955437545</v>
       </c>
       <c r="Q24">
-        <v>-1205.887762166994</v>
+        <v>276.7334044562455</v>
       </c>
       <c r="R24">
         <v>0.282051282051282</v>
       </c>
       <c r="S24">
-        <v>0.1232887629047352</v>
+        <v>0.1217201124356568</v>
       </c>
       <c r="T24">
-        <v>1.198402188667336</v>
+        <v>1.174459993890505</v>
       </c>
       <c r="U24">
-        <v>0.2316309777667576</v>
+        <v>0.1344309777667576</v>
       </c>
       <c r="V24">
-        <v>0.1222178497039851</v>
+        <v>0.2105871763917581</v>
       </c>
       <c r="W24">
-        <v>0.2033215377392729</v>
+        <v>0.1061215377392729</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y24">
-        <v>0.4888713988159404</v>
+        <v>0.8423487055670326</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3304,13 +3304,13 @@
         <v>0.23</v>
       </c>
       <c r="B25">
-        <v>0.1427542831460011</v>
+        <v>0.1191747357801199</v>
       </c>
       <c r="C25">
-        <v>38518.25550391689</v>
+        <v>57014.0641033025</v>
       </c>
       <c r="D25">
-        <v>57618.43709285224</v>
+        <v>76114.24569223785</v>
       </c>
       <c r="E25">
         <v>15025.71381095557</v>
@@ -3337,45 +3337,45 @@
         <v>2303</v>
       </c>
       <c r="M25">
-        <v>4924.979910899447</v>
+        <v>2858.29586045493</v>
       </c>
       <c r="N25">
-        <v>-2621.979910899447</v>
+        <v>-555.2958604549303</v>
       </c>
       <c r="O25">
-        <v>-655.4949777248617</v>
+        <v>-138.8239651137326</v>
       </c>
       <c r="P25">
-        <v>-1966.484933174585</v>
+        <v>-416.4718953411978</v>
       </c>
       <c r="Q25">
-        <v>-1366.484933174585</v>
+        <v>183.5281046588022</v>
       </c>
       <c r="R25">
         <v>0.2987012987012987</v>
       </c>
       <c r="S25">
-        <v>0.1242951104749266</v>
+        <v>0.1227060879218342</v>
       </c>
       <c r="T25">
-        <v>1.213965853455223</v>
+        <v>1.189712721083888</v>
       </c>
       <c r="U25">
-        <v>0.2316309777667576</v>
+        <v>0.1344309777667576</v>
       </c>
       <c r="V25">
-        <v>0.1169040301516379</v>
+        <v>0.2014312122008121</v>
       </c>
       <c r="W25">
-        <v>0.2045523829578592</v>
+        <v>0.1073523829578592</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y25">
-        <v>0.4676161206065518</v>
+        <v>0.8057248488032486</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3386,13 +3386,13 @@
         <v>0.24</v>
       </c>
       <c r="B26">
-        <v>0.1446125929236686</v>
+        <v>0.1408806337021775</v>
       </c>
       <c r="C26">
-        <v>36510.21708337298</v>
+        <v>38713.54826445068</v>
       </c>
       <c r="D26">
-        <v>56534.84135008813</v>
+        <v>58738.17253116583</v>
       </c>
       <c r="E26">
         <v>15950.15648873537</v>
@@ -3419,37 +3419,37 @@
         <v>2303</v>
       </c>
       <c r="M26">
-        <v>5139.109472242901</v>
+        <v>4806.310108242173</v>
       </c>
       <c r="N26">
-        <v>-2836.109472242901</v>
+        <v>-2503.310108242173</v>
       </c>
       <c r="O26">
-        <v>-709.0273680607252</v>
+        <v>-625.8275270605432</v>
       </c>
       <c r="P26">
-        <v>-2127.082104182175</v>
+        <v>-1877.482581181629</v>
       </c>
       <c r="Q26">
-        <v>-1527.082104182175</v>
+        <v>-1277.482581181629</v>
       </c>
       <c r="R26">
         <v>0.3157894736842105</v>
       </c>
       <c r="S26">
-        <v>0.1253279408759124</v>
+        <v>0.1251543103213188</v>
       </c>
       <c r="T26">
-        <v>1.229939088369108</v>
+        <v>1.22758594297589</v>
       </c>
       <c r="U26">
-        <v>0.2316309777667576</v>
+        <v>0.2166309777667576</v>
       </c>
       <c r="V26">
-        <v>0.1120330288953197</v>
+        <v>0.1197904394501442</v>
       </c>
       <c r="W26">
-        <v>0.2056806577415633</v>
+        <v>0.1906806577415633</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>0.4481321155812787</v>
+        <v>0.4791617578005768</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3468,13 +3468,13 @@
         <v>0.25</v>
       </c>
       <c r="B27">
-        <v>0.1464709027013362</v>
+        <v>0.1425889434798451</v>
       </c>
       <c r="C27">
-        <v>34542.18340123481</v>
+        <v>36752.38598988954</v>
       </c>
       <c r="D27">
-        <v>55491.25034572976</v>
+        <v>57701.45293438448</v>
       </c>
       <c r="E27">
         <v>16874.59916651517</v>
@@ -3501,37 +3501,37 @@
         <v>2303</v>
       </c>
       <c r="M27">
-        <v>5353.239033586355</v>
+        <v>5006.573029418931</v>
       </c>
       <c r="N27">
-        <v>-3050.239033586355</v>
+        <v>-2703.573029418931</v>
       </c>
       <c r="O27">
-        <v>-762.5597583965887</v>
+        <v>-675.8932573547327</v>
       </c>
       <c r="P27">
-        <v>-2287.679275189766</v>
+        <v>-2027.679772064198</v>
       </c>
       <c r="Q27">
-        <v>-1687.679275189766</v>
+        <v>-1427.679772064198</v>
       </c>
       <c r="R27">
         <v>0.3333333333333333</v>
       </c>
       <c r="S27">
-        <v>0.1263883134209246</v>
+        <v>0.1262123677922698</v>
       </c>
       <c r="T27">
-        <v>1.246338276214029</v>
+        <v>1.243953755548902</v>
       </c>
       <c r="U27">
-        <v>0.2316309777667576</v>
+        <v>0.2166309777667576</v>
       </c>
       <c r="V27">
-        <v>0.1075517077395069</v>
+        <v>0.1149988218721384</v>
       </c>
       <c r="W27">
-        <v>0.206718670542571</v>
+        <v>0.1917186705425711</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>0.4302068309580276</v>
+        <v>0.4599952874885537</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3550,13 +3550,13 @@
         <v>0.26</v>
       </c>
       <c r="B28">
-        <v>0.1483292124790038</v>
+        <v>0.1442972532575126</v>
       </c>
       <c r="C28">
-        <v>32611.97923754106</v>
+        <v>34827.18488511357</v>
       </c>
       <c r="D28">
-        <v>54485.48885981581</v>
+        <v>56700.69450738832</v>
       </c>
       <c r="E28">
         <v>17799.04184429497</v>
@@ -3583,37 +3583,37 @@
         <v>2303</v>
       </c>
       <c r="M28">
-        <v>5567.36859492981</v>
+        <v>5206.835950595688</v>
       </c>
       <c r="N28">
-        <v>-3264.36859492981</v>
+        <v>-2903.835950595688</v>
       </c>
       <c r="O28">
-        <v>-816.0921487324524</v>
+        <v>-725.9589876489219</v>
       </c>
       <c r="P28">
-        <v>-2448.276446197357</v>
+        <v>-2177.876962946766</v>
       </c>
       <c r="Q28">
-        <v>-1848.276446197357</v>
+        <v>-1577.876962946766</v>
       </c>
       <c r="R28">
         <v>0.3513513513513514</v>
       </c>
       <c r="S28">
-        <v>0.1274773446833695</v>
+        <v>0.1272990214110842</v>
       </c>
       <c r="T28">
-        <v>1.263180685352057</v>
+        <v>1.260763941434698</v>
       </c>
       <c r="U28">
-        <v>0.2316309777667576</v>
+        <v>0.2166309777667576</v>
       </c>
       <c r="V28">
-        <v>0.1034151035956797</v>
+        <v>0.1105757902616716</v>
       </c>
       <c r="W28">
-        <v>0.2076768362050398</v>
+        <v>0.1926768362050398</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>0.4136604143827188</v>
+        <v>0.4423031610466862</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3632,13 +3632,13 @@
         <v>0.27</v>
       </c>
       <c r="B29">
-        <v>0.1501875222566714</v>
+        <v>0.1460055630351803</v>
       </c>
       <c r="C29">
-        <v>30717.58426565244</v>
+        <v>32936.10574630706</v>
       </c>
       <c r="D29">
-        <v>53515.53656570698</v>
+        <v>55734.05804636161</v>
       </c>
       <c r="E29">
         <v>18723.48452207476</v>
@@ -3665,37 +3665,37 @@
         <v>2303</v>
       </c>
       <c r="M29">
-        <v>5781.498156273264</v>
+        <v>5407.098871772445</v>
       </c>
       <c r="N29">
-        <v>-3478.498156273264</v>
+        <v>-3104.098871772445</v>
       </c>
       <c r="O29">
-        <v>-869.6245390683159</v>
+        <v>-776.0247179431112</v>
       </c>
       <c r="P29">
-        <v>-2608.873617204948</v>
+        <v>-2328.074153829334</v>
       </c>
       <c r="Q29">
-        <v>-2008.873617204948</v>
+        <v>-1728.074153829334</v>
       </c>
       <c r="R29">
         <v>0.3698630136986302</v>
       </c>
       <c r="S29">
-        <v>0.1285962124187582</v>
+        <v>0.128415446361921</v>
       </c>
       <c r="T29">
-        <v>1.280484530356879</v>
+        <v>1.278034680358461</v>
       </c>
       <c r="U29">
-        <v>0.2316309777667576</v>
+        <v>0.2166309777667576</v>
       </c>
       <c r="V29">
-        <v>0.0995849145736175</v>
+        <v>0.1064803906223504</v>
       </c>
       <c r="W29">
-        <v>0.2085640266332515</v>
+        <v>0.1935640266332515</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>0.3983396582944699</v>
+        <v>0.4259215624894015</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3714,13 +3714,13 @@
         <v>0.28</v>
       </c>
       <c r="B30">
-        <v>0.152045832034339</v>
+        <v>0.1477138728128478</v>
       </c>
       <c r="C30">
-        <v>28857.11950631898</v>
+        <v>31077.43268671717</v>
       </c>
       <c r="D30">
-        <v>52579.51448415332</v>
+        <v>54799.82766455151</v>
       </c>
       <c r="E30">
         <v>19647.92719985456</v>
@@ -3747,37 +3747,37 @@
         <v>2303</v>
       </c>
       <c r="M30">
-        <v>5995.627717616718</v>
+        <v>5607.361792949203</v>
       </c>
       <c r="N30">
-        <v>-3692.627717616718</v>
+        <v>-3304.361792949203</v>
       </c>
       <c r="O30">
-        <v>-923.1569294041794</v>
+        <v>-826.0904482373007</v>
       </c>
       <c r="P30">
-        <v>-2769.470788212539</v>
+        <v>-2478.271344711902</v>
       </c>
       <c r="Q30">
-        <v>-2169.470788212539</v>
+        <v>-1878.271344711902</v>
       </c>
       <c r="R30">
         <v>0.388888888888889</v>
       </c>
       <c r="S30">
-        <v>0.1297461598134631</v>
+        <v>0.1295628831169477</v>
       </c>
       <c r="T30">
-        <v>1.298269037722947</v>
+        <v>1.295785162030107</v>
       </c>
       <c r="U30">
-        <v>0.2316309777667576</v>
+        <v>0.2166309777667576</v>
       </c>
       <c r="V30">
-        <v>0.09602831048170259</v>
+        <v>0.102677519528695</v>
       </c>
       <c r="W30">
-        <v>0.209387846316591</v>
+        <v>0.194387846316591</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>0.3841132419268103</v>
+        <v>0.41071007811478</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3796,13 +3796,13 @@
         <v>0.29</v>
       </c>
       <c r="B31">
-        <v>0.1539041418120065</v>
+        <v>0.1494221825905154</v>
       </c>
       <c r="C31">
-        <v>27028.83517887482</v>
+        <v>29249.5629716611</v>
       </c>
       <c r="D31">
-        <v>51675.67283448896</v>
+        <v>53896.40062727524</v>
       </c>
       <c r="E31">
         <v>20572.36987763436</v>
@@ -3829,37 +3829,37 @@
         <v>2303</v>
       </c>
       <c r="M31">
-        <v>6209.757278960171</v>
+        <v>5807.624714125959</v>
       </c>
       <c r="N31">
-        <v>-3906.757278960171</v>
+        <v>-3504.624714125959</v>
       </c>
       <c r="O31">
-        <v>-976.6893197400427</v>
+        <v>-876.1561785314898</v>
       </c>
       <c r="P31">
-        <v>-2930.067959220128</v>
+        <v>-2628.468535594469</v>
       </c>
       <c r="Q31">
-        <v>-2330.067959220128</v>
+        <v>-2028.468535594469</v>
       </c>
       <c r="R31">
         <v>0.4084507042253521</v>
       </c>
       <c r="S31">
-        <v>0.130928500092526</v>
+        <v>0.1307426420340878</v>
       </c>
       <c r="T31">
-        <v>1.316554517127496</v>
+        <v>1.314035657269967</v>
       </c>
       <c r="U31">
-        <v>0.2316309777667576</v>
+        <v>0.2166309777667576</v>
       </c>
       <c r="V31">
-        <v>0.09271698943060941</v>
+        <v>0.09913691540701589</v>
       </c>
       <c r="W31">
-        <v>0.2101548508493554</v>
+        <v>0.1951548508493554</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>0.3708679577224376</v>
+        <v>0.3965476616280635</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3878,13 +3878,13 @@
         <v>0.3</v>
       </c>
       <c r="B32">
-        <v>0.1557624515896741</v>
+        <v>0.151130492368183</v>
       </c>
       <c r="C32">
-        <v>25231.09978428462</v>
+        <v>27450.99784270329</v>
       </c>
       <c r="D32">
-        <v>50802.38011767855</v>
+        <v>53022.27817609722</v>
       </c>
       <c r="E32">
         <v>21496.81255541416</v>
@@ -3911,37 +3911,37 @@
         <v>2303</v>
       </c>
       <c r="M32">
-        <v>6423.886840303626</v>
+        <v>6007.887635302716</v>
       </c>
       <c r="N32">
-        <v>-4120.886840303626</v>
+        <v>-3704.887635302716</v>
       </c>
       <c r="O32">
-        <v>-1030.221710075906</v>
+        <v>-926.2219088256791</v>
       </c>
       <c r="P32">
-        <v>-3090.66513022772</v>
+        <v>-2778.665726477037</v>
       </c>
       <c r="Q32">
-        <v>-2490.66513022772</v>
+        <v>-2178.665726477037</v>
       </c>
       <c r="R32">
         <v>0.4285714285714286</v>
       </c>
       <c r="S32">
-        <v>0.1321446215224192</v>
+        <v>0.1319561083488605</v>
       </c>
       <c r="T32">
-        <v>1.335362438800746</v>
+        <v>1.332807595230967</v>
       </c>
       <c r="U32">
-        <v>0.2316309777667576</v>
+        <v>0.2166309777667576</v>
       </c>
       <c r="V32">
-        <v>0.08962642311625575</v>
+        <v>0.09583235156011535</v>
       </c>
       <c r="W32">
-        <v>0.2108707217466021</v>
+        <v>0.1958707217466021</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>0.358505692465023</v>
+        <v>0.3833294062404614</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3960,13 +3960,13 @@
         <v>0.31</v>
       </c>
       <c r="B33">
-        <v>0.1576207613673417</v>
+        <v>0.1528388021458505</v>
       </c>
       <c r="C33">
-        <v>23462.39027674022</v>
+        <v>25680.33422049425</v>
       </c>
       <c r="D33">
-        <v>49958.11328791395</v>
+        <v>52176.05723166798</v>
       </c>
       <c r="E33">
         <v>22421.25523319396</v>
@@ -3993,37 +3993,37 @@
         <v>2303</v>
       </c>
       <c r="M33">
-        <v>6638.016401647081</v>
+        <v>6208.150556479474</v>
       </c>
       <c r="N33">
-        <v>-4335.016401647081</v>
+        <v>-3905.150556479474</v>
       </c>
       <c r="O33">
-        <v>-1083.75410041177</v>
+        <v>-976.2876391198686</v>
       </c>
       <c r="P33">
-        <v>-3251.262301235311</v>
+        <v>-2928.862917359605</v>
       </c>
       <c r="Q33">
-        <v>-2651.262301235311</v>
+        <v>-2328.862917359605</v>
       </c>
       <c r="R33">
         <v>0.4492753623188406</v>
       </c>
       <c r="S33">
-        <v>0.1333959928488311</v>
+        <v>0.1332047476002932</v>
       </c>
       <c r="T33">
-        <v>1.354715517623945</v>
+        <v>1.352123647335763</v>
       </c>
       <c r="U33">
-        <v>0.2316309777667576</v>
+        <v>0.2166309777667576</v>
       </c>
       <c r="V33">
-        <v>0.08673524817702169</v>
+        <v>0.09274098538075679</v>
       </c>
       <c r="W33">
-        <v>0.2115404074246717</v>
+        <v>0.1965404074246717</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>0.3469409927080868</v>
+        <v>0.3709639415230271</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4042,13 +4042,13 @@
         <v>0.32</v>
       </c>
       <c r="B34">
-        <v>0.1594790711450093</v>
+        <v>0.1545471119235181</v>
       </c>
       <c r="C34">
-        <v>21721.2831992458</v>
+        <v>23936.25718965053</v>
       </c>
       <c r="D34">
-        <v>49141.44888819933</v>
+        <v>51356.42287860406</v>
       </c>
       <c r="E34">
         <v>23345.69791097375</v>
@@ -4075,37 +4075,37 @@
         <v>2303</v>
       </c>
       <c r="M34">
-        <v>6852.145962990534</v>
+        <v>6408.41347765623</v>
       </c>
       <c r="N34">
-        <v>-4549.145962990534</v>
+        <v>-4105.41347765623</v>
       </c>
       <c r="O34">
-        <v>-1137.286490747633</v>
+        <v>-1026.353369414058</v>
       </c>
       <c r="P34">
-        <v>-3411.859472242901</v>
+        <v>-3079.060108242173</v>
       </c>
       <c r="Q34">
-        <v>-2811.859472242901</v>
+        <v>-2479.060108242173</v>
       </c>
       <c r="R34">
         <v>0.4705882352941177</v>
       </c>
       <c r="S34">
-        <v>0.1346841692142551</v>
+        <v>0.1344901115355916</v>
       </c>
       <c r="T34">
-        <v>1.374637804647826</v>
+        <v>1.372007818620113</v>
       </c>
       <c r="U34">
-        <v>0.2316309777667576</v>
+        <v>0.2166309777667576</v>
       </c>
       <c r="V34">
-        <v>0.08402477167148976</v>
+        <v>0.08984282958760814</v>
       </c>
       <c r="W34">
-        <v>0.2121682377478619</v>
+        <v>0.1971682377478619</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>0.3360990866859591</v>
+        <v>0.3593713183504326</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4124,13 +4124,13 @@
         <v>0.33</v>
       </c>
       <c r="B35">
-        <v>0.1613373809226768</v>
+        <v>0.1562554217011857</v>
       </c>
       <c r="C35">
-        <v>20006.44667465717</v>
+        <v>22217.53318101047</v>
       </c>
       <c r="D35">
-        <v>48351.0550413905</v>
+        <v>50562.1415477438</v>
       </c>
       <c r="E35">
         <v>24270.14058875355</v>
@@ -4157,37 +4157,37 @@
         <v>2303</v>
       </c>
       <c r="M35">
-        <v>7066.275524333989</v>
+        <v>6608.676398832989</v>
       </c>
       <c r="N35">
-        <v>-4763.275524333989</v>
+        <v>-4305.676398832989</v>
       </c>
       <c r="O35">
-        <v>-1190.818881083497</v>
+        <v>-1076.419099708247</v>
       </c>
       <c r="P35">
-        <v>-3572.456643250492</v>
+        <v>-3229.257299124742</v>
       </c>
       <c r="Q35">
-        <v>-2972.456643250492</v>
+        <v>-2629.257299124742</v>
       </c>
       <c r="R35">
         <v>0.4925373134328359</v>
       </c>
       <c r="S35">
-        <v>0.1360107986055126</v>
+        <v>0.1358138445435856</v>
       </c>
       <c r="T35">
-        <v>1.395154786806749</v>
+        <v>1.392485547256234</v>
       </c>
       <c r="U35">
-        <v>0.2316309777667576</v>
+        <v>0.2166309777667576</v>
       </c>
       <c r="V35">
-        <v>0.0814785664693234</v>
+        <v>0.08712031960010486</v>
       </c>
       <c r="W35">
-        <v>0.2127580177484345</v>
+        <v>0.1977580177484344</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>0.3259142658772937</v>
+        <v>0.3484812784004194</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4206,13 +4206,13 @@
         <v>0.34</v>
       </c>
       <c r="B36">
-        <v>0.1631956907003444</v>
+        <v>0.1579637314788533</v>
       </c>
       <c r="C36">
-        <v>18316.63315738627</v>
+        <v>20523.00377691568</v>
       </c>
       <c r="D36">
-        <v>47585.6842018994</v>
+        <v>49792.05482142881</v>
       </c>
       <c r="E36">
         <v>25194.58326653335</v>
@@ -4239,37 +4239,37 @@
         <v>2303</v>
       </c>
       <c r="M36">
-        <v>7280.405085677444</v>
+        <v>6808.939320009747</v>
       </c>
       <c r="N36">
-        <v>-4977.405085677444</v>
+        <v>-4505.939320009747</v>
       </c>
       <c r="O36">
-        <v>-1244.351271419361</v>
+        <v>-1126.484830002437</v>
       </c>
       <c r="P36">
-        <v>-3733.053814258083</v>
+        <v>-3379.45449000731</v>
       </c>
       <c r="Q36">
-        <v>-3133.053814258083</v>
+        <v>-2779.45449000731</v>
       </c>
       <c r="R36">
         <v>0.5151515151515152</v>
       </c>
       <c r="S36">
-        <v>0.1373776288874143</v>
+        <v>0.1371776906730338</v>
       </c>
       <c r="T36">
-        <v>1.416293495697761</v>
+        <v>1.413583813123753</v>
       </c>
       <c r="U36">
-        <v>0.2316309777667576</v>
+        <v>0.2166309777667576</v>
       </c>
       <c r="V36">
-        <v>0.07908213804375507</v>
+        <v>0.08455795725892529</v>
       </c>
       <c r="W36">
-        <v>0.2133131048077969</v>
+        <v>0.1983131048077969</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>0.3163285521750202</v>
+        <v>0.3382318290357011</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4288,13 +4288,13 @@
         <v>0.35</v>
       </c>
       <c r="B37">
-        <v>0.165054000478012</v>
+        <v>0.1596720412565208</v>
       </c>
       <c r="C37">
-        <v>16650.67286279751</v>
+        <v>18851.58007409225</v>
       </c>
       <c r="D37">
-        <v>46844.16658509043</v>
+        <v>49045.07379638517</v>
       </c>
       <c r="E37">
         <v>26119.02594431315</v>
@@ -4321,37 +4321,37 @@
         <v>2303</v>
       </c>
       <c r="M37">
-        <v>7494.534647020898</v>
+        <v>7009.202241186503</v>
       </c>
       <c r="N37">
-        <v>-5191.534647020898</v>
+        <v>-4706.202241186503</v>
       </c>
       <c r="O37">
-        <v>-1297.883661755224</v>
+        <v>-1176.550560296626</v>
       </c>
       <c r="P37">
-        <v>-3893.650985265674</v>
+        <v>-3529.651680889877</v>
       </c>
       <c r="Q37">
-        <v>-3293.650985265674</v>
+        <v>-2929.651680889877</v>
       </c>
       <c r="R37">
         <v>0.5384615384615385</v>
       </c>
       <c r="S37">
-        <v>0.1387865154856822</v>
+        <v>0.1385835012987728</v>
       </c>
       <c r="T37">
-        <v>1.438082626400803</v>
+        <v>1.43533125640258</v>
       </c>
       <c r="U37">
-        <v>0.2316309777667576</v>
+        <v>0.2166309777667576</v>
       </c>
       <c r="V37">
-        <v>0.07682264838536206</v>
+        <v>0.08214201562295601</v>
       </c>
       <c r="W37">
-        <v>0.2138364726066244</v>
+        <v>0.1988364726066243</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>0.3072905935414483</v>
+        <v>0.328568062491824</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4370,13 +4370,13 @@
         <v>0.36</v>
       </c>
       <c r="B38">
-        <v>0.1669123102556795</v>
+        <v>0.1613803510341884</v>
       </c>
       <c r="C38">
-        <v>15007.46780150781</v>
+        <v>17202.23754644084</v>
       </c>
       <c r="D38">
-        <v>46125.40420158053</v>
+        <v>48320.17394651356</v>
       </c>
       <c r="E38">
         <v>27043.46862209294</v>
@@ -4403,37 +4403,37 @@
         <v>2303</v>
       </c>
       <c r="M38">
-        <v>7708.664208364351</v>
+        <v>7209.46516236326</v>
       </c>
       <c r="N38">
-        <v>-5405.664208364351</v>
+        <v>-4906.46516236326</v>
       </c>
       <c r="O38">
-        <v>-1351.416052091088</v>
+        <v>-1226.616290590815</v>
       </c>
       <c r="P38">
-        <v>-4054.248156273263</v>
+        <v>-3679.848871772445</v>
       </c>
       <c r="Q38">
-        <v>-3454.248156273263</v>
+        <v>-3079.848871772445</v>
       </c>
       <c r="R38">
         <v>0.5625</v>
       </c>
       <c r="S38">
-        <v>0.140239429790146</v>
+        <v>0.1400332435065661</v>
       </c>
       <c r="T38">
-        <v>1.460552667438316</v>
+        <v>1.45775830728387</v>
       </c>
       <c r="U38">
-        <v>0.2316309777667576</v>
+        <v>0.2166309777667576</v>
       </c>
       <c r="V38">
-        <v>0.07468868593021312</v>
+        <v>0.07986029296676279</v>
       </c>
       <c r="W38">
-        <v>0.214330764416628</v>
+        <v>0.199330764416628</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>0.2987547437208525</v>
+        <v>0.3194411718670511</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4452,13 +4452,13 @@
         <v>0.37</v>
       </c>
       <c r="B39">
-        <v>0.1687706200333471</v>
+        <v>0.163088660811856</v>
       </c>
       <c r="C39">
-        <v>13385.98635460232</v>
+        <v>15574.01135676777</v>
       </c>
       <c r="D39">
-        <v>45428.36543245484</v>
+        <v>47616.39043462029</v>
       </c>
       <c r="E39">
         <v>27967.91129987274</v>
@@ -4485,37 +4485,37 @@
         <v>2303</v>
       </c>
       <c r="M39">
-        <v>7922.793769707806</v>
+        <v>7409.728083540018</v>
       </c>
       <c r="N39">
-        <v>-5619.793769707806</v>
+        <v>-5106.728083540018</v>
       </c>
       <c r="O39">
-        <v>-1404.948442426951</v>
+        <v>-1276.682020885004</v>
       </c>
       <c r="P39">
-        <v>-4214.845327280855</v>
+        <v>-3830.046062655013</v>
       </c>
       <c r="Q39">
-        <v>-3614.845327280855</v>
+        <v>-3230.046062655013</v>
       </c>
       <c r="R39">
         <v>0.5873015873015873</v>
       </c>
       <c r="S39">
-        <v>0.1417384683582436</v>
+        <v>0.1415290092765116</v>
       </c>
       <c r="T39">
-        <v>1.48373604311194</v>
+        <v>1.480897328034408</v>
       </c>
       <c r="U39">
-        <v>0.2316309777667576</v>
+        <v>0.2166309777667576</v>
       </c>
       <c r="V39">
-        <v>0.07267007279696411</v>
+        <v>0.07770190667036379</v>
       </c>
       <c r="W39">
-        <v>0.2147983377504153</v>
+        <v>0.1997983377504153</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>0.2906802911878564</v>
+        <v>0.3108076266814551</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4534,13 +4534,13 @@
         <v>0.38</v>
       </c>
       <c r="B40">
-        <v>0.1706289298110147</v>
+        <v>0.1647969705895236</v>
       </c>
       <c r="C40">
-        <v>11785.25833339779</v>
+        <v>13965.99207234231</v>
       </c>
       <c r="D40">
-        <v>44752.0800890301</v>
+        <v>46932.81382797462</v>
       </c>
       <c r="E40">
         <v>28892.35397765254</v>
@@ -4567,37 +4567,37 @@
         <v>2303</v>
       </c>
       <c r="M40">
-        <v>8136.923331051259</v>
+        <v>7609.991004716774</v>
       </c>
       <c r="N40">
-        <v>-5833.923331051259</v>
+        <v>-5306.991004716774</v>
       </c>
       <c r="O40">
-        <v>-1458.480832762815</v>
+        <v>-1326.747751179194</v>
       </c>
       <c r="P40">
-        <v>-4375.442498288445</v>
+        <v>-3980.243253537581</v>
       </c>
       <c r="Q40">
-        <v>-3775.442498288445</v>
+        <v>-3380.243253537581</v>
       </c>
       <c r="R40">
         <v>0.6129032258064516</v>
       </c>
       <c r="S40">
-        <v>0.143285863009183</v>
+        <v>0.143073025555165</v>
       </c>
       <c r="T40">
-        <v>1.507667269613745</v>
+        <v>1.504782768809156</v>
       </c>
       <c r="U40">
-        <v>0.2316309777667576</v>
+        <v>0.2166309777667576</v>
       </c>
       <c r="V40">
-        <v>0.07075770246020191</v>
+        <v>0.07565711965272265</v>
       </c>
       <c r="W40">
-        <v>0.2152413019613717</v>
+        <v>0.2002413019613717</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.2830308098408076</v>
+        <v>0.3026284786108906</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4616,13 +4616,13 @@
         <v>0.39</v>
       </c>
       <c r="B41">
-        <v>0.1724872395886823</v>
+        <v>0.1665052803671911</v>
       </c>
       <c r="C41">
-        <v>10204.37047400053</v>
+        <v>12377.32174427345</v>
       </c>
       <c r="D41">
-        <v>44095.63490741264</v>
+        <v>46268.58617768557</v>
       </c>
       <c r="E41">
         <v>29816.79665543234</v>
@@ -4649,37 +4649,37 @@
         <v>2303</v>
       </c>
       <c r="M41">
-        <v>8351.052892394713</v>
+        <v>7810.253925893531</v>
       </c>
       <c r="N41">
-        <v>-6048.052892394713</v>
+        <v>-5507.253925893531</v>
       </c>
       <c r="O41">
-        <v>-1512.013223098678</v>
+        <v>-1376.813481473383</v>
       </c>
       <c r="P41">
-        <v>-4536.039669296035</v>
+        <v>-4130.440444420148</v>
       </c>
       <c r="Q41">
-        <v>-3936.039669296035</v>
+        <v>-3530.440444420148</v>
       </c>
       <c r="R41">
         <v>0.639344262295082</v>
       </c>
       <c r="S41">
-        <v>0.1448839919109729</v>
+        <v>0.1446676653183645</v>
       </c>
       <c r="T41">
-        <v>1.532383126492659</v>
+        <v>1.529451338789634</v>
       </c>
       <c r="U41">
-        <v>0.2316309777667576</v>
+        <v>0.2166309777667576</v>
       </c>
       <c r="V41">
-        <v>0.06894340239711981</v>
+        <v>0.07371719350778104</v>
       </c>
       <c r="W41">
-        <v>0.2156615500589457</v>
+        <v>0.2006615500589457</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.2757736095884793</v>
+        <v>0.2948687740311242</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4698,13 +4698,13 @@
         <v>0.4</v>
       </c>
       <c r="B42">
-        <v>0.1743455493663498</v>
+        <v>0.1682135901448587</v>
       </c>
       <c r="C42">
-        <v>8642.462322660314</v>
+        <v>10807.1903151658</v>
       </c>
       <c r="D42">
-        <v>43458.16943385223</v>
+        <v>45622.89742635772</v>
       </c>
       <c r="E42">
         <v>30741.23933321214</v>
@@ -4731,37 +4731,37 @@
         <v>2303</v>
       </c>
       <c r="M42">
-        <v>8565.182453738169</v>
+        <v>8010.516847070289</v>
       </c>
       <c r="N42">
-        <v>-6262.182453738169</v>
+        <v>-5707.516847070289</v>
       </c>
       <c r="O42">
-        <v>-1565.545613434542</v>
+        <v>-1426.879211767572</v>
       </c>
       <c r="P42">
-        <v>-4696.636840303627</v>
+        <v>-4280.637635302717</v>
       </c>
       <c r="Q42">
-        <v>-4096.636840303627</v>
+        <v>-3680.637635302717</v>
       </c>
       <c r="R42">
         <v>0.6666666666666667</v>
       </c>
       <c r="S42">
-        <v>0.1465353917761557</v>
+        <v>0.1463154597403372</v>
       </c>
       <c r="T42">
-        <v>1.557922845267537</v>
+        <v>1.554942194436128</v>
       </c>
       <c r="U42">
-        <v>0.2316309777667576</v>
+        <v>0.2166309777667576</v>
       </c>
       <c r="V42">
-        <v>0.0672198173371918</v>
+        <v>0.07187426367008651</v>
       </c>
       <c r="W42">
-        <v>0.216060785751641</v>
+        <v>0.201060785751641</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.2688792693487672</v>
+        <v>0.287497054680346</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4780,13 +4780,13 @@
         <v>0.41</v>
       </c>
       <c r="B43">
-        <v>0.1762038591440174</v>
+        <v>0.1699218999225263</v>
       </c>
       <c r="C43">
-        <v>7098.722472936599</v>
+        <v>9254.832323427552</v>
       </c>
       <c r="D43">
-        <v>42838.87226190831</v>
+        <v>44994.98211239927</v>
       </c>
       <c r="E43">
         <v>31665.68201099194</v>
@@ -4813,37 +4813,37 @@
         <v>2303</v>
       </c>
       <c r="M43">
-        <v>8779.312015081623</v>
+        <v>8210.779768247046</v>
       </c>
       <c r="N43">
-        <v>-6476.312015081623</v>
+        <v>-5907.779768247046</v>
       </c>
       <c r="O43">
-        <v>-1619.078003770406</v>
+        <v>-1476.944942061762</v>
       </c>
       <c r="P43">
-        <v>-4857.234011311217</v>
+        <v>-4430.834826185284</v>
       </c>
       <c r="Q43">
-        <v>-4257.234011311217</v>
+        <v>-3830.834826185284</v>
       </c>
       <c r="R43">
         <v>0.6949152542372882</v>
       </c>
       <c r="S43">
-        <v>0.1482427712977855</v>
+        <v>0.1480191116003429</v>
       </c>
       <c r="T43">
-        <v>1.584328317221224</v>
+        <v>1.581297146884198</v>
       </c>
       <c r="U43">
-        <v>0.2316309777667576</v>
+        <v>0.2166309777667576</v>
       </c>
       <c r="V43">
-        <v>0.0655803095972603</v>
+        <v>0.07012123284886489</v>
       </c>
       <c r="W43">
-        <v>0.2164405465324975</v>
+        <v>0.2014405465324975</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.2623212383890412</v>
+        <v>0.2804849313954595</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4862,13 +4862,13 @@
         <v>0.42</v>
       </c>
       <c r="B44">
-        <v>0.178062168921685</v>
+        <v>0.1716302097001939</v>
       </c>
       <c r="C44">
-        <v>5572.385120076338</v>
+        <v>7719.523876038613</v>
       </c>
       <c r="D44">
-        <v>42236.97758682784</v>
+        <v>44384.11634279012</v>
       </c>
       <c r="E44">
         <v>32590.12468877173</v>
@@ -4895,37 +4895,37 @@
         <v>2303</v>
       </c>
       <c r="M44">
-        <v>8993.441576425075</v>
+        <v>8411.042689423803</v>
       </c>
       <c r="N44">
-        <v>-6690.441576425075</v>
+        <v>-6108.042689423803</v>
       </c>
       <c r="O44">
-        <v>-1672.610394106269</v>
+        <v>-1527.010672355951</v>
       </c>
       <c r="P44">
-        <v>-5017.831182318807</v>
+        <v>-4581.032017067851</v>
       </c>
       <c r="Q44">
-        <v>-4417.831182318807</v>
+        <v>-3981.032017067851</v>
       </c>
       <c r="R44">
         <v>0.7241379310344827</v>
       </c>
       <c r="S44">
-        <v>0.1500090259753335</v>
+        <v>0.1497815100762109</v>
       </c>
       <c r="T44">
-        <v>1.611644322690555</v>
+        <v>1.608560890795995</v>
       </c>
       <c r="U44">
-        <v>0.2316309777667576</v>
+        <v>0.2166309777667576</v>
       </c>
       <c r="V44">
-        <v>0.0640188736544684</v>
+        <v>0.06845167968579668</v>
       </c>
       <c r="W44">
-        <v>0.2168022234666465</v>
+        <v>0.2018022234666465</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.2560754946178736</v>
+        <v>0.2738067187431867</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4944,13 +4944,13 @@
         <v>0.43</v>
       </c>
       <c r="B45">
-        <v>0.1799204786993526</v>
+        <v>0.1733385194778614</v>
       </c>
       <c r="C45">
-        <v>4062.726901837035</v>
+        <v>6200.579864607331</v>
       </c>
       <c r="D45">
-        <v>41651.76204636834</v>
+        <v>43789.61500913864</v>
       </c>
       <c r="E45">
         <v>33514.56736655153</v>
@@ -4977,37 +4977,37 @@
         <v>2303</v>
       </c>
       <c r="M45">
-        <v>9207.571137768531</v>
+        <v>8611.305610600561</v>
       </c>
       <c r="N45">
-        <v>-6904.571137768531</v>
+        <v>-6308.305610600561</v>
       </c>
       <c r="O45">
-        <v>-1726.142784442133</v>
+        <v>-1577.07640265014</v>
       </c>
       <c r="P45">
-        <v>-5178.428353326399</v>
+        <v>-4731.22920795042</v>
       </c>
       <c r="Q45">
-        <v>-4578.428353326399</v>
+        <v>-4131.22920795042</v>
       </c>
       <c r="R45">
         <v>0.7543859649122806</v>
       </c>
       <c r="S45">
-        <v>0.1518372545012166</v>
+        <v>0.1516057470950918</v>
       </c>
       <c r="T45">
-        <v>1.639918784492144</v>
+        <v>1.636781257301187</v>
       </c>
       <c r="U45">
-        <v>0.2316309777667576</v>
+        <v>0.2166309777667576</v>
       </c>
       <c r="V45">
-        <v>0.06253006263924819</v>
+        <v>0.06685978015822001</v>
       </c>
       <c r="W45">
-        <v>0.2171470782178119</v>
+        <v>0.2021470782178119</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.2501202505569927</v>
+        <v>0.26743912063288</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5026,13 +5026,13 @@
         <v>0.44</v>
       </c>
       <c r="B46">
-        <v>0.1817787884770202</v>
+        <v>0.175046829255529</v>
       </c>
       <c r="C46">
-        <v>2569.063998353202</v>
+        <v>4697.351402206747</v>
       </c>
       <c r="D46">
-        <v>41082.54182066431</v>
+        <v>43210.82922451785</v>
       </c>
       <c r="E46">
         <v>34439.01004433133</v>
@@ -5059,37 +5059,37 @@
         <v>2303</v>
       </c>
       <c r="M46">
-        <v>9421.700699111985</v>
+        <v>8811.568531777319</v>
       </c>
       <c r="N46">
-        <v>-7118.700699111985</v>
+        <v>-6508.568531777319</v>
       </c>
       <c r="O46">
-        <v>-1779.675174777996</v>
+        <v>-1627.14213294433</v>
       </c>
       <c r="P46">
-        <v>-5339.025524333989</v>
+        <v>-4881.426398832989</v>
       </c>
       <c r="Q46">
-        <v>-4739.025524333989</v>
+        <v>-4281.426398832989</v>
       </c>
       <c r="R46">
         <v>0.7857142857142857</v>
       </c>
       <c r="S46">
-        <v>0.153730776903024</v>
+        <v>0.1534951354360756</v>
       </c>
       <c r="T46">
-        <v>1.669203048500932</v>
+        <v>1.666009494038709</v>
       </c>
       <c r="U46">
-        <v>0.2316309777667576</v>
+        <v>0.2166309777667576</v>
       </c>
       <c r="V46">
-        <v>0.06110892485199255</v>
+        <v>0.06534023970007864</v>
       </c>
       <c r="W46">
-        <v>0.2174762577530152</v>
+        <v>0.2024762577530152</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.2444356994079702</v>
+        <v>0.2613609588003145</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5108,13 +5108,13 @@
         <v>0.45</v>
       </c>
       <c r="B47">
-        <v>0.1836370982546877</v>
+        <v>0.1767551390331966</v>
       </c>
       <c r="C47">
-        <v>1090.749466598987</v>
+        <v>3209.223460829489</v>
       </c>
       <c r="D47">
-        <v>40528.66996668989</v>
+        <v>42647.1439609204</v>
       </c>
       <c r="E47">
         <v>35363.45272211113</v>
@@ -5141,37 +5141,37 @@
         <v>2303</v>
       </c>
       <c r="M47">
-        <v>9635.830260455439</v>
+        <v>9011.831452954077</v>
       </c>
       <c r="N47">
-        <v>-7332.830260455439</v>
+        <v>-6708.831452954077</v>
       </c>
       <c r="O47">
-        <v>-1833.20756511386</v>
+        <v>-1677.207863238519</v>
       </c>
       <c r="P47">
-        <v>-5499.622695341579</v>
+        <v>-5031.623589715558</v>
       </c>
       <c r="Q47">
-        <v>-4899.622695341579</v>
+        <v>-4431.623589715558</v>
       </c>
       <c r="R47">
         <v>0.8181818181818181</v>
       </c>
       <c r="S47">
-        <v>0.1556931546648972</v>
+        <v>0.1554532288076406</v>
       </c>
       <c r="T47">
-        <v>1.699552194837312</v>
+        <v>1.696300575748503</v>
       </c>
       <c r="U47">
-        <v>0.2316309777667576</v>
+        <v>0.2166309777667576</v>
       </c>
       <c r="V47">
-        <v>0.05975094874417049</v>
+        <v>0.06388823437341022</v>
       </c>
       <c r="W47">
-        <v>0.217790807086654</v>
+        <v>0.202790807086654</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.239003794976682</v>
+        <v>0.2555529374936408</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5190,13 +5190,13 @@
         <v>0.46</v>
       </c>
       <c r="B48">
-        <v>0.1854954080323553</v>
+        <v>0.1784634488108642</v>
       </c>
       <c r="C48">
-        <v>-372.8292123979554</v>
+        <v>1735.61269137809</v>
       </c>
       <c r="D48">
-        <v>39989.53396547274</v>
+        <v>42097.97586924879</v>
       </c>
       <c r="E48">
         <v>36287.89539989092</v>
@@ -5223,37 +5223,37 @@
         <v>2303</v>
       </c>
       <c r="M48">
-        <v>9849.959821798893</v>
+        <v>9212.094374130831</v>
       </c>
       <c r="N48">
-        <v>-7546.959821798893</v>
+        <v>-6909.094374130831</v>
       </c>
       <c r="O48">
-        <v>-1886.739955449723</v>
+        <v>-1727.273593532708</v>
       </c>
       <c r="P48">
-        <v>-5660.21986634917</v>
+        <v>-5181.820780598124</v>
       </c>
       <c r="Q48">
-        <v>-5060.21986634917</v>
+        <v>-4581.820780598124</v>
       </c>
       <c r="R48">
         <v>0.8518518518518519</v>
       </c>
       <c r="S48">
-        <v>0.1577282130846175</v>
+        <v>0.1574838441559302</v>
       </c>
       <c r="T48">
-        <v>1.731025383630596</v>
+        <v>1.727713549373475</v>
       </c>
       <c r="U48">
-        <v>0.2316309777667576</v>
+        <v>0.2166309777667576</v>
       </c>
       <c r="V48">
-        <v>0.05845201507581897</v>
+        <v>0.06249935971311871</v>
       </c>
       <c r="W48">
-        <v>0.2180916803623084</v>
+        <v>0.2030916803623084</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.2338080603032758</v>
+        <v>0.2499974388524748</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5272,13 +5272,13 @@
         <v>0.47</v>
       </c>
       <c r="B49">
-        <v>0.1873537178100229</v>
+        <v>0.1801717585885318</v>
       </c>
       <c r="C49">
-        <v>-1822.252393142306</v>
+        <v>275.9654099458858</v>
       </c>
       <c r="D49">
-        <v>39464.55346250819</v>
+        <v>41562.77126559638</v>
       </c>
       <c r="E49">
         <v>37212.33807767072</v>
@@ -5305,37 +5305,37 @@
         <v>2303</v>
       </c>
       <c r="M49">
-        <v>10064.08938314235</v>
+        <v>9412.357295307589</v>
       </c>
       <c r="N49">
-        <v>-7761.089383142347</v>
+        <v>-7109.357295307589</v>
       </c>
       <c r="O49">
-        <v>-1940.272345785587</v>
+        <v>-1777.339323826897</v>
       </c>
       <c r="P49">
-        <v>-5820.817037356761</v>
+        <v>-5332.017971480692</v>
       </c>
       <c r="Q49">
-        <v>-5220.817037356761</v>
+        <v>-4732.017971480692</v>
       </c>
       <c r="R49">
         <v>0.8867924528301887</v>
       </c>
       <c r="S49">
-        <v>0.1598400661616858</v>
+        <v>0.159591086498495</v>
       </c>
       <c r="T49">
-        <v>1.763686239925513</v>
+        <v>1.760311918229579</v>
       </c>
       <c r="U49">
-        <v>0.2316309777667576</v>
+        <v>0.2166309777667576</v>
       </c>
       <c r="V49">
-        <v>0.05720835518058878</v>
+        <v>0.06116958610220129</v>
       </c>
       <c r="W49">
-        <v>0.2183797505198499</v>
+        <v>0.2033797505198499</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.2288334207223551</v>
+        <v>0.2446783444088052</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5354,13 +5354,13 @@
         <v>0.48</v>
       </c>
       <c r="B50">
-        <v>0.1892120275876905</v>
+        <v>0.1818800683661993</v>
       </c>
       <c r="C50">
-        <v>-3258.07034958079</v>
+        <v>-1170.244264223918</v>
       </c>
       <c r="D50">
-        <v>38953.1781838495</v>
+        <v>41041.00426920637</v>
       </c>
       <c r="E50">
         <v>38136.78075545051</v>
@@ -5387,37 +5387,37 @@
         <v>2303</v>
       </c>
       <c r="M50">
-        <v>10278.2189444858</v>
+        <v>9612.620216484345</v>
       </c>
       <c r="N50">
-        <v>-7975.218944485801</v>
+        <v>-7309.620216484345</v>
       </c>
       <c r="O50">
-        <v>-1993.80473612145</v>
+        <v>-1827.405054121086</v>
       </c>
       <c r="P50">
-        <v>-5981.414208364351</v>
+        <v>-5482.215162363259</v>
       </c>
       <c r="Q50">
-        <v>-5381.414208364351</v>
+        <v>-4882.215162363259</v>
       </c>
       <c r="R50">
         <v>0.923076923076923</v>
       </c>
       <c r="S50">
-        <v>0.1620331443571028</v>
+        <v>0.161779376623466</v>
       </c>
       <c r="T50">
-        <v>1.797603283001004</v>
+        <v>1.794164070503225</v>
       </c>
       <c r="U50">
-        <v>0.2316309777667576</v>
+        <v>0.2166309777667576</v>
       </c>
       <c r="V50">
-        <v>0.05601651444765984</v>
+        <v>0.0598952197250721</v>
       </c>
       <c r="W50">
-        <v>0.2186558177541604</v>
+        <v>0.2036558177541604</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.2240660577906394</v>
+        <v>0.2395808789002885</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5436,13 +5436,13 @@
         <v>0.49</v>
       </c>
       <c r="B51">
-        <v>0.1910703373653581</v>
+        <v>0.1835883781438669</v>
       </c>
       <c r="C51">
-        <v>-4680.805199066788</v>
+        <v>-2603.516132265155</v>
       </c>
       <c r="D51">
-        <v>38454.8860121433</v>
+        <v>40532.17507894494</v>
       </c>
       <c r="E51">
         <v>39061.22343323031</v>
@@ -5469,37 +5469,37 @@
         <v>2303</v>
       </c>
       <c r="M51">
-        <v>10492.34850582926</v>
+        <v>9812.883137661103</v>
       </c>
       <c r="N51">
-        <v>-8189.348505829255</v>
+        <v>-7509.883137661103</v>
       </c>
       <c r="O51">
-        <v>-2047.337126457314</v>
+        <v>-1877.470784415276</v>
       </c>
       <c r="P51">
-        <v>-6142.011379371941</v>
+        <v>-5632.412353245827</v>
       </c>
       <c r="Q51">
-        <v>-5542.011379371941</v>
+        <v>-5032.412353245827</v>
       </c>
       <c r="R51">
         <v>0.9607843137254901</v>
       </c>
       <c r="S51">
-        <v>0.1643122256190068</v>
+        <v>0.1640534820474555</v>
       </c>
       <c r="T51">
-        <v>1.832850406197102</v>
+        <v>1.82934375816015</v>
       </c>
       <c r="U51">
-        <v>0.2316309777667576</v>
+        <v>0.2166309777667576</v>
       </c>
       <c r="V51">
-        <v>0.05487332027525862</v>
+        <v>0.05867286830211144</v>
       </c>
       <c r="W51">
-        <v>0.218920616938091</v>
+        <v>0.203920616938091</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.2194932811010345</v>
+        <v>0.2346914732084457</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5518,13 +5518,13 @@
         <v>0.5</v>
       </c>
       <c r="B52">
-        <v>0.1929286471430256</v>
+        <v>0.1852966879215345</v>
       </c>
       <c r="C52">
-        <v>-6090.952680520801</v>
+        <v>-4024.325512575153</v>
       </c>
       <c r="D52">
-        <v>37969.18120846909</v>
+        <v>40035.80837641474</v>
       </c>
       <c r="E52">
         <v>39985.66611101011</v>
@@ -5551,37 +5551,37 @@
         <v>2303</v>
       </c>
       <c r="M52">
-        <v>10706.47806717271</v>
+        <v>10013.14605883786</v>
       </c>
       <c r="N52">
-        <v>-8403.478067172709</v>
+        <v>-7710.146058837861</v>
       </c>
       <c r="O52">
-        <v>-2100.869516793177</v>
+        <v>-1927.536514709465</v>
       </c>
       <c r="P52">
-        <v>-6302.608550379532</v>
+        <v>-5782.609544128396</v>
       </c>
       <c r="Q52">
-        <v>-5702.608550379532</v>
+        <v>-5182.609544128396</v>
       </c>
       <c r="R52">
         <v>1</v>
       </c>
       <c r="S52">
-        <v>0.1666824701313869</v>
+        <v>0.1664185516884046</v>
       </c>
       <c r="T52">
-        <v>1.869507414321044</v>
+        <v>1.865930633323354</v>
       </c>
       <c r="U52">
-        <v>0.2316309777667576</v>
+        <v>0.2166309777667576</v>
       </c>
       <c r="V52">
-        <v>0.05377585386975345</v>
+        <v>0.05749941093606921</v>
       </c>
       <c r="W52">
-        <v>0.2191748241546643</v>
+        <v>0.2041748241546643</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.2151034154790138</v>
+        <v>0.2299976437442768</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5600,13 +5600,13 @@
         <v>0.51</v>
       </c>
       <c r="B53">
-        <v>0.1947869569206932</v>
+        <v>0.187004997699202</v>
       </c>
       <c r="C53">
-        <v>-7488.983799517577</v>
+        <v>-5433.124721785571</v>
       </c>
       <c r="D53">
-        <v>37495.59276725211</v>
+        <v>39551.45184498412</v>
       </c>
       <c r="E53">
         <v>40910.10878878991</v>
@@ -5633,37 +5633,37 @@
         <v>2303</v>
       </c>
       <c r="M53">
-        <v>10920.60762851617</v>
+        <v>10213.40898001462</v>
       </c>
       <c r="N53">
-        <v>-8617.607628516165</v>
+        <v>-7910.408980014619</v>
       </c>
       <c r="O53">
-        <v>-2154.401907129041</v>
+        <v>-1977.602245003655</v>
       </c>
       <c r="P53">
-        <v>-6463.205721387124</v>
+        <v>-5932.806735010965</v>
       </c>
       <c r="Q53">
-        <v>-5863.205721387124</v>
+        <v>-5332.806735010965</v>
       </c>
       <c r="R53">
         <v>1.040816326530612</v>
       </c>
       <c r="S53">
-        <v>0.1691494593177418</v>
+        <v>0.1688801547840864</v>
       </c>
       <c r="T53">
-        <v>1.907660626858208</v>
+        <v>1.904010850329953</v>
       </c>
       <c r="U53">
-        <v>0.2316309777667576</v>
+        <v>0.2166309777667576</v>
       </c>
       <c r="V53">
-        <v>0.05272142536250338</v>
+        <v>0.0563719715059502</v>
       </c>
       <c r="W53">
-        <v>0.2194190624607838</v>
+        <v>0.2044190624607838</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.2108857014500135</v>
+        <v>0.2254878860238008</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5682,13 +5682,13 @@
         <v>0.52</v>
       </c>
       <c r="B54">
-        <v>0.1966452666983608</v>
+        <v>0.1887133074768696</v>
       </c>
       <c r="C54">
-        <v>-8875.346351774839</v>
+        <v>-6830.344449516931</v>
       </c>
       <c r="D54">
-        <v>37033.67289277465</v>
+        <v>39078.67479503256</v>
       </c>
       <c r="E54">
         <v>41834.55146656971</v>
@@ -5715,37 +5715,37 @@
         <v>2303</v>
       </c>
       <c r="M54">
-        <v>11134.73718985962</v>
+        <v>10413.67190119138</v>
       </c>
       <c r="N54">
-        <v>-8831.737189859619</v>
+        <v>-8110.671901191376</v>
       </c>
       <c r="O54">
-        <v>-2207.934297464905</v>
+        <v>-2027.667975297844</v>
       </c>
       <c r="P54">
-        <v>-6623.802892394715</v>
+        <v>-6083.003925893532</v>
       </c>
       <c r="Q54">
-        <v>-6023.802892394715</v>
+        <v>-5483.003925893532</v>
       </c>
       <c r="R54">
         <v>1.083333333333333</v>
       </c>
       <c r="S54">
-        <v>0.1717192397201947</v>
+        <v>0.1714443246754215</v>
       </c>
       <c r="T54">
-        <v>1.947403556584421</v>
+        <v>1.94367774304516</v>
       </c>
       <c r="U54">
-        <v>0.2316309777667576</v>
+        <v>0.2166309777667576</v>
       </c>
       <c r="V54">
-        <v>0.05170755179783985</v>
+        <v>0.05528789513083578</v>
       </c>
       <c r="W54">
-        <v>0.2196539069858987</v>
+        <v>0.2046539069858987</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.2068302071913594</v>
+        <v>0.2211515805233432</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5764,13 +5764,13 @@
         <v>0.53</v>
       </c>
       <c r="B55">
-        <v>0.1985035764760284</v>
+        <v>0.1904216172545372</v>
       </c>
       <c r="C55">
-        <v>-10250.46633540273</v>
+        <v>-8216.395035699177</v>
       </c>
       <c r="D55">
-        <v>36582.99558692655</v>
+        <v>38617.06688663011</v>
       </c>
       <c r="E55">
         <v>42758.9941443495</v>
@@ -5797,37 +5797,37 @@
         <v>2303</v>
       </c>
       <c r="M55">
-        <v>11348.86675120307</v>
+        <v>10613.93482236813</v>
       </c>
       <c r="N55">
-        <v>-9045.866751203072</v>
+        <v>-8310.934822368132</v>
       </c>
       <c r="O55">
-        <v>-2261.466687800768</v>
+        <v>-2077.733705592033</v>
       </c>
       <c r="P55">
-        <v>-6784.400063402303</v>
+        <v>-6233.201116776099</v>
       </c>
       <c r="Q55">
-        <v>-6184.400063402303</v>
+        <v>-5633.201116776099</v>
       </c>
       <c r="R55">
         <v>1.127659574468085</v>
       </c>
       <c r="S55">
-        <v>0.1743983724801989</v>
+        <v>0.1741176081791539</v>
       </c>
       <c r="T55">
-        <v>1.988837674809622</v>
+        <v>1.985032588641866</v>
       </c>
       <c r="U55">
-        <v>0.2316309777667576</v>
+        <v>0.2166309777667576</v>
       </c>
       <c r="V55">
-        <v>0.05073193761297495</v>
+        <v>0.0542447272981785</v>
       </c>
       <c r="W55">
-        <v>0.2198798894534621</v>
+        <v>0.204879889453462</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.2029277504518998</v>
+        <v>0.216978909192714</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5846,13 +5846,13 @@
         <v>0.54</v>
       </c>
       <c r="B56">
-        <v>0.2167533823297391</v>
+        <v>0.1921299270322048</v>
       </c>
       <c r="C56">
-        <v>-15080.25769894776</v>
+        <v>-9591.667658420811</v>
       </c>
       <c r="D56">
-        <v>32677.64690116132</v>
+        <v>38166.23694168827</v>
       </c>
       <c r="E56">
         <v>43683.4368221293</v>
@@ -5879,45 +5879,45 @@
         <v>2303</v>
       </c>
       <c r="M56">
-        <v>13060.5934505498</v>
+        <v>10814.19774354489</v>
       </c>
       <c r="N56">
-        <v>-10757.5934505498</v>
+        <v>-8511.19774354489</v>
       </c>
       <c r="O56">
-        <v>-2689.39836263745</v>
+        <v>-2127.799435886222</v>
       </c>
       <c r="P56">
-        <v>-8068.195087912349</v>
+        <v>-6383.398307658667</v>
       </c>
       <c r="Q56">
-        <v>-7468.195087912349</v>
+        <v>-5783.398307658667</v>
       </c>
       <c r="R56">
         <v>1.173913043478261</v>
       </c>
       <c r="S56">
-        <v>0.1776102850907319</v>
+        <v>0.1769071214004398</v>
       </c>
       <c r="T56">
-        <v>2.038511497929023</v>
+        <v>2.028185471003645</v>
       </c>
       <c r="U56">
-        <v>0.2616309777667576</v>
+        <v>0.2166309777667576</v>
       </c>
       <c r="V56">
-        <v>0.04408298919799569</v>
+        <v>0.05324019531117519</v>
       </c>
       <c r="W56">
-        <v>0.2500975022000045</v>
+        <v>0.2050975022000046</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>D2/D</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y56">
-        <v>0.1763319567919828</v>
+        <v>0.2129607812447007</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5928,13 +5928,13 @@
         <v>0.55</v>
       </c>
       <c r="B57">
-        <v>0.2189116921074067</v>
+        <v>0.1938382368098724</v>
       </c>
       <c r="C57">
-        <v>-16412.1164441194</v>
+        <v>-10956.53543953389</v>
       </c>
       <c r="D57">
-        <v>32270.23083376948</v>
+        <v>37725.81183835499</v>
       </c>
       <c r="E57">
         <v>44607.8794999091</v>
@@ -5961,45 +5961,45 @@
         <v>2303</v>
       </c>
       <c r="M57">
-        <v>13302.45629222665</v>
+        <v>11014.46066472165</v>
       </c>
       <c r="N57">
-        <v>-10999.45629222665</v>
+        <v>-8711.460664721648</v>
       </c>
       <c r="O57">
-        <v>-2749.864073056662</v>
+        <v>-2177.865166180412</v>
       </c>
       <c r="P57">
-        <v>-8249.592219169986</v>
+        <v>-6533.595498541235</v>
       </c>
       <c r="Q57">
-        <v>-7649.592219169986</v>
+        <v>-5933.595498541235</v>
       </c>
       <c r="R57">
         <v>1.222222222222223</v>
       </c>
       <c r="S57">
-        <v>0.1805394025371926</v>
+        <v>0.1798206129871163</v>
       </c>
       <c r="T57">
-        <v>2.083811753438557</v>
+        <v>2.073256259248171</v>
       </c>
       <c r="U57">
-        <v>0.2616309777667576</v>
+        <v>0.2166309777667576</v>
       </c>
       <c r="V57">
-        <v>0.04328148030348667</v>
+        <v>0.05227219176006291</v>
       </c>
       <c r="W57">
-        <v>0.2503072017557637</v>
+        <v>0.2053072017557637</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>D2/D</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y57">
-        <v>0.1731259212139467</v>
+        <v>0.2090887670402517</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6010,13 +6010,13 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="B58">
-        <v>0.2210700018850743</v>
+        <v>0.1955465465875399</v>
       </c>
       <c r="C58">
-        <v>-17733.94118378667</v>
+        <v>-12311.35447458236</v>
       </c>
       <c r="D58">
-        <v>31872.84877188201</v>
+        <v>37295.43548108632</v>
       </c>
       <c r="E58">
         <v>45532.3221776889</v>
@@ -6043,45 +6043,45 @@
         <v>2303</v>
       </c>
       <c r="M58">
-        <v>13544.3191339035</v>
+        <v>11214.72358589841</v>
       </c>
       <c r="N58">
-        <v>-11241.3191339035</v>
+        <v>-8911.723585898406</v>
       </c>
       <c r="O58">
-        <v>-2810.329783475874</v>
+        <v>-2227.930896474601</v>
       </c>
       <c r="P58">
-        <v>-8430.989350427622</v>
+        <v>-6683.792689423804</v>
       </c>
       <c r="Q58">
-        <v>-7830.989350427622</v>
+        <v>-6083.792689423804</v>
       </c>
       <c r="R58">
         <v>1.272727272727273</v>
       </c>
       <c r="S58">
-        <v>0.1836016616857652</v>
+        <v>0.1828665360095507</v>
       </c>
       <c r="T58">
-        <v>2.131171111471251</v>
+        <v>2.120375719685629</v>
       </c>
       <c r="U58">
-        <v>0.2616309777667576</v>
+        <v>0.2166309777667576</v>
       </c>
       <c r="V58">
-        <v>0.0425085967266387</v>
+        <v>0.0513387597643475</v>
       </c>
       <c r="W58">
-        <v>0.2505094120416743</v>
+        <v>0.2055094120416743</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>D2/D</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y58">
-        <v>0.1700343869065548</v>
+        <v>0.2053550390573901</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6092,13 +6092,13 @@
         <v>0.5700000000000001</v>
       </c>
       <c r="B59">
-        <v>0.2232283116627419</v>
+        <v>0.1972548563652075</v>
       </c>
       <c r="C59">
-        <v>-19046.09809105896</v>
+        <v>-13656.46479302916</v>
       </c>
       <c r="D59">
-        <v>31485.13454238952</v>
+        <v>36874.76784041932</v>
       </c>
       <c r="E59">
         <v>46456.7648554687</v>
@@ -6125,45 +6125,45 @@
         <v>2303</v>
       </c>
       <c r="M59">
-        <v>13786.18197558034</v>
+        <v>11414.98650707516</v>
       </c>
       <c r="N59">
-        <v>-11483.18197558034</v>
+        <v>-9111.986507075162</v>
       </c>
       <c r="O59">
-        <v>-2870.795493895086</v>
+        <v>-2277.996626768791</v>
       </c>
       <c r="P59">
-        <v>-8612.386481685258</v>
+        <v>-6833.989880306372</v>
       </c>
       <c r="Q59">
-        <v>-8012.386481685258</v>
+        <v>-6233.989880306372</v>
       </c>
       <c r="R59">
         <v>1.325581395348838</v>
       </c>
       <c r="S59">
-        <v>0.1868063514924109</v>
+        <v>0.186054129870238</v>
       </c>
       <c r="T59">
-        <v>2.180733230342675</v>
+        <v>2.169686782934132</v>
       </c>
       <c r="U59">
-        <v>0.2616309777667576</v>
+        <v>0.2166309777667576</v>
       </c>
       <c r="V59">
-        <v>0.04176283187178539</v>
+        <v>0.05043807976848176</v>
       </c>
       <c r="W59">
-        <v>0.2507045272298337</v>
+        <v>0.2057045272298337</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>D2/D</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y59">
-        <v>0.1670513274871416</v>
+        <v>0.201752319073927</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6174,13 +6174,13 @@
         <v>0.58</v>
       </c>
       <c r="B60">
-        <v>0.2253866214404094</v>
+        <v>0.219511473901245</v>
       </c>
       <c r="C60">
-        <v>-20348.93573606389</v>
+        <v>-19305.45206261271</v>
       </c>
       <c r="D60">
-        <v>31106.73957516437</v>
+        <v>32150.22324861556</v>
       </c>
       <c r="E60">
         <v>47381.20753324849</v>
@@ -6207,37 +6207,37 @@
         <v>2303</v>
       </c>
       <c r="M60">
-        <v>14028.04481725719</v>
+        <v>13491.86806414491</v>
       </c>
       <c r="N60">
-        <v>-11725.04481725719</v>
+        <v>-11188.86806414491</v>
       </c>
       <c r="O60">
-        <v>-2931.261204314298</v>
+        <v>-2797.217016036227</v>
       </c>
       <c r="P60">
-        <v>-8793.783612942892</v>
+        <v>-8391.651048108681</v>
       </c>
       <c r="Q60">
-        <v>-8193.783612942892</v>
+        <v>-7791.651048108681</v>
       </c>
       <c r="R60">
         <v>1.380952380952381</v>
       </c>
       <c r="S60">
-        <v>0.1901636455755635</v>
+        <v>0.1899847228632673</v>
       </c>
       <c r="T60">
-        <v>2.232655450112738</v>
+        <v>2.230491806457928</v>
       </c>
       <c r="U60">
-        <v>0.2616309777667576</v>
+        <v>0.2516309777667576</v>
       </c>
       <c r="V60">
-        <v>0.04104278304640978</v>
+        <v>0.0426738534102683</v>
       </c>
       <c r="W60">
-        <v>0.2508929143080565</v>
+        <v>0.2408929143080565</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.1641711321856392</v>
+        <v>0.1706954136410732</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6256,13 +6256,13 @@
         <v>0.59</v>
       </c>
       <c r="B61">
-        <v>0.227544931218077</v>
+        <v>0.2215697836789126</v>
       </c>
       <c r="C61">
-        <v>-21642.78613116747</v>
+        <v>-20606.38219734761</v>
       </c>
       <c r="D61">
-        <v>30737.3318578406</v>
+        <v>31773.73579166046</v>
       </c>
       <c r="E61">
         <v>48305.65021102829</v>
@@ -6289,37 +6289,37 @@
         <v>2303</v>
       </c>
       <c r="M61">
-        <v>14269.90765893404</v>
+        <v>13724.48647904396</v>
       </c>
       <c r="N61">
-        <v>-11966.90765893404</v>
+        <v>-11421.48647904396</v>
       </c>
       <c r="O61">
-        <v>-2991.72691473351</v>
+        <v>-2855.371619760989</v>
       </c>
       <c r="P61">
-        <v>-8975.180744200528</v>
+        <v>-8566.114859282967</v>
       </c>
       <c r="Q61">
-        <v>-8375.180744200528</v>
+        <v>-7966.114859282967</v>
       </c>
       <c r="R61">
         <v>1.439024390243902</v>
       </c>
       <c r="S61">
-        <v>0.1936847101017967</v>
+        <v>0.193501423420908</v>
       </c>
       <c r="T61">
-        <v>2.287110461091098</v>
+        <v>2.284894045639829</v>
       </c>
       <c r="U61">
-        <v>0.2616309777667576</v>
+        <v>0.2516309777667576</v>
       </c>
       <c r="V61">
-        <v>0.04034714265579267</v>
+        <v>0.0419505677592468</v>
       </c>
       <c r="W61">
-        <v>0.2510749153836277</v>
+        <v>0.2410749153836277</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.1613885706231707</v>
+        <v>0.1678022710369872</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6338,13 +6338,13 @@
         <v>0.6</v>
       </c>
       <c r="B62">
-        <v>0.2297032409957446</v>
+        <v>0.2236280934565802</v>
       </c>
       <c r="C62">
-        <v>-22927.96570259302</v>
+        <v>-21898.59686087931</v>
       </c>
       <c r="D62">
-        <v>30376.59496419484</v>
+        <v>31405.96380590856</v>
       </c>
       <c r="E62">
         <v>49230.09288880809</v>
@@ -6371,37 +6371,37 @@
         <v>2303</v>
       </c>
       <c r="M62">
-        <v>14511.77050061089</v>
+        <v>13957.10489394301</v>
       </c>
       <c r="N62">
-        <v>-12208.77050061089</v>
+        <v>-11654.10489394301</v>
       </c>
       <c r="O62">
-        <v>-3052.192625152722</v>
+        <v>-2913.526223485752</v>
       </c>
       <c r="P62">
-        <v>-9156.577875458166</v>
+        <v>-8740.578670457257</v>
       </c>
       <c r="Q62">
-        <v>-8556.577875458166</v>
+        <v>-8140.578670457257</v>
       </c>
       <c r="R62">
         <v>1.5</v>
       </c>
       <c r="S62">
-        <v>0.1973818278543417</v>
+        <v>0.1971939590064307</v>
       </c>
       <c r="T62">
-        <v>2.344288222618375</v>
+        <v>2.342016396780825</v>
       </c>
       <c r="U62">
-        <v>0.2616309777667576</v>
+        <v>0.2516309777667576</v>
       </c>
       <c r="V62">
-        <v>0.03967469027819612</v>
+        <v>0.04125139162992601</v>
       </c>
       <c r="W62">
-        <v>0.2512508497566799</v>
+        <v>0.2412508497566799</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.1586987611127845</v>
+        <v>0.1650055665197041</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6420,13 +6420,13 @@
         <v>0.61</v>
       </c>
       <c r="B63">
-        <v>0.2318615507734121</v>
+        <v>0.2256864032342478</v>
       </c>
       <c r="C63">
-        <v>-24204.77619441577</v>
+        <v>-23182.39522767469</v>
       </c>
       <c r="D63">
-        <v>30024.2271501519</v>
+        <v>31046.60811689298</v>
       </c>
       <c r="E63">
         <v>50154.53556658789</v>
@@ -6453,37 +6453,37 @@
         <v>2303</v>
       </c>
       <c r="M63">
-        <v>14753.63334228774</v>
+        <v>14189.72330884206</v>
       </c>
       <c r="N63">
-        <v>-12450.63334228774</v>
+        <v>-11886.72330884206</v>
       </c>
       <c r="O63">
-        <v>-3112.658335571934</v>
+        <v>-2971.680827210515</v>
       </c>
       <c r="P63">
-        <v>-9337.975006715802</v>
+        <v>-8915.042481631544</v>
       </c>
       <c r="Q63">
-        <v>-8737.975006715802</v>
+        <v>-8315.042481631544</v>
       </c>
       <c r="R63">
         <v>1.564102564102564</v>
       </c>
       <c r="S63">
-        <v>0.2012685413890684</v>
+        <v>0.201075855391211</v>
       </c>
       <c r="T63">
-        <v>2.404398177044488</v>
+        <v>2.402068099262385</v>
       </c>
       <c r="U63">
-        <v>0.2616309777667576</v>
+        <v>0.2516309777667576</v>
       </c>
       <c r="V63">
-        <v>0.03902428551953716</v>
+        <v>0.04057513930812395</v>
       </c>
       <c r="W63">
-        <v>0.2514210157896319</v>
+        <v>0.241421015789632</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.1560971420781486</v>
+        <v>0.1623005572324958</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6502,13 +6502,13 @@
         <v>0.62</v>
       </c>
       <c r="B64">
-        <v>0.2340198605510797</v>
+        <v>0.2277447130119154</v>
       </c>
       <c r="C64">
-        <v>-25473.50551036094</v>
+        <v>-24458.06293415993</v>
       </c>
       <c r="D64">
-        <v>29679.94051198653</v>
+        <v>30695.38308818754</v>
       </c>
       <c r="E64">
         <v>51078.97824436769</v>
@@ -6535,37 +6535,37 @@
         <v>2303</v>
       </c>
       <c r="M64">
-        <v>14995.49618396459</v>
+        <v>14422.34172374111</v>
       </c>
       <c r="N64">
-        <v>-12692.49618396459</v>
+        <v>-12119.34172374111</v>
       </c>
       <c r="O64">
-        <v>-3173.124045991146</v>
+        <v>-3029.835430935278</v>
       </c>
       <c r="P64">
-        <v>-9519.37213797344</v>
+        <v>-9089.506292805832</v>
       </c>
       <c r="Q64">
-        <v>-8919.37213797344</v>
+        <v>-8489.506292805832</v>
       </c>
       <c r="R64">
         <v>1.631578947368421</v>
       </c>
       <c r="S64">
-        <v>0.2053598187940439</v>
+        <v>0.2051620621120324</v>
       </c>
       <c r="T64">
-        <v>2.467671813282501</v>
+        <v>2.465280417664026</v>
       </c>
       <c r="U64">
-        <v>0.2616309777667576</v>
+        <v>0.2516309777667576</v>
       </c>
       <c r="V64">
-        <v>0.03839486155954463</v>
+        <v>0.03992070157734775</v>
       </c>
       <c r="W64">
-        <v>0.2515856925957146</v>
+        <v>0.2415856925957146</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.1535794462381785</v>
+        <v>0.159682806309391</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6584,13 +6584,13 @@
         <v>0.63</v>
       </c>
       <c r="B65">
-        <v>0.2361781703287473</v>
+        <v>0.2298030227895829</v>
       </c>
       <c r="C65">
-        <v>-26734.42849834119</v>
+        <v>-25725.87283592234</v>
       </c>
       <c r="D65">
-        <v>29343.46020178607</v>
+        <v>30352.01586420492</v>
       </c>
       <c r="E65">
         <v>52003.42092214748</v>
@@ -6617,37 +6617,37 @@
         <v>2303</v>
       </c>
       <c r="M65">
-        <v>15237.35902564143</v>
+        <v>14654.96013864016</v>
       </c>
       <c r="N65">
-        <v>-12934.35902564143</v>
+        <v>-12351.96013864016</v>
       </c>
       <c r="O65">
-        <v>-3233.589756410358</v>
+        <v>-3087.99003466004</v>
       </c>
       <c r="P65">
-        <v>-9700.769269231074</v>
+        <v>-9263.970103980118</v>
       </c>
       <c r="Q65">
-        <v>-9100.769269231074</v>
+        <v>-8663.970103980118</v>
       </c>
       <c r="R65">
         <v>1.702702702702703</v>
       </c>
       <c r="S65">
-        <v>0.209672246329018</v>
+        <v>0.209469144871817</v>
       </c>
       <c r="T65">
-        <v>2.53436564607392</v>
+        <v>2.531909618141433</v>
       </c>
       <c r="U65">
-        <v>0.2616309777667576</v>
+        <v>0.2516309777667576</v>
       </c>
       <c r="V65">
-        <v>0.03778541931256773</v>
+        <v>0.03928703964754858</v>
       </c>
       <c r="W65">
-        <v>0.2517451415666835</v>
+        <v>0.2417451415666836</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.1511416772502709</v>
+        <v>0.1571481585901944</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6666,13 +6666,13 @@
         <v>0.64</v>
       </c>
       <c r="B66">
-        <v>0.2383364801064149</v>
+        <v>0.2318613325672506</v>
       </c>
       <c r="C66">
-        <v>-27987.8076822268</v>
+        <v>-26986.08571465259</v>
       </c>
       <c r="D66">
-        <v>29014.52369568025</v>
+        <v>30016.24566325447</v>
       </c>
       <c r="E66">
         <v>52927.86359992728</v>
@@ -6699,37 +6699,37 @@
         <v>2303</v>
       </c>
       <c r="M66">
-        <v>15479.22186731828</v>
+        <v>14887.57855353921</v>
       </c>
       <c r="N66">
-        <v>-13176.22186731828</v>
+        <v>-12584.57855353921</v>
       </c>
       <c r="O66">
-        <v>-3294.05546682957</v>
+        <v>-3146.144638384802</v>
       </c>
       <c r="P66">
-        <v>-9882.16640048871</v>
+        <v>-9438.433915154408</v>
       </c>
       <c r="Q66">
-        <v>-9282.16640048871</v>
+        <v>-8838.433915154408</v>
       </c>
       <c r="R66">
         <v>1.777777777777778</v>
       </c>
       <c r="S66">
-        <v>0.2142242531714908</v>
+        <v>0.2140155100071453</v>
       </c>
       <c r="T66">
-        <v>2.604764691798196</v>
+        <v>2.602240440867584</v>
       </c>
       <c r="U66">
-        <v>0.2616309777667576</v>
+        <v>0.2516309777667576</v>
       </c>
       <c r="V66">
-        <v>0.03719502213580887</v>
+        <v>0.03867317965305563</v>
       </c>
       <c r="W66">
-        <v>0.2518996077573097</v>
+        <v>0.2418996077573097</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.1487800885432354</v>
+        <v>0.1546927186122226</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6748,13 +6748,13 @@
         <v>0.65</v>
       </c>
       <c r="B67">
-        <v>0.2404947898840825</v>
+        <v>0.2339196423449181</v>
       </c>
       <c r="C67">
-        <v>-29233.89394494299</v>
+        <v>-28238.95093867702</v>
       </c>
       <c r="D67">
-        <v>28692.88011074387</v>
+        <v>29687.82311700984</v>
       </c>
       <c r="E67">
         <v>53852.30627770708</v>
@@ -6781,37 +6781,37 @@
         <v>2303</v>
       </c>
       <c r="M67">
-        <v>15721.08470899513</v>
+        <v>15120.19696843826</v>
       </c>
       <c r="N67">
-        <v>-13418.08470899513</v>
+        <v>-12817.19696843826</v>
       </c>
       <c r="O67">
-        <v>-3354.521177248782</v>
+        <v>-3204.299242109565</v>
       </c>
       <c r="P67">
-        <v>-10063.56353174635</v>
+        <v>-9612.897726328694</v>
       </c>
       <c r="Q67">
-        <v>-9463.563531746348</v>
+        <v>-9012.897726328694</v>
       </c>
       <c r="R67">
         <v>1.857142857142857</v>
       </c>
       <c r="S67">
-        <v>0.2190363746906762</v>
+        <v>0.2188216674359209</v>
       </c>
       <c r="T67">
-        <v>2.679186540135287</v>
+        <v>2.676590167749515</v>
       </c>
       <c r="U67">
-        <v>0.2616309777667576</v>
+        <v>0.2516309777667576</v>
       </c>
       <c r="V67">
-        <v>0.03662279102602718</v>
+        <v>0.03807820765839324</v>
       </c>
       <c r="W67">
-        <v>0.2520493211420705</v>
+        <v>0.2420493211420705</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.1464911641041088</v>
+        <v>0.1523128306335729</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6830,13 +6830,13 @@
         <v>0.66</v>
       </c>
       <c r="B68">
-        <v>0.2426530996617501</v>
+        <v>0.2359779521225857</v>
       </c>
       <c r="C68">
-        <v>-30472.92716663027</v>
+        <v>-29484.70708059602</v>
       </c>
       <c r="D68">
-        <v>28378.28956683639</v>
+        <v>29366.50965287063</v>
       </c>
       <c r="E68">
         <v>54776.74895548688</v>
@@ -6863,37 +6863,37 @@
         <v>2303</v>
       </c>
       <c r="M68">
-        <v>15962.94755067198</v>
+        <v>15352.81538333731</v>
       </c>
       <c r="N68">
-        <v>-13659.94755067198</v>
+        <v>-13049.81538333731</v>
       </c>
       <c r="O68">
-        <v>-3414.986887667994</v>
+        <v>-3262.453845834328</v>
       </c>
       <c r="P68">
-        <v>-10244.96066300398</v>
+        <v>-9787.361537502984</v>
       </c>
       <c r="Q68">
-        <v>-9644.960663003983</v>
+        <v>-9187.361537502984</v>
       </c>
       <c r="R68">
         <v>1.941176470588236</v>
       </c>
       <c r="S68">
-        <v>0.2241315621815785</v>
+        <v>0.2239105400075656</v>
       </c>
       <c r="T68">
-        <v>2.757986144256913</v>
+        <v>2.755313407977441</v>
       </c>
       <c r="U68">
-        <v>0.2616309777667576</v>
+        <v>0.2516309777667576</v>
       </c>
       <c r="V68">
-        <v>0.03606790025290556</v>
+        <v>0.03750126511811455</v>
       </c>
       <c r="W68">
-        <v>0.2521944977575961</v>
+        <v>0.242194497757596</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.1442716010116223</v>
+        <v>0.1500050604724582</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6912,13 +6912,13 @@
         <v>0.67</v>
       </c>
       <c r="B69">
-        <v>0.2448114094394176</v>
+        <v>0.2380362619002532</v>
       </c>
       <c r="C69">
-        <v>-31705.13682127895</v>
+        <v>-30723.58249524332</v>
       </c>
       <c r="D69">
-        <v>28070.52258996751</v>
+        <v>29052.07691600314</v>
       </c>
       <c r="E69">
         <v>55701.19163326668</v>
@@ -6945,37 +6945,37 @@
         <v>2303</v>
       </c>
       <c r="M69">
-        <v>16204.81039234883</v>
+        <v>15585.43379823636</v>
       </c>
       <c r="N69">
-        <v>-13901.81039234883</v>
+        <v>-13282.43379823636</v>
       </c>
       <c r="O69">
-        <v>-3475.452598087207</v>
+        <v>-3320.60844955909</v>
       </c>
       <c r="P69">
-        <v>-10426.35779426162</v>
+        <v>-9961.82534867727</v>
       </c>
       <c r="Q69">
-        <v>-9826.357794261621</v>
+        <v>-9361.82534867727</v>
       </c>
       <c r="R69">
         <v>2.030303030303031</v>
       </c>
       <c r="S69">
-        <v>0.2295355489143536</v>
+        <v>0.229307829098704</v>
       </c>
       <c r="T69">
-        <v>2.841561481961668</v>
+        <v>2.838807753673728</v>
       </c>
       <c r="U69">
-        <v>0.2616309777667576</v>
+        <v>0.2516309777667576</v>
       </c>
       <c r="V69">
-        <v>0.0355295733834592</v>
+        <v>0.03694154474321732</v>
       </c>
       <c r="W69">
-        <v>0.2523353407428074</v>
+        <v>0.2423353407428074</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.1421182935338369</v>
+        <v>0.1477661789728693</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6994,13 +6994,13 @@
         <v>0.68</v>
       </c>
       <c r="B70">
-        <v>0.2469697192170852</v>
+        <v>0.2400945716779208</v>
       </c>
       <c r="C70">
-        <v>-32930.74253495674</v>
+        <v>-31955.79586090875</v>
       </c>
       <c r="D70">
-        <v>27769.35955406952</v>
+        <v>28744.30622811751</v>
       </c>
       <c r="E70">
         <v>56625.63431104648</v>
@@ -7027,37 +7027,37 @@
         <v>2303</v>
       </c>
       <c r="M70">
-        <v>16446.67323402567</v>
+        <v>15818.05221313541</v>
       </c>
       <c r="N70">
-        <v>-14143.67323402567</v>
+        <v>-13515.05221313541</v>
       </c>
       <c r="O70">
-        <v>-3535.918308506419</v>
+        <v>-3378.763053283853</v>
       </c>
       <c r="P70">
-        <v>-10607.75492551926</v>
+        <v>-10136.28915985156</v>
       </c>
       <c r="Q70">
-        <v>-10007.75492551926</v>
+        <v>-9536.28915985156</v>
       </c>
       <c r="R70">
         <v>2.125</v>
       </c>
       <c r="S70">
-        <v>0.2352772848179271</v>
+        <v>0.2350424487580385</v>
       </c>
       <c r="T70">
-        <v>2.93036027827297</v>
+        <v>2.927520495976032</v>
       </c>
       <c r="U70">
-        <v>0.2616309777667576</v>
+        <v>0.2516309777667576</v>
       </c>
       <c r="V70">
-        <v>0.03500707965723186</v>
+        <v>0.03639828673228765</v>
       </c>
       <c r="W70">
-        <v>0.2524720412872772</v>
+        <v>0.2424720412872773</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.1400283186289275</v>
+        <v>0.1455931469291506</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7076,13 +7076,13 @@
         <v>0.6900000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2491280289947528</v>
+        <v>0.2421528814555884</v>
       </c>
       <c r="C71">
-        <v>-34149.95460848307</v>
+        <v>-33181.5566865202</v>
       </c>
       <c r="D71">
-        <v>27474.59015832299</v>
+        <v>28442.98808028585</v>
       </c>
       <c r="E71">
         <v>57550.07698882627</v>
@@ -7109,37 +7109,37 @@
         <v>2303</v>
       </c>
       <c r="M71">
-        <v>16688.53607570252</v>
+        <v>16050.67062803446</v>
       </c>
       <c r="N71">
-        <v>-14385.53607570252</v>
+        <v>-13747.67062803446</v>
       </c>
       <c r="O71">
-        <v>-3596.384018925631</v>
+        <v>-3436.917657008615</v>
       </c>
       <c r="P71">
-        <v>-10789.15205677689</v>
+        <v>-10310.75297102585</v>
       </c>
       <c r="Q71">
-        <v>-10189.15205677689</v>
+        <v>-9710.752971025846</v>
       </c>
       <c r="R71">
         <v>2.225806451612904</v>
       </c>
       <c r="S71">
-        <v>0.2413894552959248</v>
+        <v>0.2411470438792655</v>
       </c>
       <c r="T71">
-        <v>3.024888029185002</v>
+        <v>3.021956641007517</v>
       </c>
       <c r="U71">
-        <v>0.2616309777667576</v>
+        <v>0.2516309777667576</v>
       </c>
       <c r="V71">
-        <v>0.03449973067669227</v>
+        <v>0.03587077533037044</v>
       </c>
       <c r="W71">
-        <v>0.2526047794971248</v>
+        <v>0.2426047794971248</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.1379989227067691</v>
+        <v>0.1434831013214818</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7158,13 +7158,13 @@
         <v>0.7000000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2512863387724203</v>
+        <v>0.244211191233256</v>
       </c>
       <c r="C72">
-        <v>-35362.97450716411</v>
+        <v>-34401.06578725649</v>
       </c>
       <c r="D72">
-        <v>27186.01293742174</v>
+        <v>28147.92165732936</v>
       </c>
       <c r="E72">
         <v>58474.51966660607</v>
@@ -7191,37 +7191,37 @@
         <v>2303</v>
       </c>
       <c r="M72">
-        <v>16930.39891737937</v>
+        <v>16283.28904293351</v>
       </c>
       <c r="N72">
-        <v>-14627.39891737937</v>
+        <v>-13980.28904293351</v>
       </c>
       <c r="O72">
-        <v>-3656.849729344843</v>
+        <v>-3495.072260733378</v>
       </c>
       <c r="P72">
-        <v>-10970.54918803453</v>
+        <v>-10485.21678220013</v>
       </c>
       <c r="Q72">
-        <v>-10370.54918803453</v>
+        <v>-9885.216782200134</v>
       </c>
       <c r="R72">
         <v>2.333333333333334</v>
       </c>
       <c r="S72">
-        <v>0.247909103805789</v>
+        <v>0.2476586120085744</v>
       </c>
       <c r="T72">
-        <v>3.125717630157835</v>
+        <v>3.122688529041101</v>
       </c>
       <c r="U72">
-        <v>0.2616309777667576</v>
+        <v>0.2516309777667576</v>
       </c>
       <c r="V72">
-        <v>0.03400687738131095</v>
+        <v>0.03535833568279372</v>
       </c>
       <c r="W72">
-        <v>0.252733725186691</v>
+        <v>0.242733725186691</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.1360275095252438</v>
+        <v>0.1414333427311749</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7240,13 +7240,13 @@
         <v>0.71</v>
       </c>
       <c r="B73">
-        <v>0.2534446485500879</v>
+        <v>0.2462695010109235</v>
       </c>
       <c r="C73">
-        <v>-36569.99531998541</v>
+        <v>-35614.51573086045</v>
       </c>
       <c r="D73">
-        <v>26903.43480238023</v>
+        <v>27858.91439150518</v>
       </c>
       <c r="E73">
         <v>59398.96234438586</v>
@@ -7273,37 +7273,37 @@
         <v>2303</v>
       </c>
       <c r="M73">
-        <v>17172.26175905621</v>
+        <v>16515.90745783256</v>
       </c>
       <c r="N73">
-        <v>-14869.26175905621</v>
+        <v>-14212.90745783256</v>
       </c>
       <c r="O73">
-        <v>-3717.315439764054</v>
+        <v>-3553.22686445814</v>
       </c>
       <c r="P73">
-        <v>-11151.94631929216</v>
+        <v>-10659.68059337442</v>
       </c>
       <c r="Q73">
-        <v>-10551.94631929216</v>
+        <v>-10059.68059337442</v>
       </c>
       <c r="R73">
         <v>2.448275862068965</v>
       </c>
       <c r="S73">
-        <v>0.2548783832473678</v>
+        <v>0.2546192538019734</v>
       </c>
       <c r="T73">
-        <v>3.233500996715001</v>
+        <v>3.23036744383562</v>
       </c>
       <c r="U73">
-        <v>0.2616309777667576</v>
+        <v>0.2516309777667576</v>
       </c>
       <c r="V73">
-        <v>0.03352790727734883</v>
+        <v>0.03486033095486706</v>
       </c>
       <c r="W73">
-        <v>0.2528590386033116</v>
+        <v>0.2428590386033116</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.1341116291093953</v>
+        <v>0.1394413238194682</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7322,13 +7322,13 @@
         <v>0.72</v>
       </c>
       <c r="B74">
-        <v>0.2556029583277555</v>
+        <v>0.2483278107885911</v>
       </c>
       <c r="C74">
-        <v>-37771.20219046123</v>
+        <v>-36822.09125673635</v>
       </c>
       <c r="D74">
-        <v>26626.67060968421</v>
+        <v>27575.7815434091</v>
       </c>
       <c r="E74">
         <v>60323.40502216567</v>
@@ -7355,37 +7355,37 @@
         <v>2303</v>
       </c>
       <c r="M74">
-        <v>17414.12460073307</v>
+        <v>16748.52587273161</v>
       </c>
       <c r="N74">
-        <v>-15111.12460073307</v>
+        <v>-14445.52587273161</v>
       </c>
       <c r="O74">
-        <v>-3777.781150183267</v>
+        <v>-3611.381468182903</v>
       </c>
       <c r="P74">
-        <v>-11333.3434505498</v>
+        <v>-10834.14440454871</v>
       </c>
       <c r="Q74">
-        <v>-10733.3434505498</v>
+        <v>-10234.14440454871</v>
       </c>
       <c r="R74">
         <v>2.571428571428571</v>
       </c>
       <c r="S74">
-        <v>0.2623454683633452</v>
+        <v>0.2620770842949011</v>
       </c>
       <c r="T74">
-        <v>3.348983175169108</v>
+        <v>3.345737709686893</v>
       </c>
       <c r="U74">
-        <v>0.2616309777667576</v>
+        <v>0.2516309777667576</v>
       </c>
       <c r="V74">
-        <v>0.03306224189849676</v>
+        <v>0.03437615969160501</v>
       </c>
       <c r="W74">
-        <v>0.2529808710916928</v>
+        <v>0.2429808710916928</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.1322489675939871</v>
+        <v>0.1375046387664201</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7404,13 +7404,13 @@
         <v>0.73</v>
       </c>
       <c r="B75">
-        <v>0.2577612681054231</v>
+        <v>0.2503861205662587</v>
       </c>
       <c r="C75">
-        <v>-38966.772721161</v>
+        <v>-38023.96966974844</v>
       </c>
       <c r="D75">
-        <v>26355.54275676424</v>
+        <v>27298.3458081768</v>
       </c>
       <c r="E75">
         <v>61247.84769994546</v>
@@ -7437,37 +7437,37 @@
         <v>2303</v>
       </c>
       <c r="M75">
-        <v>17655.98744240991</v>
+        <v>16981.14428763066</v>
       </c>
       <c r="N75">
-        <v>-15352.98744240991</v>
+        <v>-14678.14428763066</v>
       </c>
       <c r="O75">
-        <v>-3838.246860602478</v>
+        <v>-3669.536071907665</v>
       </c>
       <c r="P75">
-        <v>-11514.74058180743</v>
+        <v>-11008.608215723</v>
       </c>
       <c r="Q75">
-        <v>-10914.74058180743</v>
+        <v>-10408.608215723</v>
       </c>
       <c r="R75">
         <v>2.703703703703703</v>
       </c>
       <c r="S75">
-        <v>0.2703656708953209</v>
+        <v>0.2700873466761937</v>
       </c>
       <c r="T75">
-        <v>3.47301958906426</v>
+        <v>3.469653921156778</v>
       </c>
       <c r="U75">
-        <v>0.2616309777667576</v>
+        <v>0.2516309777667576</v>
       </c>
       <c r="V75">
-        <v>0.03260933447522969</v>
+        <v>0.03390525339445973</v>
       </c>
       <c r="W75">
-        <v>0.25309936570368</v>
+        <v>0.24309936570368</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.1304373379009187</v>
+        <v>0.135621013577839</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7486,13 +7486,13 @@
         <v>0.74</v>
       </c>
       <c r="B76">
-        <v>0.2599195778830907</v>
+        <v>0.2524444303439263</v>
       </c>
       <c r="C76">
-        <v>-40156.87735377016</v>
+        <v>-39220.32121048479</v>
       </c>
       <c r="D76">
-        <v>26089.88080193488</v>
+        <v>27026.43694522025</v>
       </c>
       <c r="E76">
         <v>62172.29037772526</v>
@@ -7519,37 +7519,37 @@
         <v>2303</v>
       </c>
       <c r="M76">
-        <v>17897.85028408676</v>
+        <v>17213.76270252971</v>
       </c>
       <c r="N76">
-        <v>-15594.85028408676</v>
+        <v>-14910.76270252971</v>
       </c>
       <c r="O76">
-        <v>-3898.712571021691</v>
+        <v>-3727.690675632428</v>
       </c>
       <c r="P76">
-        <v>-11696.13771306507</v>
+        <v>-11183.07202689728</v>
       </c>
       <c r="Q76">
-        <v>-11096.13771306507</v>
+        <v>-10583.07202689728</v>
       </c>
       <c r="R76">
         <v>2.846153846153846</v>
       </c>
       <c r="S76">
-        <v>0.2790028120836026</v>
+        <v>0.2787137830868165</v>
       </c>
       <c r="T76">
-        <v>3.606597265566732</v>
+        <v>3.603102148893577</v>
       </c>
       <c r="U76">
-        <v>0.2616309777667576</v>
+        <v>0.2516309777667576</v>
       </c>
       <c r="V76">
-        <v>0.03216866779313199</v>
+        <v>0.03344707429453461</v>
       </c>
       <c r="W76">
-        <v>0.2532146577585865</v>
+        <v>0.2432146577585864</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.128674671172528</v>
+        <v>0.1337882971781384</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7568,13 +7568,13 @@
         <v>0.75</v>
       </c>
       <c r="B77">
-        <v>0.2620778876607582</v>
+        <v>0.2545027401215939</v>
       </c>
       <c r="C77">
-        <v>-41341.67972639459</v>
+        <v>-40411.30940361074</v>
       </c>
       <c r="D77">
-        <v>25829.52110709024</v>
+        <v>26759.8914298741</v>
       </c>
       <c r="E77">
         <v>63096.73305550506</v>
@@ -7601,37 +7601,37 @@
         <v>2303</v>
       </c>
       <c r="M77">
-        <v>18139.71312576361</v>
+        <v>17446.38111742876</v>
       </c>
       <c r="N77">
-        <v>-15836.71312576361</v>
+        <v>-15143.38111742876</v>
       </c>
       <c r="O77">
-        <v>-3959.178281440903</v>
+        <v>-3785.845279357191</v>
       </c>
       <c r="P77">
-        <v>-11877.53484432271</v>
+        <v>-11357.53583807157</v>
       </c>
       <c r="Q77">
-        <v>-11277.53484432271</v>
+        <v>-10757.53583807157</v>
       </c>
       <c r="R77">
         <v>3</v>
       </c>
       <c r="S77">
-        <v>0.2883309245669466</v>
+        <v>0.2880303344102892</v>
       </c>
       <c r="T77">
-        <v>3.750861156189401</v>
+        <v>3.74722623484932</v>
       </c>
       <c r="U77">
-        <v>0.2616309777667576</v>
+        <v>0.2516309777667576</v>
       </c>
       <c r="V77">
-        <v>0.03173975222255689</v>
+        <v>0.03300111330394081</v>
       </c>
       <c r="W77">
-        <v>0.2533268753586954</v>
+        <v>0.2433268753586954</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.1269590088902276</v>
+        <v>0.1320044532157633</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7650,13 +7650,13 @@
         <v>0.76</v>
       </c>
       <c r="B78">
-        <v>0.2642361974384259</v>
+        <v>0.2565610498992614</v>
       </c>
       <c r="C78">
-        <v>-42521.33700968234</v>
+        <v>-41597.0913858102</v>
       </c>
       <c r="D78">
-        <v>25574.30650158229</v>
+        <v>26498.55212545443</v>
       </c>
       <c r="E78">
         <v>64021.17573328485</v>
@@ -7683,37 +7683,37 @@
         <v>2303</v>
       </c>
       <c r="M78">
-        <v>18381.57596744046</v>
+        <v>17678.99953232781</v>
       </c>
       <c r="N78">
-        <v>-16078.57596744046</v>
+        <v>-15375.99953232781</v>
       </c>
       <c r="O78">
-        <v>-4019.643991860115</v>
+        <v>-3843.999883081952</v>
       </c>
       <c r="P78">
-        <v>-12058.93197558034</v>
+        <v>-11531.99964924586</v>
       </c>
       <c r="Q78">
-        <v>-11458.93197558034</v>
+        <v>-10931.99964924586</v>
       </c>
       <c r="R78">
         <v>3.166666666666667</v>
       </c>
       <c r="S78">
-        <v>0.2984363797572361</v>
+        <v>0.2981232650107179</v>
       </c>
       <c r="T78">
-        <v>3.907147037697293</v>
+        <v>3.903360661301375</v>
       </c>
       <c r="U78">
-        <v>0.2616309777667576</v>
+        <v>0.2516309777667576</v>
       </c>
       <c r="V78">
-        <v>0.03132212390383904</v>
+        <v>0.03256688812888896</v>
       </c>
       <c r="W78">
-        <v>0.2534361398640647</v>
+        <v>0.2434361398640646</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.1252884956153562</v>
+        <v>0.1302675525155559</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7732,13 +7732,13 @@
         <v>0.77</v>
       </c>
       <c r="B79">
-        <v>0.2663945072160934</v>
+        <v>0.258619359676929</v>
       </c>
       <c r="C79">
-        <v>-43696.00022321356</v>
+        <v>-42777.81821469663</v>
       </c>
       <c r="D79">
-        <v>25324.08596583088</v>
+        <v>26242.26797434781</v>
       </c>
       <c r="E79">
         <v>64945.61841106466</v>
@@ -7765,37 +7765,37 @@
         <v>2303</v>
       </c>
       <c r="M79">
-        <v>18623.43880911731</v>
+        <v>17911.61794722686</v>
       </c>
       <c r="N79">
-        <v>-16320.43880911731</v>
+        <v>-15608.61794722686</v>
       </c>
       <c r="O79">
-        <v>-4080.109702279326</v>
+        <v>-3902.154486806716</v>
       </c>
       <c r="P79">
-        <v>-12240.32910683798</v>
+        <v>-11706.46346042015</v>
       </c>
       <c r="Q79">
-        <v>-11640.32910683798</v>
+        <v>-11106.46346042015</v>
       </c>
       <c r="R79">
         <v>3.347826086956522</v>
       </c>
       <c r="S79">
-        <v>0.3094205701814638</v>
+        <v>0.3090938417503143</v>
       </c>
       <c r="T79">
-        <v>4.077022995858045</v>
+        <v>4.073071994401436</v>
       </c>
       <c r="U79">
-        <v>0.2616309777667576</v>
+        <v>0.2516309777667576</v>
       </c>
       <c r="V79">
-        <v>0.03091534307391905</v>
+        <v>0.03214394152981247</v>
       </c>
       <c r="W79">
-        <v>0.2535425663303334</v>
+        <v>0.2435425663303334</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.1236613722956762</v>
+        <v>0.1285757661192499</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7814,13 +7814,13 @@
         <v>0.78</v>
       </c>
       <c r="B80">
-        <v>0.268552816993761</v>
+        <v>0.2606776694545966</v>
       </c>
       <c r="C80">
-        <v>-44865.81453349702</v>
+        <v>-43953.63515996952</v>
       </c>
       <c r="D80">
-        <v>25078.71433332721</v>
+        <v>25990.89370685471</v>
       </c>
       <c r="E80">
         <v>65870.06108884445</v>
@@ -7847,37 +7847,37 @@
         <v>2303</v>
       </c>
       <c r="M80">
-        <v>18865.30165079415</v>
+        <v>18144.23636212591</v>
       </c>
       <c r="N80">
-        <v>-16562.30165079415</v>
+        <v>-15841.23636212591</v>
       </c>
       <c r="O80">
-        <v>-4140.575412698538</v>
+        <v>-3960.309090531478</v>
       </c>
       <c r="P80">
-        <v>-12421.72623809562</v>
+        <v>-11880.92727159443</v>
       </c>
       <c r="Q80">
-        <v>-11821.72623809562</v>
+        <v>-11280.92727159443</v>
       </c>
       <c r="R80">
         <v>3.545454545454546</v>
       </c>
       <c r="S80">
-        <v>0.3214033233715303</v>
+        <v>0.3210617436480559</v>
       </c>
       <c r="T80">
-        <v>4.262342222942501</v>
+        <v>4.258211630510591</v>
       </c>
       <c r="U80">
-        <v>0.2616309777667576</v>
+        <v>0.2516309777667576</v>
       </c>
       <c r="V80">
-        <v>0.03051899252168932</v>
+        <v>0.0317318397153277</v>
       </c>
       <c r="W80">
-        <v>0.2536462639128517</v>
+        <v>0.2436462639128517</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.1220759700867573</v>
+        <v>0.1269273588613108</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7896,13 +7896,13 @@
         <v>0.79</v>
       </c>
       <c r="B81">
-        <v>0.2707111267714285</v>
+        <v>0.2627359792322642</v>
       </c>
       <c r="C81">
-        <v>-46030.91953480855</v>
+        <v>-45124.68197799598</v>
       </c>
       <c r="D81">
-        <v>24838.05200979549</v>
+        <v>25744.28956660806</v>
       </c>
       <c r="E81">
         <v>66794.50376662426</v>
@@ -7929,37 +7929,37 @@
         <v>2303</v>
       </c>
       <c r="M81">
-        <v>19107.16449247101</v>
+        <v>18376.85477702496</v>
       </c>
       <c r="N81">
-        <v>-16804.16449247101</v>
+        <v>-16073.85477702496</v>
       </c>
       <c r="O81">
-        <v>-4201.041123117751</v>
+        <v>-4018.463694256241</v>
       </c>
       <c r="P81">
-        <v>-12603.12336935325</v>
+        <v>-12055.39108276872</v>
       </c>
       <c r="Q81">
-        <v>-12003.12336935325</v>
+        <v>-11455.39108276872</v>
       </c>
       <c r="R81">
         <v>3.761904761904763</v>
       </c>
       <c r="S81">
-        <v>0.3345272911511271</v>
+        <v>0.3341694457265348</v>
       </c>
       <c r="T81">
-        <v>4.465310900225479</v>
+        <v>4.460983612915858</v>
       </c>
       <c r="U81">
-        <v>0.2616309777667576</v>
+        <v>0.2516309777667576</v>
       </c>
       <c r="V81">
-        <v>0.03013267616065527</v>
+        <v>0.03133017085817165</v>
       </c>
       <c r="W81">
-        <v>0.2537473362401163</v>
+        <v>0.2437473362401163</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.1205307046426211</v>
+        <v>0.1253206834326867</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7978,13 +7978,13 @@
         <v>0.8</v>
       </c>
       <c r="B82">
-        <v>0.2728694365490961</v>
+        <v>0.2647942890099317</v>
       </c>
       <c r="C82">
-        <v>-47191.44951401329</v>
+        <v>-46291.09317090746</v>
       </c>
       <c r="D82">
-        <v>24601.96470837054</v>
+        <v>25502.32105147636</v>
       </c>
       <c r="E82">
         <v>67718.94644440405</v>
@@ -8011,37 +8011,37 @@
         <v>2303</v>
       </c>
       <c r="M82">
-        <v>19349.02733414785</v>
+        <v>18609.47319192401</v>
       </c>
       <c r="N82">
-        <v>-17046.02733414785</v>
+        <v>-16306.47319192401</v>
       </c>
       <c r="O82">
-        <v>-4261.506833536962</v>
+        <v>-4076.618297981003</v>
       </c>
       <c r="P82">
-        <v>-12784.52050061089</v>
+        <v>-12229.85489394301</v>
       </c>
       <c r="Q82">
-        <v>-12184.52050061089</v>
+        <v>-11629.85489394301</v>
       </c>
       <c r="R82">
         <v>4.000000000000001</v>
       </c>
       <c r="S82">
-        <v>0.3489636557086834</v>
+        <v>0.3485879180128615</v>
       </c>
       <c r="T82">
-        <v>4.688576445236753</v>
+        <v>4.684032793561651</v>
       </c>
       <c r="U82">
-        <v>0.2616309777667576</v>
+        <v>0.2516309777667576</v>
       </c>
       <c r="V82">
-        <v>0.02975601770864709</v>
+        <v>0.03093854372244451</v>
       </c>
       <c r="W82">
-        <v>0.2538458817591993</v>
+        <v>0.2438458817591993</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.1190240708345883</v>
+        <v>0.123754174889778</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8060,13 +8060,13 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2750277463267637</v>
+        <v>0.2668525987875993</v>
       </c>
       <c r="C83">
-        <v>-48347.53370042711</v>
+        <v>-47452.99823122143</v>
       </c>
       <c r="D83">
-        <v>24370.32319973651</v>
+        <v>25264.8586689422</v>
       </c>
       <c r="E83">
         <v>68643.38912218384</v>
@@ -8093,37 +8093,37 @@
         <v>2303</v>
       </c>
       <c r="M83">
-        <v>19590.8901758247</v>
+        <v>18842.09160682306</v>
       </c>
       <c r="N83">
-        <v>-17287.8901758247</v>
+        <v>-16539.09160682306</v>
       </c>
       <c r="O83">
-        <v>-4321.972543956174</v>
+        <v>-4134.772901705765</v>
       </c>
       <c r="P83">
-        <v>-12965.91763186852</v>
+        <v>-12404.3187051173</v>
       </c>
       <c r="Q83">
-        <v>-12365.91763186852</v>
+        <v>-11804.3187051173</v>
       </c>
       <c r="R83">
         <v>4.263157894736843</v>
       </c>
       <c r="S83">
-        <v>0.3649196375880878</v>
+        <v>0.3645241242240648</v>
       </c>
       <c r="T83">
-        <v>4.935343626565003</v>
+        <v>4.930560835328055</v>
       </c>
       <c r="U83">
-        <v>0.2616309777667576</v>
+        <v>0.2516309777667576</v>
       </c>
       <c r="V83">
-        <v>0.02938865946533046</v>
+        <v>0.03055658639253779</v>
       </c>
       <c r="W83">
-        <v>0.2539419940555889</v>
+        <v>0.2439419940555889</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.1175546378613218</v>
+        <v>0.1222263455701511</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8142,13 +8142,13 @@
         <v>0.8200000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2771860561044313</v>
+        <v>0.2689109085652669</v>
       </c>
       <c r="C84">
-        <v>-49499.29650169426</v>
+        <v>-48610.52187292218</v>
       </c>
       <c r="D84">
-        <v>24143.00307624917</v>
+        <v>25031.77770502124</v>
       </c>
       <c r="E84">
         <v>69567.83179996365</v>
@@ -8175,37 +8175,37 @@
         <v>2303</v>
       </c>
       <c r="M84">
-        <v>19832.75301750155</v>
+        <v>19074.71002172211</v>
       </c>
       <c r="N84">
-        <v>-17529.75301750155</v>
+        <v>-16771.71002172211</v>
       </c>
       <c r="O84">
-        <v>-4382.438254375387</v>
+        <v>-4192.927505430528</v>
       </c>
       <c r="P84">
-        <v>-13147.31476312616</v>
+        <v>-12578.78251629158</v>
       </c>
       <c r="Q84">
-        <v>-12547.31476312616</v>
+        <v>-11978.78251629158</v>
       </c>
       <c r="R84">
         <v>4.555555555555557</v>
       </c>
       <c r="S84">
-        <v>0.3826485063429816</v>
+        <v>0.3822310200142907</v>
       </c>
       <c r="T84">
-        <v>5.209529383596393</v>
+        <v>5.204480881735169</v>
       </c>
       <c r="U84">
-        <v>0.2616309777667576</v>
+        <v>0.2516309777667576</v>
       </c>
       <c r="V84">
-        <v>0.02903026117916789</v>
+        <v>0.03018394509506781</v>
       </c>
       <c r="W84">
-        <v>0.2540357621496276</v>
+        <v>0.2440357621496275</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.1161210447166715</v>
+        <v>0.1207357803802712</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8224,13 +8224,13 @@
         <v>0.8300000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2793443658820989</v>
+        <v>0.2709692183429345</v>
       </c>
       <c r="C85">
-        <v>-50646.85772658572</v>
+        <v>-49763.78424986786</v>
       </c>
       <c r="D85">
-        <v>23919.88452913751</v>
+        <v>24802.95800585536</v>
       </c>
       <c r="E85">
         <v>70492.27447774344</v>
@@ -8257,37 +8257,37 @@
         <v>2303</v>
       </c>
       <c r="M85">
-        <v>20074.6158591784</v>
+        <v>19307.32843662116</v>
       </c>
       <c r="N85">
-        <v>-17771.6158591784</v>
+        <v>-17004.32843662116</v>
       </c>
       <c r="O85">
-        <v>-4442.903964794599</v>
+        <v>-4251.082109155291</v>
       </c>
       <c r="P85">
-        <v>-13328.7118943838</v>
+        <v>-12753.24632746587</v>
       </c>
       <c r="Q85">
-        <v>-12728.7118943838</v>
+        <v>-12153.24632746587</v>
       </c>
       <c r="R85">
         <v>4.882352941176473</v>
       </c>
       <c r="S85">
-        <v>0.402463124363157</v>
+        <v>0.4020210800151313</v>
       </c>
       <c r="T85">
-        <v>5.515972288513828</v>
+        <v>5.510626815954885</v>
       </c>
       <c r="U85">
-        <v>0.2616309777667576</v>
+        <v>0.2516309777667576</v>
       </c>
       <c r="V85">
-        <v>0.02868049899628635</v>
+        <v>0.02982028310597061</v>
       </c>
       <c r="W85">
-        <v>0.2541272707715207</v>
+        <v>0.2441272707715207</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.1147219959851454</v>
+        <v>0.1192811324238824</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8306,13 +8306,13 @@
         <v>0.84</v>
       </c>
       <c r="B86">
-        <v>0.2815026756597664</v>
+        <v>0.273027528120602</v>
       </c>
       <c r="C86">
-        <v>-51790.33279555668</v>
+        <v>-50912.90116232679</v>
       </c>
       <c r="D86">
-        <v>23700.85213794634</v>
+        <v>24578.28377117622</v>
       </c>
       <c r="E86">
         <v>71416.71715552323</v>
@@ -8339,37 +8339,37 @@
         <v>2303</v>
       </c>
       <c r="M86">
-        <v>20316.47870085524</v>
+        <v>19539.94685152021</v>
       </c>
       <c r="N86">
-        <v>-18013.47870085524</v>
+        <v>-17236.94685152021</v>
       </c>
       <c r="O86">
-        <v>-4503.36967521381</v>
+        <v>-4309.236712880052</v>
       </c>
       <c r="P86">
-        <v>-13510.10902564143</v>
+        <v>-12927.71013864016</v>
       </c>
       <c r="Q86">
-        <v>-12910.10902564143</v>
+        <v>-12327.71013864016</v>
       </c>
       <c r="R86">
         <v>5.249999999999999</v>
       </c>
       <c r="S86">
-        <v>0.4247545696358541</v>
+        <v>0.4242848975160768</v>
       </c>
       <c r="T86">
-        <v>5.860720556545939</v>
+        <v>5.855040991952062</v>
       </c>
       <c r="U86">
-        <v>0.2616309777667576</v>
+        <v>0.2516309777667576</v>
       </c>
       <c r="V86">
-        <v>0.0283390644844258</v>
+        <v>0.02946527973566144</v>
       </c>
       <c r="W86">
-        <v>0.2542166006167021</v>
+        <v>0.2442166006167021</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.1133562579377032</v>
+        <v>0.1178611189426457</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8388,13 +8388,13 @@
         <v>0.85</v>
       </c>
       <c r="B87">
-        <v>0.283660985437434</v>
+        <v>0.2750858378982696</v>
       </c>
       <c r="C87">
-        <v>-52929.83293984074</v>
+        <v>-52057.98425238947</v>
       </c>
       <c r="D87">
-        <v>23485.79467144207</v>
+        <v>24357.64335889334</v>
       </c>
       <c r="E87">
         <v>72341.15983330303</v>
@@ -8421,37 +8421,37 @@
         <v>2303</v>
       </c>
       <c r="M87">
-        <v>20558.34154253209</v>
+        <v>19772.56526641926</v>
       </c>
       <c r="N87">
-        <v>-18255.34154253209</v>
+        <v>-17469.56526641926</v>
       </c>
       <c r="O87">
-        <v>-4563.835385633022</v>
+        <v>-4367.391316604815</v>
       </c>
       <c r="P87">
-        <v>-13691.50615689907</v>
+        <v>-13102.17394981445</v>
       </c>
       <c r="Q87">
-        <v>-13091.50615689907</v>
+        <v>-12502.17394981445</v>
       </c>
       <c r="R87">
         <v>5.666666666666666</v>
       </c>
       <c r="S87">
-        <v>0.4500182076115777</v>
+        <v>0.4495172240171486</v>
       </c>
       <c r="T87">
-        <v>6.251435260315668</v>
+        <v>6.2453770580822</v>
       </c>
       <c r="U87">
-        <v>0.2616309777667576</v>
+        <v>0.2516309777667576</v>
       </c>
       <c r="V87">
-        <v>0.0280056637257855</v>
+        <v>0.02911862938583013</v>
       </c>
       <c r="W87">
-        <v>0.2543038285831733</v>
+        <v>0.2443038285831733</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.112022654903142</v>
+        <v>0.1164745175433205</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8470,13 +8470,13 @@
         <v>0.86</v>
       </c>
       <c r="B88">
-        <v>0.2858192952151015</v>
+        <v>0.2771441476759372</v>
       </c>
       <c r="C88">
-        <v>-54065.46538980214</v>
+        <v>-53199.14118894871</v>
       </c>
       <c r="D88">
-        <v>23274.60489926047</v>
+        <v>24140.92910011391</v>
       </c>
       <c r="E88">
         <v>73265.60251108283</v>
@@ -8503,37 +8503,37 @@
         <v>2303</v>
       </c>
       <c r="M88">
-        <v>20800.20438420894</v>
+        <v>20005.18368131831</v>
       </c>
       <c r="N88">
-        <v>-18497.20438420894</v>
+        <v>-17702.18368131831</v>
       </c>
       <c r="O88">
-        <v>-4624.301096052235</v>
+        <v>-4425.545920329578</v>
       </c>
       <c r="P88">
-        <v>-13872.90328815671</v>
+        <v>-13276.63776098873</v>
       </c>
       <c r="Q88">
-        <v>-13272.90328815671</v>
+        <v>-12676.63776098873</v>
       </c>
       <c r="R88">
         <v>6.142857142857142</v>
       </c>
       <c r="S88">
-        <v>0.4788909367266904</v>
+        <v>0.4783541685898021</v>
       </c>
       <c r="T88">
-        <v>6.697966350338215</v>
+        <v>6.691475419373785</v>
       </c>
       <c r="U88">
-        <v>0.2616309777667576</v>
+        <v>0.2516309777667576</v>
       </c>
       <c r="V88">
-        <v>0.02768001647316008</v>
+        <v>0.0287800406720414</v>
       </c>
       <c r="W88">
-        <v>0.2543890279922847</v>
+        <v>0.2443890279922847</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.1107200658926403</v>
+        <v>0.1151201626881656</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8552,13 +8552,13 @@
         <v>0.87</v>
       </c>
       <c r="B89">
-        <v>0.2879776049927691</v>
+        <v>0.2792024574536048</v>
       </c>
       <c r="C89">
-        <v>-55197.33355321643</v>
+        <v>-54336.47584289213</v>
       </c>
       <c r="D89">
-        <v>23067.17941362598</v>
+        <v>23928.03712395028</v>
       </c>
       <c r="E89">
         <v>74190.04518886263</v>
@@ -8585,37 +8585,37 @@
         <v>2303</v>
       </c>
       <c r="M89">
-        <v>21042.06722588578</v>
+        <v>20237.80209621736</v>
       </c>
       <c r="N89">
-        <v>-18739.06722588578</v>
+        <v>-17934.80209621736</v>
       </c>
       <c r="O89">
-        <v>-4684.766806471446</v>
+        <v>-4483.70052405434</v>
       </c>
       <c r="P89">
-        <v>-14054.30041941434</v>
+        <v>-13451.10157216302</v>
       </c>
       <c r="Q89">
-        <v>-13454.30041941434</v>
+        <v>-12851.10157216302</v>
       </c>
       <c r="R89">
         <v>6.692307692307692</v>
       </c>
       <c r="S89">
-        <v>0.5122056241672052</v>
+        <v>0.511627566173633</v>
       </c>
       <c r="T89">
-        <v>7.213194531133464</v>
+        <v>7.206204297787154</v>
       </c>
       <c r="U89">
-        <v>0.2616309777667576</v>
+        <v>0.2516309777667576</v>
       </c>
       <c r="V89">
-        <v>0.02736185536427319</v>
+        <v>0.02844923560684553</v>
       </c>
       <c r="W89">
-        <v>0.2544722687942902</v>
+        <v>0.2444722687942902</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.1094474214570927</v>
+        <v>0.1137969424273821</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8634,13 +8634,13 @@
         <v>0.88</v>
       </c>
       <c r="B90">
-        <v>0.2901359147704367</v>
+        <v>0.2812607672312724</v>
       </c>
       <c r="C90">
-        <v>-56325.5371841022</v>
+        <v>-55470.08845310591</v>
       </c>
       <c r="D90">
-        <v>22863.41846052001</v>
+        <v>23718.8671915163</v>
       </c>
       <c r="E90">
         <v>75114.48786664243</v>
@@ -8667,37 +8667,37 @@
         <v>2303</v>
       </c>
       <c r="M90">
-        <v>21283.93006756264</v>
+        <v>20470.42051111642</v>
       </c>
       <c r="N90">
-        <v>-18980.93006756264</v>
+        <v>-18167.42051111642</v>
       </c>
       <c r="O90">
-        <v>-4745.232516890659</v>
+        <v>-4541.855127779104</v>
       </c>
       <c r="P90">
-        <v>-14235.69755067198</v>
+        <v>-13625.56538333731</v>
       </c>
       <c r="Q90">
-        <v>-13635.69755067198</v>
+        <v>-13025.56538333731</v>
       </c>
       <c r="R90">
         <v>7.333333333333334</v>
       </c>
       <c r="S90">
-        <v>0.5510727595144722</v>
+        <v>0.5504465300214358</v>
       </c>
       <c r="T90">
-        <v>7.814294075394587</v>
+        <v>7.806721322602752</v>
       </c>
       <c r="U90">
-        <v>0.2616309777667576</v>
+        <v>0.2516309777667576</v>
       </c>
       <c r="V90">
-        <v>0.02705092518967917</v>
+        <v>0.02812594883858591</v>
       </c>
       <c r="W90">
-        <v>0.2545536177598864</v>
+        <v>0.2445536177598864</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.1082037007587167</v>
+        <v>0.1125037953543436</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8716,13 +8716,13 @@
         <v>0.89</v>
       </c>
       <c r="B91">
-        <v>0.2922942245481043</v>
+        <v>0.2833190770089399</v>
       </c>
       <c r="C91">
-        <v>-57450.17254268298</v>
+        <v>-56600.07578384703</v>
       </c>
       <c r="D91">
-        <v>22663.22577971903</v>
+        <v>23513.32253855497</v>
       </c>
       <c r="E91">
         <v>76038.93054442223</v>
@@ -8749,37 +8749,37 @@
         <v>2303</v>
       </c>
       <c r="M91">
-        <v>21525.79290923948</v>
+        <v>20703.03892601546</v>
       </c>
       <c r="N91">
-        <v>-19222.79290923948</v>
+        <v>-18400.03892601546</v>
       </c>
       <c r="O91">
-        <v>-4805.698227309871</v>
+        <v>-4600.009731503866</v>
       </c>
       <c r="P91">
-        <v>-14417.09468192961</v>
+        <v>-13800.0291945116</v>
       </c>
       <c r="Q91">
-        <v>-13817.09468192961</v>
+        <v>-13200.0291945116</v>
       </c>
       <c r="R91">
         <v>8.090909090909092</v>
       </c>
       <c r="S91">
-        <v>0.5970066467430607</v>
+        <v>0.5963234872961117</v>
       </c>
       <c r="T91">
-        <v>8.524684445885004</v>
+        <v>8.516423261021183</v>
       </c>
       <c r="U91">
-        <v>0.2616309777667576</v>
+        <v>0.2516309777667576</v>
       </c>
       <c r="V91">
-        <v>0.02674698221001985</v>
+        <v>0.02780992694152315</v>
       </c>
       <c r="W91">
-        <v>0.25463313865884</v>
+        <v>0.24463313865884</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.1069879288400795</v>
+        <v>0.1112397077660926</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8798,13 +8798,13 @@
         <v>0.9</v>
       </c>
       <c r="B92">
-        <v>0.2944525343257719</v>
+        <v>0.2853773867866075</v>
       </c>
       <c r="C92">
-        <v>-58571.33254701845</v>
+        <v>-57726.53127400327</v>
       </c>
       <c r="D92">
-        <v>22466.50845316336</v>
+        <v>23311.30972617854</v>
       </c>
       <c r="E92">
         <v>76963.37322220203</v>
@@ -8831,37 +8831,37 @@
         <v>2303</v>
       </c>
       <c r="M92">
-        <v>21767.65575091634</v>
+        <v>20935.65734091452</v>
       </c>
       <c r="N92">
-        <v>-19464.65575091634</v>
+        <v>-18632.65734091452</v>
       </c>
       <c r="O92">
-        <v>-4866.163937729084</v>
+        <v>-4658.164335228629</v>
       </c>
       <c r="P92">
-        <v>-14598.49181318725</v>
+        <v>-13974.49300568589</v>
       </c>
       <c r="Q92">
-        <v>-13998.49181318725</v>
+        <v>-13374.49300568589</v>
       </c>
       <c r="R92">
         <v>9.000000000000002</v>
       </c>
       <c r="S92">
-        <v>0.6521273114173668</v>
+        <v>0.651375836025723</v>
       </c>
       <c r="T92">
-        <v>9.377152890473505</v>
+        <v>9.368065587123303</v>
       </c>
       <c r="U92">
-        <v>0.2616309777667576</v>
+        <v>0.2516309777667576</v>
       </c>
       <c r="V92">
-        <v>0.02644979351879741</v>
+        <v>0.027500927753284</v>
       </c>
       <c r="W92">
-        <v>0.2547108924267058</v>
+        <v>0.2447108924267057</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.1057991740751896</v>
+        <v>0.110003711013136</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8880,13 +8880,13 @@
         <v>0.91</v>
       </c>
       <c r="B93">
-        <v>0.2966108441034395</v>
+        <v>0.2874356965642751</v>
       </c>
       <c r="C93">
-        <v>-59689.10691680641</v>
+        <v>-58849.54517872455</v>
       </c>
       <c r="D93">
-        <v>22273.1767611552</v>
+        <v>23112.73849923705</v>
       </c>
       <c r="E93">
         <v>77887.81589998183</v>
@@ -8913,37 +8913,37 @@
         <v>2303</v>
       </c>
       <c r="M93">
-        <v>22009.51859259318</v>
+        <v>21168.27575581356</v>
       </c>
       <c r="N93">
-        <v>-19706.51859259318</v>
+        <v>-18865.27575581356</v>
       </c>
       <c r="O93">
-        <v>-4926.629648148295</v>
+        <v>-4716.318938953391</v>
       </c>
       <c r="P93">
-        <v>-14779.88894444489</v>
+        <v>-14148.95681686017</v>
       </c>
       <c r="Q93">
-        <v>-14179.88894444489</v>
+        <v>-13548.95681686017</v>
       </c>
       <c r="R93">
         <v>10.11111111111111</v>
       </c>
       <c r="S93">
-        <v>0.7194970126859632</v>
+        <v>0.7186620400285813</v>
       </c>
       <c r="T93">
-        <v>10.41905876719279</v>
+        <v>10.40896176347034</v>
       </c>
       <c r="U93">
-        <v>0.2616309777667576</v>
+        <v>0.2516309777667576</v>
       </c>
       <c r="V93">
-        <v>0.02615913644716228</v>
+        <v>0.02719871975599517</v>
       </c>
       <c r="W93">
-        <v>0.2547869373205525</v>
+        <v>0.2447869373205525</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.1046365457886491</v>
+        <v>0.1087948790239807</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8962,13 +8962,13 @@
         <v>0.92</v>
       </c>
       <c r="B94">
-        <v>0.298769153881107</v>
+        <v>0.2894940063419427</v>
       </c>
       <c r="C94">
-        <v>-60803.58230982354</v>
+        <v>-59969.20470387687</v>
       </c>
       <c r="D94">
-        <v>22083.14404591786</v>
+        <v>22917.52165186452</v>
       </c>
       <c r="E94">
         <v>78812.25857776162</v>
@@ -8995,37 +8995,37 @@
         <v>2303</v>
       </c>
       <c r="M94">
-        <v>22251.38143427003</v>
+        <v>21400.89417071261</v>
       </c>
       <c r="N94">
-        <v>-19948.38143427003</v>
+        <v>-19097.89417071261</v>
       </c>
       <c r="O94">
-        <v>-4987.095358567507</v>
+        <v>-4774.473542678154</v>
       </c>
       <c r="P94">
-        <v>-14961.28607570252</v>
+        <v>-14323.42062803446</v>
       </c>
       <c r="Q94">
-        <v>-14361.28607570252</v>
+        <v>-13723.42062803446</v>
       </c>
       <c r="R94">
         <v>11.50000000000001</v>
       </c>
       <c r="S94">
-        <v>0.8037091392717087</v>
+        <v>0.8027697950321541</v>
       </c>
       <c r="T94">
-        <v>11.72144111309189</v>
+        <v>11.71008198390413</v>
       </c>
       <c r="U94">
-        <v>0.2616309777667576</v>
+        <v>0.2516309777667576</v>
       </c>
       <c r="V94">
-        <v>0.02587479800751921</v>
+        <v>0.02690308149777783</v>
       </c>
       <c r="W94">
-        <v>0.254861329064533</v>
+        <v>0.244861329064533</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.1034991920300768</v>
+        <v>0.1076123259911114</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9044,13 +9044,13 @@
         <v>0.93</v>
       </c>
       <c r="B95">
-        <v>0.3009274636587746</v>
+        <v>0.2915523161196102</v>
       </c>
       <c r="C95">
-        <v>-61914.84245144053</v>
+        <v>-61085.5941337393</v>
       </c>
       <c r="D95">
-        <v>21896.32658208067</v>
+        <v>22725.57489978191</v>
       </c>
       <c r="E95">
         <v>79736.70125554143</v>
@@ -9077,37 +9077,37 @@
         <v>2303</v>
       </c>
       <c r="M95">
-        <v>22493.24427594688</v>
+        <v>21633.51258561166</v>
       </c>
       <c r="N95">
-        <v>-20190.24427594688</v>
+        <v>-19330.51258561166</v>
       </c>
       <c r="O95">
-        <v>-5047.56106898672</v>
+        <v>-4832.628146402916</v>
       </c>
       <c r="P95">
-        <v>-15142.68320696016</v>
+        <v>-14497.88443920875</v>
       </c>
       <c r="Q95">
-        <v>-14542.68320696016</v>
+        <v>-13897.88443920875</v>
       </c>
       <c r="R95">
         <v>13.2857142857143</v>
       </c>
       <c r="S95">
-        <v>0.9119818734533814</v>
+        <v>0.9109083371796047</v>
       </c>
       <c r="T95">
-        <v>13.39593270067644</v>
+        <v>13.38295083874758</v>
       </c>
       <c r="U95">
-        <v>0.2616309777667576</v>
+        <v>0.2516309777667576</v>
       </c>
       <c r="V95">
-        <v>0.02559657437302975</v>
+        <v>0.02661380105156517</v>
       </c>
       <c r="W95">
-        <v>0.2549341209860623</v>
+        <v>0.2449341209860623</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.102386297492119</v>
+        <v>0.1064552042062606</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9126,13 +9126,13 @@
         <v>0.9400000000000001</v>
       </c>
       <c r="B96">
-        <v>0.3030857734364422</v>
+        <v>0.2936106258972778</v>
       </c>
       <c r="C96">
-        <v>-63022.96825761834</v>
+        <v>-62198.79495233719</v>
       </c>
       <c r="D96">
-        <v>21712.64345368266</v>
+        <v>22536.8167589638</v>
       </c>
       <c r="E96">
         <v>80661.14393332122</v>
@@ -9159,37 +9159,37 @@
         <v>2303</v>
       </c>
       <c r="M96">
-        <v>22735.10711762372</v>
+        <v>21866.13100051072</v>
       </c>
       <c r="N96">
-        <v>-20432.10711762372</v>
+        <v>-19563.13100051072</v>
       </c>
       <c r="O96">
-        <v>-5108.026779405931</v>
+        <v>-4890.782750127679</v>
       </c>
       <c r="P96">
-        <v>-15324.08033821779</v>
+        <v>-14672.34825038304</v>
       </c>
       <c r="Q96">
-        <v>-14724.08033821779</v>
+        <v>-14072.34825038304</v>
       </c>
       <c r="R96">
         <v>15.66666666666668</v>
       </c>
       <c r="S96">
-        <v>1.056345519028945</v>
+        <v>1.055093060042873</v>
       </c>
       <c r="T96">
-        <v>15.62858815078919</v>
+        <v>15.61344264520552</v>
       </c>
       <c r="U96">
-        <v>0.2616309777667576</v>
+        <v>0.2516309777667576</v>
       </c>
       <c r="V96">
-        <v>0.02532427039033795</v>
+        <v>0.02633067550846341</v>
       </c>
       <c r="W96">
-        <v>0.2550053641433037</v>
+        <v>0.2450053641433037</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.1012970815613518</v>
+        <v>0.1053227020338536</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9208,13 +9208,13 @@
         <v>0.9500000000000001</v>
       </c>
       <c r="B97">
-        <v>0.3052440832141098</v>
+        <v>0.2956689356749454</v>
       </c>
       <c r="C97">
-        <v>-64128.03795176536</v>
+        <v>-63308.88595877848</v>
       </c>
       <c r="D97">
-        <v>21532.01643731544</v>
+        <v>22351.16843030232</v>
       </c>
       <c r="E97">
         <v>81585.58661110103</v>
@@ -9241,37 +9241,37 @@
         <v>2303</v>
       </c>
       <c r="M97">
-        <v>22976.96995930058</v>
+        <v>22098.74941540977</v>
       </c>
       <c r="N97">
-        <v>-20673.96995930058</v>
+        <v>-19795.74941540977</v>
       </c>
       <c r="O97">
-        <v>-5168.492489825144</v>
+        <v>-4948.937353852441</v>
       </c>
       <c r="P97">
-        <v>-15505.47746947543</v>
+        <v>-14846.81206155732</v>
       </c>
       <c r="Q97">
-        <v>-14905.47746947543</v>
+        <v>-14246.81206155732</v>
       </c>
       <c r="R97">
         <v>19.00000000000003</v>
       </c>
       <c r="S97">
-        <v>1.258454622834735</v>
+        <v>1.256951672051448</v>
       </c>
       <c r="T97">
-        <v>18.75430578094703</v>
+        <v>18.73613117424663</v>
       </c>
       <c r="U97">
-        <v>0.2616309777667576</v>
+        <v>0.2516309777667576</v>
       </c>
       <c r="V97">
-        <v>0.02505769912307123</v>
+        <v>0.02605351050311116</v>
       </c>
       <c r="W97">
-        <v>0.2550751074446033</v>
+        <v>0.2450751074446032</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.1002307964922849</v>
+        <v>0.1042140420124447</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9290,13 +9290,13 @@
         <v>0.96</v>
       </c>
       <c r="B98">
-        <v>0.3074023929917773</v>
+        <v>0.2977272454526129</v>
       </c>
       <c r="C98">
-        <v>-65230.12717580979</v>
+        <v>-64415.94337693592</v>
       </c>
       <c r="D98">
-        <v>21354.3698910508</v>
+        <v>22168.55368992467</v>
       </c>
       <c r="E98">
         <v>82510.0292888808</v>
@@ -9323,37 +9323,37 @@
         <v>2303</v>
       </c>
       <c r="M98">
-        <v>23218.83280097742</v>
+        <v>22331.36783030881</v>
       </c>
       <c r="N98">
-        <v>-20915.83280097742</v>
+        <v>-20028.36783030881</v>
       </c>
       <c r="O98">
-        <v>-5228.958200244355</v>
+        <v>-5007.091957577203</v>
       </c>
       <c r="P98">
-        <v>-15686.87460073306</v>
+        <v>-15021.27587273161</v>
       </c>
       <c r="Q98">
-        <v>-15086.87460073306</v>
+        <v>-14421.27587273161</v>
       </c>
       <c r="R98">
         <v>23.99999999999998</v>
       </c>
       <c r="S98">
-        <v>1.561618278543415</v>
+        <v>1.559739590064306</v>
       </c>
       <c r="T98">
-        <v>23.44288222618374</v>
+        <v>23.42016396780823</v>
       </c>
       <c r="U98">
-        <v>0.2616309777667576</v>
+        <v>0.2516309777667576</v>
       </c>
       <c r="V98">
-        <v>0.02479668142387257</v>
+        <v>0.02578211976870376</v>
       </c>
       <c r="W98">
-        <v>0.255143397760459</v>
+        <v>0.245143397760459</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.09918672569549025</v>
+        <v>0.103128479074815</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9372,13 +9372,13 @@
         <v>0.97</v>
       </c>
       <c r="B99">
-        <v>0.3095607027694449</v>
+        <v>0.2997855552302805</v>
       </c>
       <c r="C99">
-        <v>-66329.30909581884</v>
+        <v>-65520.04095979624</v>
       </c>
       <c r="D99">
-        <v>21179.63064882155</v>
+        <v>21988.89878484415</v>
       </c>
       <c r="E99">
         <v>83434.47196666061</v>
@@ -9405,37 +9405,37 @@
         <v>2303</v>
       </c>
       <c r="M99">
-        <v>23460.69564265427</v>
+        <v>22563.98624520786</v>
       </c>
       <c r="N99">
-        <v>-21157.69564265427</v>
+        <v>-20260.98624520786</v>
       </c>
       <c r="O99">
-        <v>-5289.423910663567</v>
+        <v>-5065.246561301966</v>
       </c>
       <c r="P99">
-        <v>-15868.2717319907</v>
+        <v>-15195.7396839059</v>
       </c>
       <c r="Q99">
-        <v>-15268.2717319907</v>
+        <v>-14595.7396839059</v>
       </c>
       <c r="R99">
         <v>32.33333333333331</v>
       </c>
       <c r="S99">
-        <v>2.066891038057888</v>
+        <v>2.064386120085741</v>
       </c>
       <c r="T99">
-        <v>31.25717630157832</v>
+        <v>31.22688529041098</v>
       </c>
       <c r="U99">
-        <v>0.2616309777667576</v>
+        <v>0.2516309777667576</v>
       </c>
       <c r="V99">
-        <v>0.02454104553290481</v>
+        <v>0.02551632471954186</v>
       </c>
       <c r="W99">
-        <v>0.2552102800285652</v>
+        <v>0.2452102800285652</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.09816418213161926</v>
+        <v>0.1020652988781675</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9454,13 +9454,13 @@
         <v>0.98</v>
       </c>
       <c r="B100">
-        <v>0.3117190125471124</v>
+        <v>0.3018438650079481</v>
       </c>
       <c r="C100">
-        <v>-67425.65450247418</v>
+        <v>-66621.25008877604</v>
       </c>
       <c r="D100">
-        <v>21007.72791994601</v>
+        <v>21812.13233364415</v>
       </c>
       <c r="E100">
         <v>84358.9146444404</v>
@@ -9487,37 +9487,37 @@
         <v>2303</v>
       </c>
       <c r="M100">
-        <v>23702.55848433112</v>
+        <v>22796.60466010691</v>
       </c>
       <c r="N100">
-        <v>-21399.55848433112</v>
+        <v>-20493.60466010691</v>
       </c>
       <c r="O100">
-        <v>-5349.889621082779</v>
+        <v>-5123.401165026728</v>
       </c>
       <c r="P100">
-        <v>-16049.66886324834</v>
+        <v>-15370.20349508019</v>
       </c>
       <c r="Q100">
-        <v>-15449.66886324834</v>
+        <v>-14770.20349508019</v>
       </c>
       <c r="R100">
         <v>48.99999999999996</v>
       </c>
       <c r="S100">
-        <v>3.077436557086831</v>
+        <v>3.073679180128612</v>
       </c>
       <c r="T100">
-        <v>46.88576445236748</v>
+        <v>46.84032793561646</v>
       </c>
       <c r="U100">
-        <v>0.2616309777667576</v>
+        <v>0.2516309777667576</v>
       </c>
       <c r="V100">
-        <v>0.0242906267009364</v>
+        <v>0.02525595405913838</v>
       </c>
       <c r="W100">
-        <v>0.2552757973524243</v>
+        <v>0.2452757973524243</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,7 +9525,7 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.09716250680374561</v>
+        <v>0.1010238162365535</v>
       </c>
       <c r="Z100">
         <v>0</v>
@@ -9536,13 +9536,13 @@
         <v>0.99</v>
       </c>
       <c r="B101">
-        <v>0.3138773223247801</v>
+        <v>0.3039021747856157</v>
       </c>
       <c r="C101">
-        <v>-68519.2319066941</v>
+        <v>-67719.63986828565</v>
       </c>
       <c r="D101">
-        <v>20838.59319350589</v>
+        <v>21638.18523191434</v>
       </c>
       <c r="E101">
         <v>85283.35732222021</v>
@@ -9569,37 +9569,37 @@
         <v>2303</v>
       </c>
       <c r="M101">
-        <v>23944.42132600797</v>
+        <v>23029.22307500596</v>
       </c>
       <c r="N101">
-        <v>-21641.42132600797</v>
+        <v>-20726.22307500596</v>
       </c>
       <c r="O101">
-        <v>-5410.355331501992</v>
+        <v>-5181.555768751491</v>
       </c>
       <c r="P101">
-        <v>-16231.06599450597</v>
+        <v>-15544.66730625447</v>
       </c>
       <c r="Q101">
-        <v>-15631.06599450597</v>
+        <v>-14944.66730625447</v>
       </c>
       <c r="R101">
         <v>98.99999999999991</v>
       </c>
       <c r="S101">
-        <v>6.109073114173661</v>
+        <v>6.101558360257224</v>
       </c>
       <c r="T101">
-        <v>93.77152890473495</v>
+        <v>93.68065587123291</v>
       </c>
       <c r="U101">
-        <v>0.2616309777667576</v>
+        <v>0.2516309777667576</v>
       </c>
       <c r="V101">
-        <v>0.02404526683527037</v>
+        <v>0.02500084341207637</v>
       </c>
       <c r="W101">
-        <v>0.2553399910939832</v>
+        <v>0.2453399910939832</v>
       </c>
       <c r="X101" t="inlineStr">
         <is>
@@ -9607,7 +9607,7 @@
         </is>
       </c>
       <c r="Y101">
-        <v>0.09618106734108145</v>
+        <v>0.1000033736483055</v>
       </c>
       <c r="Z101">
         <v>0</v>

--- a/research/traditional_assets/database/data/uruguay/uruguay_retail_general.xlsx
+++ b/research/traditional_assets/database/data/uruguay/uruguay_retail_general.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1078944736735083</v>
+        <v>0.1077772198225752</v>
       </c>
       <c r="C2">
-        <v>92103.38022871723</v>
+        <v>91349.09641285871</v>
       </c>
       <c r="D2">
-        <v>89941.38022871723</v>
+        <v>90111.5390906385</v>
       </c>
       <c r="E2">
-        <v>-6236.467777979779</v>
+        <v>-5312.025100199981</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>924.4426777797978</v>
       </c>
       <c r="G2">
         <v>2162</v>
@@ -1451,28 +1451,28 @@
         <v>2303</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>61.13429817089765</v>
       </c>
       <c r="N2">
-        <v>2303</v>
+        <v>2241.865701829102</v>
       </c>
       <c r="O2">
-        <v>575.75</v>
+        <v>560.4664254572756</v>
       </c>
       <c r="P2">
-        <v>1727.25</v>
+        <v>1681.399276371827</v>
       </c>
       <c r="Q2">
-        <v>2327.25</v>
+        <v>2281.399276371827</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1078944736735083</v>
+        <v>0.1083648863528531</v>
       </c>
       <c r="T2">
-        <v>0.960581759320096</v>
+        <v>0.9678588938603998</v>
       </c>
       <c r="U2">
         <v>0.06613097776675758</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>37.67116117963908</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1077772198225752</v>
+        <v>0.1076599659716421</v>
       </c>
       <c r="C3">
-        <v>91349.09641285871</v>
+        <v>90595.45765981317</v>
       </c>
       <c r="D3">
-        <v>90111.5390906385</v>
+        <v>90282.34301537277</v>
       </c>
       <c r="E3">
-        <v>-5312.025100199981</v>
+        <v>-4387.582422420184</v>
       </c>
       <c r="F3">
-        <v>924.4426777797978</v>
+        <v>1848.885355559596</v>
       </c>
       <c r="G3">
         <v>2162</v>
@@ -1533,28 +1533,28 @@
         <v>2303</v>
       </c>
       <c r="M3">
-        <v>61.13429817089765</v>
+        <v>122.2685963417953</v>
       </c>
       <c r="N3">
-        <v>2241.865701829102</v>
+        <v>2180.731403658205</v>
       </c>
       <c r="O3">
-        <v>560.4664254572756</v>
+        <v>545.1828509145512</v>
       </c>
       <c r="P3">
-        <v>1681.399276371827</v>
+        <v>1635.548552743654</v>
       </c>
       <c r="Q3">
-        <v>2281.399276371827</v>
+        <v>2235.548552743654</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1083648863528531</v>
+        <v>0.10884489929096</v>
       </c>
       <c r="T3">
-        <v>0.9678588938603998</v>
+        <v>0.9752845413505058</v>
       </c>
       <c r="U3">
         <v>0.06613097776675758</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>37.67116117963908</v>
+        <v>18.83558058981954</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1076599659716421</v>
+        <v>0.107542712120709</v>
       </c>
       <c r="C4">
-        <v>90595.45765981317</v>
+        <v>89842.4676446427</v>
       </c>
       <c r="D4">
-        <v>90282.34301537277</v>
+        <v>90453.7956779821</v>
       </c>
       <c r="E4">
-        <v>-4387.582422420184</v>
+        <v>-3463.139744640386</v>
       </c>
       <c r="F4">
-        <v>1848.885355559596</v>
+        <v>2773.328033339393</v>
       </c>
       <c r="G4">
         <v>2162</v>
@@ -1615,28 +1615,28 @@
         <v>2303</v>
       </c>
       <c r="M4">
-        <v>122.2685963417953</v>
+        <v>183.4028945126929</v>
       </c>
       <c r="N4">
-        <v>2180.731403658205</v>
+        <v>2119.597105487307</v>
       </c>
       <c r="O4">
-        <v>545.1828509145512</v>
+        <v>529.8992763718268</v>
       </c>
       <c r="P4">
-        <v>1635.548552743654</v>
+        <v>1589.69782911548</v>
       </c>
       <c r="Q4">
-        <v>2235.548552743654</v>
+        <v>2189.69782911548</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.10884489929096</v>
+        <v>0.1093348094030484</v>
       </c>
       <c r="T4">
-        <v>0.9752845413505058</v>
+        <v>0.982863294974428</v>
       </c>
       <c r="U4">
         <v>0.06613097776675758</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>18.83558058981954</v>
+        <v>12.55705372654636</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.107542712120709</v>
+        <v>0.107425458269776</v>
       </c>
       <c r="C5">
-        <v>89842.4676446427</v>
+        <v>89090.13007037916</v>
       </c>
       <c r="D5">
-        <v>90453.7956779821</v>
+        <v>90625.90078149835</v>
       </c>
       <c r="E5">
-        <v>-3463.139744640386</v>
+        <v>-2538.697066860588</v>
       </c>
       <c r="F5">
-        <v>2773.328033339393</v>
+        <v>3697.770711119191</v>
       </c>
       <c r="G5">
         <v>2162</v>
@@ -1697,28 +1697,28 @@
         <v>2303</v>
       </c>
       <c r="M5">
-        <v>183.4028945126929</v>
+        <v>244.5371926835906</v>
       </c>
       <c r="N5">
-        <v>2119.597105487307</v>
+        <v>2058.462807316409</v>
       </c>
       <c r="O5">
-        <v>529.8992763718268</v>
+        <v>514.6157018291024</v>
       </c>
       <c r="P5">
-        <v>1589.69782911548</v>
+        <v>1543.847105487307</v>
       </c>
       <c r="Q5">
-        <v>2189.69782911548</v>
+        <v>2143.847105487307</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1093348094030484</v>
+        <v>0.1098349259758054</v>
       </c>
       <c r="T5">
-        <v>0.982863294974428</v>
+        <v>0.990599939298849</v>
       </c>
       <c r="U5">
         <v>0.06613097776675758</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>12.55705372654636</v>
+        <v>9.41779029490977</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.107425458269776</v>
+        <v>0.1073644544188429</v>
       </c>
       <c r="C6">
-        <v>89090.13007037916</v>
+        <v>88255.48805751454</v>
       </c>
       <c r="D6">
-        <v>90625.90078149835</v>
+        <v>90715.70144641353</v>
       </c>
       <c r="E6">
-        <v>-2538.697066860588</v>
+        <v>-1614.25438908079</v>
       </c>
       <c r="F6">
-        <v>3697.770711119191</v>
+        <v>4622.213388898989</v>
       </c>
       <c r="G6">
         <v>2162</v>
@@ -1779,45 +1779,45 @@
         <v>2303</v>
       </c>
       <c r="M6">
-        <v>244.5371926835906</v>
+        <v>312.6048109378368</v>
       </c>
       <c r="N6">
-        <v>2058.462807316409</v>
+        <v>1990.395189062163</v>
       </c>
       <c r="O6">
-        <v>514.6157018291024</v>
+        <v>497.5987972655408</v>
       </c>
       <c r="P6">
-        <v>1543.847105487307</v>
+        <v>1492.796391796623</v>
       </c>
       <c r="Q6">
-        <v>2143.847105487307</v>
+        <v>2092.796391796623</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1098349259758054</v>
+        <v>0.1103455713185152</v>
       </c>
       <c r="T6">
-        <v>0.990599939298849</v>
+        <v>0.9984994603458893</v>
       </c>
       <c r="U6">
-        <v>0.06613097776675758</v>
+        <v>0.06763097776675758</v>
       </c>
       <c r="V6">
         <v>0.25</v>
       </c>
       <c r="W6">
-        <v>0.04959823332506819</v>
+        <v>0.05072323332506819</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y6">
-        <v>9.41779029490977</v>
+        <v>7.367129101726988</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1073644544188429</v>
+        <v>0.1073349505679098</v>
       </c>
       <c r="C7">
-        <v>88255.48805751454</v>
+        <v>87374.54037742411</v>
       </c>
       <c r="D7">
-        <v>90715.70144641353</v>
+        <v>90759.1964441029</v>
       </c>
       <c r="E7">
-        <v>-1614.25438908079</v>
+        <v>-689.8117113009921</v>
       </c>
       <c r="F7">
-        <v>4622.213388898989</v>
+        <v>5546.656066678787</v>
       </c>
       <c r="G7">
         <v>2162</v>
@@ -1861,45 +1861,45 @@
         <v>2303</v>
       </c>
       <c r="M7">
-        <v>312.6048109378368</v>
+        <v>384.555088438758</v>
       </c>
       <c r="N7">
-        <v>1990.395189062163</v>
+        <v>1918.444911561242</v>
       </c>
       <c r="O7">
-        <v>497.5987972655408</v>
+        <v>479.6112278903105</v>
       </c>
       <c r="P7">
-        <v>1492.796391796623</v>
+        <v>1438.833683670931</v>
       </c>
       <c r="Q7">
-        <v>2092.796391796623</v>
+        <v>2038.833683670931</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1103455713185152</v>
+        <v>0.1108670814557507</v>
       </c>
       <c r="T7">
-        <v>0.9984994603458893</v>
+        <v>1.006567056308824</v>
       </c>
       <c r="U7">
-        <v>0.06763097776675758</v>
+        <v>0.06933097776675758</v>
       </c>
       <c r="V7">
         <v>0.25</v>
       </c>
       <c r="W7">
-        <v>0.05072323332506819</v>
+        <v>0.05199823332506819</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y7">
-        <v>7.367129101726988</v>
+        <v>5.988738854944997</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1073349505679098</v>
+        <v>0.1072836967169767</v>
       </c>
       <c r="C8">
-        <v>87374.54037742411</v>
+        <v>86525.75610298928</v>
       </c>
       <c r="D8">
-        <v>90759.1964441029</v>
+        <v>90834.85484744786</v>
       </c>
       <c r="E8">
-        <v>-689.811711300993</v>
+        <v>234.630966478805</v>
       </c>
       <c r="F8">
-        <v>5546.656066678786</v>
+        <v>6471.098744458584</v>
       </c>
       <c r="G8">
         <v>2162</v>
@@ -1943,45 +1943,45 @@
         <v>2303</v>
       </c>
       <c r="M8">
-        <v>384.555088438758</v>
+        <v>453.8244821741179</v>
       </c>
       <c r="N8">
-        <v>1918.444911561242</v>
+        <v>1849.175517825882</v>
       </c>
       <c r="O8">
-        <v>479.6112278903105</v>
+        <v>462.2938794564705</v>
       </c>
       <c r="P8">
-        <v>1438.833683670931</v>
+        <v>1386.881638369412</v>
       </c>
       <c r="Q8">
-        <v>2038.833683670931</v>
+        <v>1986.881638369412</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1108670814557507</v>
+        <v>0.1113998068647547</v>
       </c>
       <c r="T8">
-        <v>1.006567056308824</v>
+        <v>1.014808148959134</v>
       </c>
       <c r="U8">
-        <v>0.06933097776675758</v>
+        <v>0.07013097776675759</v>
       </c>
       <c r="V8">
         <v>0.25</v>
       </c>
       <c r="W8">
-        <v>0.05199823332506819</v>
+        <v>0.05259823332506819</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y8">
-        <v>5.988738854944998</v>
+        <v>5.074649099949642</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1072836967169767</v>
+        <v>0.1071964428660436</v>
       </c>
       <c r="C9">
-        <v>86525.75610298928</v>
+        <v>85730.40381733007</v>
       </c>
       <c r="D9">
-        <v>90834.85484744787</v>
+        <v>90963.94523956845</v>
       </c>
       <c r="E9">
-        <v>234.6309664788059</v>
+        <v>1159.073644258603</v>
       </c>
       <c r="F9">
-        <v>6471.098744458585</v>
+        <v>7395.541422238382</v>
       </c>
       <c r="G9">
         <v>2162</v>
@@ -2025,28 +2025,28 @@
         <v>2303</v>
       </c>
       <c r="M9">
-        <v>453.824482174118</v>
+        <v>518.6565510561347</v>
       </c>
       <c r="N9">
-        <v>1849.175517825882</v>
+        <v>1784.343448943865</v>
       </c>
       <c r="O9">
-        <v>462.2938794564705</v>
+        <v>446.0858622359663</v>
       </c>
       <c r="P9">
-        <v>1386.881638369412</v>
+        <v>1338.257586707899</v>
       </c>
       <c r="Q9">
-        <v>1986.881638369412</v>
+        <v>1938.257586707899</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1113998068647547</v>
+        <v>0.111944113260911</v>
       </c>
       <c r="T9">
-        <v>1.014808148959134</v>
+        <v>1.023228395797494</v>
       </c>
       <c r="U9">
         <v>0.07013097776675759</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>5.074649099949641</v>
+        <v>4.440317962455937</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1071964428660436</v>
+        <v>0.1071766890151105</v>
       </c>
       <c r="C10">
-        <v>85730.40381733007</v>
+        <v>84835.23753492745</v>
       </c>
       <c r="D10">
-        <v>90963.94523956845</v>
+        <v>90993.22163494563</v>
       </c>
       <c r="E10">
-        <v>1159.073644258603</v>
+        <v>2083.516322038401</v>
       </c>
       <c r="F10">
-        <v>7395.541422238382</v>
+        <v>8319.98410001818</v>
       </c>
       <c r="G10">
         <v>2162</v>
@@ -2107,45 +2107,45 @@
         <v>2303</v>
       </c>
       <c r="M10">
-        <v>518.6565510561347</v>
+        <v>591.8086040381698</v>
       </c>
       <c r="N10">
-        <v>1784.343448943865</v>
+        <v>1711.19139596183</v>
       </c>
       <c r="O10">
-        <v>446.0858622359663</v>
+        <v>427.7978489904575</v>
       </c>
       <c r="P10">
-        <v>1338.257586707899</v>
+        <v>1283.393546971372</v>
       </c>
       <c r="Q10">
-        <v>1938.257586707899</v>
+        <v>1883.393546971372</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.111944113260911</v>
+        <v>0.1125003824350048</v>
       </c>
       <c r="T10">
-        <v>1.023228395797494</v>
+        <v>1.031833703005927</v>
       </c>
       <c r="U10">
-        <v>0.07013097776675759</v>
+        <v>0.07113097776675759</v>
       </c>
       <c r="V10">
         <v>0.25</v>
       </c>
       <c r="W10">
-        <v>0.05259823332506819</v>
+        <v>0.05334823332506819</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y10">
-        <v>4.440317962455937</v>
+        <v>3.891460827513524</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1071766890151105</v>
+        <v>0.1070969351641774</v>
       </c>
       <c r="C11">
-        <v>84835.23753492745</v>
+        <v>84029.18674435632</v>
       </c>
       <c r="D11">
-        <v>90993.22163494563</v>
+        <v>91111.61352215431</v>
       </c>
       <c r="E11">
-        <v>2083.516322038401</v>
+        <v>3007.958999818197</v>
       </c>
       <c r="F11">
-        <v>8319.98410001818</v>
+        <v>9244.426777797977</v>
       </c>
       <c r="G11">
         <v>2162</v>
@@ -2189,28 +2189,28 @@
         <v>2303</v>
       </c>
       <c r="M11">
-        <v>591.8086040381698</v>
+        <v>657.5651155979664</v>
       </c>
       <c r="N11">
-        <v>1711.19139596183</v>
+        <v>1645.434884402034</v>
       </c>
       <c r="O11">
-        <v>427.7978489904575</v>
+        <v>411.3587211005084</v>
       </c>
       <c r="P11">
-        <v>1283.393546971372</v>
+        <v>1234.076163301525</v>
       </c>
       <c r="Q11">
-        <v>1883.393546971372</v>
+        <v>1834.076163301525</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1125003824350048</v>
+        <v>0.1130690131463007</v>
       </c>
       <c r="T11">
-        <v>1.031833703005927</v>
+        <v>1.040630239263437</v>
       </c>
       <c r="U11">
         <v>0.07113097776675759</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>3.891460827513524</v>
+        <v>3.502314744762173</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1070969351641774</v>
+        <v>0.1070171813132443</v>
       </c>
       <c r="C12">
-        <v>84029.18674435632</v>
+        <v>83223.44443610085</v>
       </c>
       <c r="D12">
-        <v>91111.61352215431</v>
+        <v>91230.31389167863</v>
       </c>
       <c r="E12">
-        <v>3007.958999818199</v>
+        <v>3932.401677597997</v>
       </c>
       <c r="F12">
-        <v>9244.426777797979</v>
+        <v>10168.86945557778</v>
       </c>
       <c r="G12">
         <v>2162</v>
@@ -2271,28 +2271,28 @@
         <v>2303</v>
       </c>
       <c r="M12">
-        <v>657.5651155979665</v>
+        <v>723.3216271577631</v>
       </c>
       <c r="N12">
-        <v>1645.434884402034</v>
+        <v>1579.678372842237</v>
       </c>
       <c r="O12">
-        <v>411.3587211005084</v>
+        <v>394.9195932105592</v>
       </c>
       <c r="P12">
-        <v>1234.076163301525</v>
+        <v>1184.758779631678</v>
       </c>
       <c r="Q12">
-        <v>1834.076163301525</v>
+        <v>1784.758779631678</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1130690131463007</v>
+        <v>0.1136504220758279</v>
       </c>
       <c r="T12">
-        <v>1.040630239263437</v>
+        <v>1.049624450493026</v>
       </c>
       <c r="U12">
         <v>0.07113097776675759</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>3.502314744762172</v>
+        <v>3.183922495238338</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1070171813132443</v>
+        <v>0.1071624274623112</v>
       </c>
       <c r="C13">
-        <v>83223.44443610085</v>
+        <v>82083.057697453</v>
       </c>
       <c r="D13">
-        <v>91230.31389167863</v>
+        <v>91014.36983081057</v>
       </c>
       <c r="E13">
-        <v>3932.401677597997</v>
+        <v>4856.844355377793</v>
       </c>
       <c r="F13">
-        <v>10168.86945557778</v>
+        <v>11093.31213335757</v>
       </c>
       <c r="G13">
         <v>2162</v>
@@ -2353,45 +2353,45 @@
         <v>2303</v>
       </c>
       <c r="M13">
-        <v>723.3216271577631</v>
+        <v>816.8114190509534</v>
       </c>
       <c r="N13">
-        <v>1579.678372842237</v>
+        <v>1486.188580949047</v>
       </c>
       <c r="O13">
-        <v>394.9195932105592</v>
+        <v>371.5471452372616</v>
       </c>
       <c r="P13">
-        <v>1184.758779631678</v>
+        <v>1114.641435711785</v>
       </c>
       <c r="Q13">
-        <v>1784.758779631678</v>
+        <v>1714.641435711785</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1136504220758279</v>
+        <v>0.1142450448446626</v>
       </c>
       <c r="T13">
-        <v>1.049624450493026</v>
+        <v>1.058823075614197</v>
       </c>
       <c r="U13">
-        <v>0.07113097776675759</v>
+        <v>0.07363097776675757</v>
       </c>
       <c r="V13">
         <v>0.25</v>
       </c>
       <c r="W13">
-        <v>0.05334823332506819</v>
+        <v>0.05522323332506818</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y13">
-        <v>3.183922495238338</v>
+        <v>2.819500249734311</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1071624274623112</v>
+        <v>0.1071014236113782</v>
       </c>
       <c r="C14">
-        <v>82083.057697453</v>
+        <v>81249.18758263887</v>
       </c>
       <c r="D14">
-        <v>91014.36983081057</v>
+        <v>91104.94239377625</v>
       </c>
       <c r="E14">
-        <v>4856.844355377793</v>
+        <v>5781.287033157593</v>
       </c>
       <c r="F14">
-        <v>11093.31213335757</v>
+        <v>12017.75481113737</v>
       </c>
       <c r="G14">
         <v>2162</v>
@@ -2435,28 +2435,28 @@
         <v>2303</v>
       </c>
       <c r="M14">
-        <v>816.8114190509534</v>
+        <v>884.8790373051997</v>
       </c>
       <c r="N14">
-        <v>1486.188580949047</v>
+        <v>1418.1209626948</v>
       </c>
       <c r="O14">
-        <v>371.5471452372616</v>
+        <v>354.5302406737001</v>
       </c>
       <c r="P14">
-        <v>1114.641435711785</v>
+        <v>1063.5907220211</v>
       </c>
       <c r="Q14">
-        <v>1714.641435711785</v>
+        <v>1663.5907220211</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1142450448446626</v>
+        <v>0.114853337102436</v>
       </c>
       <c r="T14">
-        <v>1.058823075614197</v>
+        <v>1.068233163381831</v>
       </c>
       <c r="U14">
         <v>0.07363097776675757</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>2.819500249734311</v>
+        <v>2.602615615139364</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1071014236113782</v>
+        <v>0.1074079197604451</v>
       </c>
       <c r="C15">
-        <v>81249.18758263887</v>
+        <v>79871.50262508025</v>
       </c>
       <c r="D15">
-        <v>91104.94239377625</v>
+        <v>90651.70011399742</v>
       </c>
       <c r="E15">
-        <v>5781.287033157593</v>
+        <v>6705.729710937391</v>
       </c>
       <c r="F15">
-        <v>12017.75481113737</v>
+        <v>12942.19748891717</v>
       </c>
       <c r="G15">
         <v>2162</v>
@@ -2517,45 +2517,45 @@
         <v>2303</v>
       </c>
       <c r="M15">
-        <v>884.8790373051997</v>
+        <v>998.2443467706561</v>
       </c>
       <c r="N15">
-        <v>1418.1209626948</v>
+        <v>1304.755653229344</v>
       </c>
       <c r="O15">
-        <v>354.5302406737001</v>
+        <v>326.188913307336</v>
       </c>
       <c r="P15">
-        <v>1063.5907220211</v>
+        <v>978.5667399220079</v>
       </c>
       <c r="Q15">
-        <v>1663.5907220211</v>
+        <v>1578.566739922008</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.114853337102436</v>
+        <v>0.1154757756917855</v>
       </c>
       <c r="T15">
-        <v>1.068233163381831</v>
+        <v>1.077862090399875</v>
       </c>
       <c r="U15">
-        <v>0.07363097776675757</v>
+        <v>0.07713097776675758</v>
       </c>
       <c r="V15">
         <v>0.25</v>
       </c>
       <c r="W15">
-        <v>0.05522323332506818</v>
+        <v>0.05784823332506818</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y15">
-        <v>2.602615615139364</v>
+        <v>2.307050380450697</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1074079197604451</v>
+        <v>0.107688165909512</v>
       </c>
       <c r="C16">
-        <v>79871.50262508025</v>
+        <v>78536.5648309892</v>
       </c>
       <c r="D16">
-        <v>90651.70011399742</v>
+        <v>90241.20499768616</v>
       </c>
       <c r="E16">
-        <v>6705.729710937391</v>
+        <v>7630.172388717189</v>
       </c>
       <c r="F16">
-        <v>12942.19748891717</v>
+        <v>13866.64016669697</v>
       </c>
       <c r="G16">
         <v>2162</v>
@@ -2599,45 +2599,45 @@
         <v>2303</v>
       </c>
       <c r="M16">
-        <v>998.2443467706561</v>
+        <v>1108.374106863883</v>
       </c>
       <c r="N16">
-        <v>1304.755653229344</v>
+        <v>1194.625893136117</v>
       </c>
       <c r="O16">
-        <v>326.188913307336</v>
+        <v>298.6564732840292</v>
       </c>
       <c r="P16">
-        <v>978.5667399220079</v>
+        <v>895.9694198520876</v>
       </c>
       <c r="Q16">
-        <v>1578.566739922008</v>
+        <v>1495.969419852088</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1154757756917855</v>
+        <v>0.1161128598950021</v>
       </c>
       <c r="T16">
-        <v>1.077862090399875</v>
+        <v>1.087717580406579</v>
       </c>
       <c r="U16">
-        <v>0.07713097776675758</v>
+        <v>0.07993097776675759</v>
       </c>
       <c r="V16">
         <v>0.25</v>
       </c>
       <c r="W16">
-        <v>0.05784823332506818</v>
+        <v>0.05994823332506819</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y16">
-        <v>2.307050380450697</v>
+        <v>2.077818297755332</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.107688165909512</v>
+        <v>0.1086104120585789</v>
       </c>
       <c r="C17">
-        <v>78536.5648309892</v>
+        <v>76287.10929198733</v>
       </c>
       <c r="D17">
-        <v>90241.20499768616</v>
+        <v>88916.1921364641</v>
       </c>
       <c r="E17">
-        <v>7630.172388717187</v>
+        <v>8554.615066496986</v>
       </c>
       <c r="F17">
-        <v>13866.64016669697</v>
+        <v>14791.08284447676</v>
       </c>
       <c r="G17">
         <v>2162</v>
@@ -2681,45 +2681,45 @@
         <v>2303</v>
       </c>
       <c r="M17">
-        <v>1108.374106863883</v>
+        <v>1297.636160175061</v>
       </c>
       <c r="N17">
-        <v>1194.625893136117</v>
+        <v>1005.363839824939</v>
       </c>
       <c r="O17">
-        <v>298.6564732840292</v>
+        <v>251.3409599562348</v>
       </c>
       <c r="P17">
-        <v>895.9694198520876</v>
+        <v>754.0228798687044</v>
       </c>
       <c r="Q17">
-        <v>1495.969419852088</v>
+        <v>1354.022879868704</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1161128598950021</v>
+        <v>0.1167651127697238</v>
       </c>
       <c r="T17">
-        <v>1.087717580406579</v>
+        <v>1.097807724937253</v>
       </c>
       <c r="U17">
-        <v>0.07993097776675759</v>
+        <v>0.08773097776675759</v>
       </c>
       <c r="V17">
         <v>0.25</v>
       </c>
       <c r="W17">
-        <v>0.05994823332506819</v>
+        <v>0.06579823332506819</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y17">
-        <v>2.077818297755332</v>
+        <v>1.774765585824387</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1086104120585789</v>
+        <v>0.1091524082076458</v>
       </c>
       <c r="C18">
-        <v>76287.10929198733</v>
+        <v>74601.96571757075</v>
       </c>
       <c r="D18">
-        <v>88916.1921364641</v>
+        <v>88155.49123982732</v>
       </c>
       <c r="E18">
-        <v>8554.615066496986</v>
+        <v>9479.057744276786</v>
       </c>
       <c r="F18">
-        <v>14791.08284447676</v>
+        <v>15715.52552225656</v>
       </c>
       <c r="G18">
         <v>2162</v>
@@ -2763,45 +2763,45 @@
         <v>2303</v>
       </c>
       <c r="M18">
-        <v>1297.636160175061</v>
+        <v>1440.028969722802</v>
       </c>
       <c r="N18">
-        <v>1005.363839824939</v>
+        <v>862.9710302771975</v>
       </c>
       <c r="O18">
-        <v>251.3409599562348</v>
+        <v>215.7427575692994</v>
       </c>
       <c r="P18">
-        <v>754.0228798687044</v>
+        <v>647.2282727078982</v>
       </c>
       <c r="Q18">
-        <v>1354.022879868704</v>
+        <v>1247.228272707898</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1167651127697238</v>
+        <v>0.1174330825811858</v>
       </c>
       <c r="T18">
-        <v>1.097807724937253</v>
+        <v>1.108141005480713</v>
       </c>
       <c r="U18">
-        <v>0.08773097776675759</v>
+        <v>0.09163097776675758</v>
       </c>
       <c r="V18">
         <v>0.25</v>
       </c>
       <c r="W18">
-        <v>0.06579823332506819</v>
+        <v>0.06872323332506819</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y18">
-        <v>1.774765585824387</v>
+        <v>1.599273381592674</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1091524082076458</v>
+        <v>0.1092264043567127</v>
       </c>
       <c r="C19">
-        <v>74601.96571757075</v>
+        <v>73574.67680505622</v>
       </c>
       <c r="D19">
-        <v>88155.49123982732</v>
+        <v>88052.64500509259</v>
       </c>
       <c r="E19">
-        <v>9479.057744276786</v>
+        <v>10403.50042205658</v>
       </c>
       <c r="F19">
-        <v>15715.52552225656</v>
+        <v>16639.96820003636</v>
       </c>
       <c r="G19">
         <v>2162</v>
@@ -2845,28 +2845,28 @@
         <v>2303</v>
       </c>
       <c r="M19">
-        <v>1440.028969722802</v>
+        <v>1524.736556177085</v>
       </c>
       <c r="N19">
-        <v>862.9710302771975</v>
+        <v>778.2634438229152</v>
       </c>
       <c r="O19">
-        <v>215.7427575692994</v>
+        <v>194.5658609557288</v>
       </c>
       <c r="P19">
-        <v>647.2282727078982</v>
+        <v>583.6975828671864</v>
       </c>
       <c r="Q19">
-        <v>1247.228272707898</v>
+        <v>1183.697582867186</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1174330825811858</v>
+        <v>0.1181173443392688</v>
       </c>
       <c r="T19">
-        <v>1.108141005480713</v>
+        <v>1.118726317256941</v>
       </c>
       <c r="U19">
         <v>0.09163097776675758</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>1.599273381592674</v>
+        <v>1.510424860393081</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1092264043567127</v>
+        <v>0.1156294966694496</v>
       </c>
       <c r="C20">
-        <v>73574.67680505622</v>
+        <v>64576.1502338016</v>
       </c>
       <c r="D20">
-        <v>88052.64500509259</v>
+        <v>79978.56111161776</v>
       </c>
       <c r="E20">
-        <v>10403.50042205658</v>
+        <v>11327.94309983638</v>
       </c>
       <c r="F20">
-        <v>16639.96820003636</v>
+        <v>17564.41087781616</v>
       </c>
       <c r="G20">
         <v>2162</v>
@@ -2927,45 +2927,45 @@
         <v>2303</v>
       </c>
       <c r="M20">
-        <v>1524.736556177085</v>
+        <v>2361.200928201899</v>
       </c>
       <c r="N20">
-        <v>778.2634438229152</v>
+        <v>-58.20092820189893</v>
       </c>
       <c r="O20">
-        <v>194.5658609557288</v>
+        <v>-14.55023205047473</v>
       </c>
       <c r="P20">
-        <v>583.6975828671864</v>
+        <v>-43.6506961514242</v>
       </c>
       <c r="Q20">
-        <v>1183.697582867186</v>
+        <v>556.3493038485758</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1181173443392688</v>
+        <v>0.1189082564195213</v>
       </c>
       <c r="T20">
-        <v>1.118726317256941</v>
+        <v>1.130961475598264</v>
       </c>
       <c r="U20">
-        <v>0.09163097776675758</v>
+        <v>0.1344309777667576</v>
       </c>
       <c r="V20">
-        <v>0.25</v>
+        <v>0.2438377831904568</v>
       </c>
       <c r="W20">
-        <v>0.06872323332506819</v>
+        <v>0.1016516261559858</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y20">
-        <v>1.510424860393081</v>
+        <v>0.9753511327618273</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1156294966694496</v>
+        <v>0.1165158064471172</v>
       </c>
       <c r="C21">
-        <v>64576.1502338016</v>
+        <v>62649.30393116854</v>
       </c>
       <c r="D21">
-        <v>79978.56111161776</v>
+        <v>78976.1574867645</v>
       </c>
       <c r="E21">
-        <v>11327.94309983638</v>
+        <v>12252.38577761618</v>
       </c>
       <c r="F21">
-        <v>17564.41087781616</v>
+        <v>18488.85355559596</v>
       </c>
       <c r="G21">
         <v>2162</v>
@@ -3009,37 +3009,37 @@
         <v>2303</v>
       </c>
       <c r="M21">
-        <v>2361.200928201899</v>
+        <v>2485.474661265157</v>
       </c>
       <c r="N21">
-        <v>-58.20092820189893</v>
+        <v>-182.474661265157</v>
       </c>
       <c r="O21">
-        <v>-14.55023205047473</v>
+        <v>-45.61866531628925</v>
       </c>
       <c r="P21">
-        <v>-43.6506961514242</v>
+        <v>-136.8559959488678</v>
       </c>
       <c r="Q21">
-        <v>556.3493038485758</v>
+        <v>463.1440040511322</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1189082564195213</v>
+        <v>0.1198221096247654</v>
       </c>
       <c r="T21">
-        <v>1.130961475598264</v>
+        <v>1.145098494043242</v>
       </c>
       <c r="U21">
         <v>0.1344309777667576</v>
       </c>
       <c r="V21">
-        <v>0.2438377831904568</v>
+        <v>0.2316458940309339</v>
       </c>
       <c r="W21">
-        <v>0.1016516261559858</v>
+        <v>0.1032905937365244</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>0.9753511327618273</v>
+        <v>0.9265835761237358</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1165158064471172</v>
+        <v>0.1174021162247847</v>
       </c>
       <c r="C22">
-        <v>62649.30393116854</v>
+        <v>60747.27365858377</v>
       </c>
       <c r="D22">
-        <v>78976.1574867645</v>
+        <v>77998.56989195953</v>
       </c>
       <c r="E22">
-        <v>12252.38577761618</v>
+        <v>13176.82845539598</v>
       </c>
       <c r="F22">
-        <v>18488.85355559596</v>
+        <v>19413.29623337576</v>
       </c>
       <c r="G22">
         <v>2162</v>
@@ -3091,37 +3091,37 @@
         <v>2303</v>
       </c>
       <c r="M22">
-        <v>2485.474661265157</v>
+        <v>2609.748394328415</v>
       </c>
       <c r="N22">
-        <v>-182.474661265157</v>
+        <v>-306.7483943284151</v>
       </c>
       <c r="O22">
-        <v>-45.61866531628925</v>
+        <v>-76.68709858210377</v>
       </c>
       <c r="P22">
-        <v>-136.8559959488678</v>
+        <v>-230.0612957463113</v>
       </c>
       <c r="Q22">
-        <v>463.1440040511322</v>
+        <v>369.9387042536887</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1198221096247654</v>
+        <v>0.1207590983541928</v>
       </c>
       <c r="T22">
-        <v>1.145098494043242</v>
+        <v>1.159593411689359</v>
       </c>
       <c r="U22">
         <v>0.1344309777667576</v>
       </c>
       <c r="V22">
-        <v>0.2316458940309339</v>
+        <v>0.220615137172318</v>
       </c>
       <c r="W22">
-        <v>0.1032905937365244</v>
+        <v>0.1047734691665355</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>0.9265835761237358</v>
+        <v>0.882460548689272</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1174021162247847</v>
+        <v>0.1182884260024523</v>
       </c>
       <c r="C23">
-        <v>60747.27365858378</v>
+        <v>58869.14914562393</v>
       </c>
       <c r="D23">
-        <v>77998.56989195953</v>
+        <v>77044.88805677948</v>
       </c>
       <c r="E23">
-        <v>13176.82845539597</v>
+        <v>14101.27113317577</v>
       </c>
       <c r="F23">
-        <v>19413.29623337575</v>
+        <v>20337.73891115555</v>
       </c>
       <c r="G23">
         <v>2162</v>
@@ -3173,37 +3173,37 @@
         <v>2303</v>
       </c>
       <c r="M23">
-        <v>2609.748394328415</v>
+        <v>2734.022127391673</v>
       </c>
       <c r="N23">
-        <v>-306.7483943284146</v>
+        <v>-431.0221273916727</v>
       </c>
       <c r="O23">
-        <v>-76.68709858210366</v>
+        <v>-107.7555318479182</v>
       </c>
       <c r="P23">
-        <v>-230.061295746311</v>
+        <v>-323.2665955437545</v>
       </c>
       <c r="Q23">
-        <v>369.938704253689</v>
+        <v>276.7334044562455</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1207590983541928</v>
+        <v>0.1217201124356568</v>
       </c>
       <c r="T23">
-        <v>1.159593411689359</v>
+        <v>1.174459993890505</v>
       </c>
       <c r="U23">
         <v>0.1344309777667576</v>
       </c>
       <c r="V23">
-        <v>0.2206151371723181</v>
+        <v>0.2105871763917581</v>
       </c>
       <c r="W23">
-        <v>0.1047734691665355</v>
+        <v>0.1061215377392729</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>0.8824605486892723</v>
+        <v>0.8423487055670326</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1182884260024523</v>
+        <v>0.1191747357801199</v>
       </c>
       <c r="C24">
-        <v>58869.14914562393</v>
+        <v>57014.0641033025</v>
       </c>
       <c r="D24">
-        <v>77044.88805677948</v>
+        <v>76114.24569223785</v>
       </c>
       <c r="E24">
-        <v>14101.27113317577</v>
+        <v>15025.71381095557</v>
       </c>
       <c r="F24">
-        <v>20337.73891115555</v>
+        <v>21262.18158893535</v>
       </c>
       <c r="G24">
         <v>2162</v>
@@ -3255,37 +3255,37 @@
         <v>2303</v>
       </c>
       <c r="M24">
-        <v>2734.022127391673</v>
+        <v>2858.29586045493</v>
       </c>
       <c r="N24">
-        <v>-431.0221273916727</v>
+        <v>-555.2958604549303</v>
       </c>
       <c r="O24">
-        <v>-107.7555318479182</v>
+        <v>-138.8239651137326</v>
       </c>
       <c r="P24">
-        <v>-323.2665955437545</v>
+        <v>-416.4718953411978</v>
       </c>
       <c r="Q24">
-        <v>276.7334044562455</v>
+        <v>183.5281046588022</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1217201124356568</v>
+        <v>0.1227060879218342</v>
       </c>
       <c r="T24">
-        <v>1.174459993890505</v>
+        <v>1.189712721083888</v>
       </c>
       <c r="U24">
         <v>0.1344309777667576</v>
       </c>
       <c r="V24">
-        <v>0.2105871763917581</v>
+        <v>0.2014312122008121</v>
       </c>
       <c r="W24">
-        <v>0.1061215377392729</v>
+        <v>0.1073523829578592</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>0.8423487055670326</v>
+        <v>0.8057248488032486</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1191747357801199</v>
+        <v>0.1408806337021775</v>
       </c>
       <c r="C25">
-        <v>57014.0641033025</v>
+        <v>38713.54826445068</v>
       </c>
       <c r="D25">
-        <v>76114.24569223785</v>
+        <v>58738.17253116583</v>
       </c>
       <c r="E25">
-        <v>15025.71381095557</v>
+        <v>15950.15648873537</v>
       </c>
       <c r="F25">
-        <v>21262.18158893535</v>
+        <v>22186.62426671515</v>
       </c>
       <c r="G25">
         <v>2162</v>
@@ -3337,45 +3337,45 @@
         <v>2303</v>
       </c>
       <c r="M25">
-        <v>2858.29586045493</v>
+        <v>4806.310108242174</v>
       </c>
       <c r="N25">
-        <v>-555.2958604549303</v>
+        <v>-2503.310108242174</v>
       </c>
       <c r="O25">
-        <v>-138.8239651137326</v>
+        <v>-625.8275270605434</v>
       </c>
       <c r="P25">
-        <v>-416.4718953411978</v>
+        <v>-1877.48258118163</v>
       </c>
       <c r="Q25">
-        <v>183.5281046588022</v>
+        <v>-1277.48258118163</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1227060879218342</v>
+        <v>0.1251543103213188</v>
       </c>
       <c r="T25">
-        <v>1.189712721083888</v>
+        <v>1.22758594297589</v>
       </c>
       <c r="U25">
-        <v>0.1344309777667576</v>
+        <v>0.2166309777667576</v>
       </c>
       <c r="V25">
-        <v>0.2014312122008121</v>
+        <v>0.1197904394501442</v>
       </c>
       <c r="W25">
-        <v>0.1073523829578592</v>
+        <v>0.1906806577415633</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y25">
-        <v>0.8057248488032486</v>
+        <v>0.4791617578005767</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1408806337021775</v>
+        <v>0.1425889434798451</v>
       </c>
       <c r="C26">
-        <v>38713.54826445068</v>
+        <v>36752.38598988954</v>
       </c>
       <c r="D26">
-        <v>58738.17253116583</v>
+        <v>57701.45293438448</v>
       </c>
       <c r="E26">
-        <v>15950.15648873537</v>
+        <v>16874.59916651517</v>
       </c>
       <c r="F26">
-        <v>22186.62426671515</v>
+        <v>23111.06694449495</v>
       </c>
       <c r="G26">
         <v>2162</v>
@@ -3419,37 +3419,37 @@
         <v>2303</v>
       </c>
       <c r="M26">
-        <v>4806.310108242173</v>
+        <v>5006.573029418931</v>
       </c>
       <c r="N26">
-        <v>-2503.310108242173</v>
+        <v>-2703.573029418931</v>
       </c>
       <c r="O26">
-        <v>-625.8275270605432</v>
+        <v>-675.8932573547327</v>
       </c>
       <c r="P26">
-        <v>-1877.482581181629</v>
+        <v>-2027.679772064198</v>
       </c>
       <c r="Q26">
-        <v>-1277.482581181629</v>
+        <v>-1427.679772064198</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1251543103213188</v>
+        <v>0.1262123677922698</v>
       </c>
       <c r="T26">
-        <v>1.22758594297589</v>
+        <v>1.243953755548902</v>
       </c>
       <c r="U26">
         <v>0.2166309777667576</v>
       </c>
       <c r="V26">
-        <v>0.1197904394501442</v>
+        <v>0.1149988218721384</v>
       </c>
       <c r="W26">
-        <v>0.1906806577415633</v>
+        <v>0.1917186705425711</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>0.4791617578005768</v>
+        <v>0.4599952874885537</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1425889434798451</v>
+        <v>0.1442972532575126</v>
       </c>
       <c r="C27">
-        <v>36752.38598988954</v>
+        <v>34827.18488511357</v>
       </c>
       <c r="D27">
-        <v>57701.45293438448</v>
+        <v>56700.69450738832</v>
       </c>
       <c r="E27">
-        <v>16874.59916651517</v>
+        <v>17799.04184429497</v>
       </c>
       <c r="F27">
-        <v>23111.06694449495</v>
+        <v>24035.50962227475</v>
       </c>
       <c r="G27">
         <v>2162</v>
@@ -3501,37 +3501,37 @@
         <v>2303</v>
       </c>
       <c r="M27">
-        <v>5006.573029418931</v>
+        <v>5206.835950595688</v>
       </c>
       <c r="N27">
-        <v>-2703.573029418931</v>
+        <v>-2903.835950595688</v>
       </c>
       <c r="O27">
-        <v>-675.8932573547327</v>
+        <v>-725.9589876489219</v>
       </c>
       <c r="P27">
-        <v>-2027.679772064198</v>
+        <v>-2177.876962946766</v>
       </c>
       <c r="Q27">
-        <v>-1427.679772064198</v>
+        <v>-1577.876962946766</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1262123677922698</v>
+        <v>0.1272990214110842</v>
       </c>
       <c r="T27">
-        <v>1.243953755548902</v>
+        <v>1.260763941434698</v>
       </c>
       <c r="U27">
         <v>0.2166309777667576</v>
       </c>
       <c r="V27">
-        <v>0.1149988218721384</v>
+        <v>0.1105757902616716</v>
       </c>
       <c r="W27">
-        <v>0.1917186705425711</v>
+        <v>0.1926768362050398</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>0.4599952874885537</v>
+        <v>0.4423031610466862</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1442972532575126</v>
+        <v>0.1460055630351803</v>
       </c>
       <c r="C28">
-        <v>34827.18488511357</v>
+        <v>32936.10574630706</v>
       </c>
       <c r="D28">
-        <v>56700.69450738832</v>
+        <v>55734.05804636161</v>
       </c>
       <c r="E28">
-        <v>17799.04184429497</v>
+        <v>18723.48452207476</v>
       </c>
       <c r="F28">
-        <v>24035.50962227475</v>
+        <v>24959.95230005454</v>
       </c>
       <c r="G28">
         <v>2162</v>
@@ -3583,37 +3583,37 @@
         <v>2303</v>
       </c>
       <c r="M28">
-        <v>5206.835950595688</v>
+        <v>5407.098871772445</v>
       </c>
       <c r="N28">
-        <v>-2903.835950595688</v>
+        <v>-3104.098871772445</v>
       </c>
       <c r="O28">
-        <v>-725.9589876489219</v>
+        <v>-776.0247179431112</v>
       </c>
       <c r="P28">
-        <v>-2177.876962946766</v>
+        <v>-2328.074153829334</v>
       </c>
       <c r="Q28">
-        <v>-1577.876962946766</v>
+        <v>-1728.074153829334</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1272990214110842</v>
+        <v>0.128415446361921</v>
       </c>
       <c r="T28">
-        <v>1.260763941434698</v>
+        <v>1.278034680358461</v>
       </c>
       <c r="U28">
         <v>0.2166309777667576</v>
       </c>
       <c r="V28">
-        <v>0.1105757902616716</v>
+        <v>0.1064803906223504</v>
       </c>
       <c r="W28">
-        <v>0.1926768362050398</v>
+        <v>0.1935640266332515</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>0.4423031610466862</v>
+        <v>0.4259215624894015</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1460055630351803</v>
+        <v>0.1477138728128478</v>
       </c>
       <c r="C29">
-        <v>32936.10574630706</v>
+        <v>31077.43268671717</v>
       </c>
       <c r="D29">
-        <v>55734.05804636161</v>
+        <v>54799.82766455151</v>
       </c>
       <c r="E29">
-        <v>18723.48452207476</v>
+        <v>19647.92719985456</v>
       </c>
       <c r="F29">
-        <v>24959.95230005454</v>
+        <v>25884.39497783434</v>
       </c>
       <c r="G29">
         <v>2162</v>
@@ -3665,37 +3665,37 @@
         <v>2303</v>
       </c>
       <c r="M29">
-        <v>5407.098871772445</v>
+        <v>5607.361792949203</v>
       </c>
       <c r="N29">
-        <v>-3104.098871772445</v>
+        <v>-3304.361792949203</v>
       </c>
       <c r="O29">
-        <v>-776.0247179431112</v>
+        <v>-826.0904482373007</v>
       </c>
       <c r="P29">
-        <v>-2328.074153829334</v>
+        <v>-2478.271344711902</v>
       </c>
       <c r="Q29">
-        <v>-1728.074153829334</v>
+        <v>-1878.271344711902</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.128415446361921</v>
+        <v>0.1295628831169477</v>
       </c>
       <c r="T29">
-        <v>1.278034680358461</v>
+        <v>1.295785162030107</v>
       </c>
       <c r="U29">
         <v>0.2166309777667576</v>
       </c>
       <c r="V29">
-        <v>0.1064803906223504</v>
+        <v>0.102677519528695</v>
       </c>
       <c r="W29">
-        <v>0.1935640266332515</v>
+        <v>0.194387846316591</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>0.4259215624894015</v>
+        <v>0.41071007811478</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1477138728128478</v>
+        <v>0.1494221825905154</v>
       </c>
       <c r="C30">
-        <v>31077.43268671717</v>
+        <v>29249.56297166108</v>
       </c>
       <c r="D30">
-        <v>54799.82766455151</v>
+        <v>53896.40062727522</v>
       </c>
       <c r="E30">
-        <v>19647.92719985456</v>
+        <v>20572.36987763436</v>
       </c>
       <c r="F30">
-        <v>25884.39497783434</v>
+        <v>26808.83765561414</v>
       </c>
       <c r="G30">
         <v>2162</v>
@@ -3747,37 +3747,37 @@
         <v>2303</v>
       </c>
       <c r="M30">
-        <v>5607.361792949203</v>
+        <v>5807.62471412596</v>
       </c>
       <c r="N30">
-        <v>-3304.361792949203</v>
+        <v>-3504.62471412596</v>
       </c>
       <c r="O30">
-        <v>-826.0904482373007</v>
+        <v>-876.15617853149</v>
       </c>
       <c r="P30">
-        <v>-2478.271344711902</v>
+        <v>-2628.46853559447</v>
       </c>
       <c r="Q30">
-        <v>-1878.271344711902</v>
+        <v>-2028.46853559447</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1295628831169477</v>
+        <v>0.1307426420340878</v>
       </c>
       <c r="T30">
-        <v>1.295785162030107</v>
+        <v>1.314035657269967</v>
       </c>
       <c r="U30">
         <v>0.2166309777667576</v>
       </c>
       <c r="V30">
-        <v>0.102677519528695</v>
+        <v>0.09913691540701587</v>
       </c>
       <c r="W30">
-        <v>0.194387846316591</v>
+        <v>0.1951548508493554</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>0.41071007811478</v>
+        <v>0.3965476616280634</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1494221825905154</v>
+        <v>0.151130492368183</v>
       </c>
       <c r="C31">
-        <v>29249.5629716611</v>
+        <v>27450.99784270329</v>
       </c>
       <c r="D31">
-        <v>53896.40062727524</v>
+        <v>53022.27817609722</v>
       </c>
       <c r="E31">
-        <v>20572.36987763436</v>
+        <v>21496.81255541416</v>
       </c>
       <c r="F31">
-        <v>26808.83765561413</v>
+        <v>27733.28033339393</v>
       </c>
       <c r="G31">
         <v>2162</v>
@@ -3829,37 +3829,37 @@
         <v>2303</v>
       </c>
       <c r="M31">
-        <v>5807.624714125959</v>
+        <v>6007.887635302716</v>
       </c>
       <c r="N31">
-        <v>-3504.624714125959</v>
+        <v>-3704.887635302716</v>
       </c>
       <c r="O31">
-        <v>-876.1561785314898</v>
+        <v>-926.2219088256791</v>
       </c>
       <c r="P31">
-        <v>-2628.468535594469</v>
+        <v>-2778.665726477037</v>
       </c>
       <c r="Q31">
-        <v>-2028.468535594469</v>
+        <v>-2178.665726477037</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1307426420340878</v>
+        <v>0.1319561083488605</v>
       </c>
       <c r="T31">
-        <v>1.314035657269967</v>
+        <v>1.332807595230967</v>
       </c>
       <c r="U31">
         <v>0.2166309777667576</v>
       </c>
       <c r="V31">
-        <v>0.09913691540701589</v>
+        <v>0.09583235156011535</v>
       </c>
       <c r="W31">
-        <v>0.1951548508493554</v>
+        <v>0.1958707217466021</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>0.3965476616280635</v>
+        <v>0.3833294062404614</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.151130492368183</v>
+        <v>0.1528388021458505</v>
       </c>
       <c r="C32">
-        <v>27450.99784270329</v>
+        <v>25680.33422049425</v>
       </c>
       <c r="D32">
-        <v>53022.27817609722</v>
+        <v>52176.05723166798</v>
       </c>
       <c r="E32">
-        <v>21496.81255541416</v>
+        <v>22421.25523319396</v>
       </c>
       <c r="F32">
-        <v>27733.28033339393</v>
+        <v>28657.72301117373</v>
       </c>
       <c r="G32">
         <v>2162</v>
@@ -3911,37 +3911,37 @@
         <v>2303</v>
       </c>
       <c r="M32">
-        <v>6007.887635302716</v>
+        <v>6208.150556479474</v>
       </c>
       <c r="N32">
-        <v>-3704.887635302716</v>
+        <v>-3905.150556479474</v>
       </c>
       <c r="O32">
-        <v>-926.2219088256791</v>
+        <v>-976.2876391198686</v>
       </c>
       <c r="P32">
-        <v>-2778.665726477037</v>
+        <v>-2928.862917359605</v>
       </c>
       <c r="Q32">
-        <v>-2178.665726477037</v>
+        <v>-2328.862917359605</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1319561083488605</v>
+        <v>0.1332047476002932</v>
       </c>
       <c r="T32">
-        <v>1.332807595230967</v>
+        <v>1.352123647335763</v>
       </c>
       <c r="U32">
         <v>0.2166309777667576</v>
       </c>
       <c r="V32">
-        <v>0.09583235156011535</v>
+        <v>0.09274098538075679</v>
       </c>
       <c r="W32">
-        <v>0.1958707217466021</v>
+        <v>0.1965404074246717</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>0.3833294062404614</v>
+        <v>0.3709639415230271</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1528388021458505</v>
+        <v>0.1545471119235181</v>
       </c>
       <c r="C33">
-        <v>25680.33422049425</v>
+        <v>23936.25718965053</v>
       </c>
       <c r="D33">
-        <v>52176.05723166798</v>
+        <v>51356.42287860406</v>
       </c>
       <c r="E33">
-        <v>22421.25523319396</v>
+        <v>23345.69791097375</v>
       </c>
       <c r="F33">
-        <v>28657.72301117373</v>
+        <v>29582.16568895353</v>
       </c>
       <c r="G33">
         <v>2162</v>
@@ -3993,37 +3993,37 @@
         <v>2303</v>
       </c>
       <c r="M33">
-        <v>6208.150556479474</v>
+        <v>6408.41347765623</v>
       </c>
       <c r="N33">
-        <v>-3905.150556479474</v>
+        <v>-4105.41347765623</v>
       </c>
       <c r="O33">
-        <v>-976.2876391198686</v>
+        <v>-1026.353369414058</v>
       </c>
       <c r="P33">
-        <v>-2928.862917359605</v>
+        <v>-3079.060108242173</v>
       </c>
       <c r="Q33">
-        <v>-2328.862917359605</v>
+        <v>-2479.060108242173</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1332047476002932</v>
+        <v>0.1344901115355916</v>
       </c>
       <c r="T33">
-        <v>1.352123647335763</v>
+        <v>1.372007818620113</v>
       </c>
       <c r="U33">
         <v>0.2166309777667576</v>
       </c>
       <c r="V33">
-        <v>0.09274098538075679</v>
+        <v>0.08984282958760814</v>
       </c>
       <c r="W33">
-        <v>0.1965404074246717</v>
+        <v>0.1971682377478619</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>0.3709639415230271</v>
+        <v>0.3593713183504326</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1545471119235181</v>
+        <v>0.1562554217011857</v>
       </c>
       <c r="C34">
-        <v>23936.25718965053</v>
+        <v>22217.53318101047</v>
       </c>
       <c r="D34">
-        <v>51356.42287860406</v>
+        <v>50562.1415477438</v>
       </c>
       <c r="E34">
-        <v>23345.69791097375</v>
+        <v>24270.14058875355</v>
       </c>
       <c r="F34">
-        <v>29582.16568895353</v>
+        <v>30506.60836673333</v>
       </c>
       <c r="G34">
         <v>2162</v>
@@ -4075,37 +4075,37 @@
         <v>2303</v>
       </c>
       <c r="M34">
-        <v>6408.41347765623</v>
+        <v>6608.676398832989</v>
       </c>
       <c r="N34">
-        <v>-4105.41347765623</v>
+        <v>-4305.676398832989</v>
       </c>
       <c r="O34">
-        <v>-1026.353369414058</v>
+        <v>-1076.419099708247</v>
       </c>
       <c r="P34">
-        <v>-3079.060108242173</v>
+        <v>-3229.257299124742</v>
       </c>
       <c r="Q34">
-        <v>-2479.060108242173</v>
+        <v>-2629.257299124742</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1344901115355916</v>
+        <v>0.1358138445435856</v>
       </c>
       <c r="T34">
-        <v>1.372007818620113</v>
+        <v>1.392485547256234</v>
       </c>
       <c r="U34">
         <v>0.2166309777667576</v>
       </c>
       <c r="V34">
-        <v>0.08984282958760814</v>
+        <v>0.08712031960010486</v>
       </c>
       <c r="W34">
-        <v>0.1971682377478619</v>
+        <v>0.1977580177484344</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>0.3593713183504326</v>
+        <v>0.3484812784004194</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1562554217011857</v>
+        <v>0.1579637314788533</v>
       </c>
       <c r="C35">
-        <v>22217.53318101047</v>
+        <v>20523.00377691568</v>
       </c>
       <c r="D35">
-        <v>50562.1415477438</v>
+        <v>49792.05482142881</v>
       </c>
       <c r="E35">
-        <v>24270.14058875355</v>
+        <v>25194.58326653335</v>
       </c>
       <c r="F35">
-        <v>30506.60836673333</v>
+        <v>31431.05104451313</v>
       </c>
       <c r="G35">
         <v>2162</v>
@@ -4157,37 +4157,37 @@
         <v>2303</v>
       </c>
       <c r="M35">
-        <v>6608.676398832989</v>
+        <v>6808.939320009747</v>
       </c>
       <c r="N35">
-        <v>-4305.676398832989</v>
+        <v>-4505.939320009747</v>
       </c>
       <c r="O35">
-        <v>-1076.419099708247</v>
+        <v>-1126.484830002437</v>
       </c>
       <c r="P35">
-        <v>-3229.257299124742</v>
+        <v>-3379.45449000731</v>
       </c>
       <c r="Q35">
-        <v>-2629.257299124742</v>
+        <v>-2779.45449000731</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1358138445435856</v>
+        <v>0.1371776906730338</v>
       </c>
       <c r="T35">
-        <v>1.392485547256234</v>
+        <v>1.413583813123753</v>
       </c>
       <c r="U35">
         <v>0.2166309777667576</v>
       </c>
       <c r="V35">
-        <v>0.08712031960010486</v>
+        <v>0.08455795725892529</v>
       </c>
       <c r="W35">
-        <v>0.1977580177484344</v>
+        <v>0.1983131048077969</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>0.3484812784004194</v>
+        <v>0.3382318290357011</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1579637314788533</v>
+        <v>0.1596720412565208</v>
       </c>
       <c r="C36">
-        <v>20523.00377691568</v>
+        <v>18851.58007409225</v>
       </c>
       <c r="D36">
-        <v>49792.05482142881</v>
+        <v>49045.07379638517</v>
       </c>
       <c r="E36">
-        <v>25194.58326653335</v>
+        <v>26119.02594431315</v>
       </c>
       <c r="F36">
-        <v>31431.05104451313</v>
+        <v>32355.49372229293</v>
       </c>
       <c r="G36">
         <v>2162</v>
@@ -4239,37 +4239,37 @@
         <v>2303</v>
       </c>
       <c r="M36">
-        <v>6808.939320009747</v>
+        <v>7009.202241186503</v>
       </c>
       <c r="N36">
-        <v>-4505.939320009747</v>
+        <v>-4706.202241186503</v>
       </c>
       <c r="O36">
-        <v>-1126.484830002437</v>
+        <v>-1176.550560296626</v>
       </c>
       <c r="P36">
-        <v>-3379.45449000731</v>
+        <v>-3529.651680889877</v>
       </c>
       <c r="Q36">
-        <v>-2779.45449000731</v>
+        <v>-2929.651680889877</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1371776906730338</v>
+        <v>0.1385835012987728</v>
       </c>
       <c r="T36">
-        <v>1.413583813123753</v>
+        <v>1.43533125640258</v>
       </c>
       <c r="U36">
         <v>0.2166309777667576</v>
       </c>
       <c r="V36">
-        <v>0.08455795725892529</v>
+        <v>0.08214201562295601</v>
       </c>
       <c r="W36">
-        <v>0.1983131048077969</v>
+        <v>0.1988364726066243</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>0.3382318290357011</v>
+        <v>0.328568062491824</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1596720412565208</v>
+        <v>0.1613803510341884</v>
       </c>
       <c r="C37">
-        <v>18851.58007409225</v>
+        <v>17202.23754644084</v>
       </c>
       <c r="D37">
-        <v>49045.07379638517</v>
+        <v>48320.17394651356</v>
       </c>
       <c r="E37">
-        <v>26119.02594431315</v>
+        <v>27043.46862209294</v>
       </c>
       <c r="F37">
-        <v>32355.49372229293</v>
+        <v>33279.93640007272</v>
       </c>
       <c r="G37">
         <v>2162</v>
@@ -4321,37 +4321,37 @@
         <v>2303</v>
       </c>
       <c r="M37">
-        <v>7009.202241186503</v>
+        <v>7209.46516236326</v>
       </c>
       <c r="N37">
-        <v>-4706.202241186503</v>
+        <v>-4906.46516236326</v>
       </c>
       <c r="O37">
-        <v>-1176.550560296626</v>
+        <v>-1226.616290590815</v>
       </c>
       <c r="P37">
-        <v>-3529.651680889877</v>
+        <v>-3679.848871772445</v>
       </c>
       <c r="Q37">
-        <v>-2929.651680889877</v>
+        <v>-3079.848871772445</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1385835012987728</v>
+        <v>0.1400332435065661</v>
       </c>
       <c r="T37">
-        <v>1.43533125640258</v>
+        <v>1.45775830728387</v>
       </c>
       <c r="U37">
         <v>0.2166309777667576</v>
       </c>
       <c r="V37">
-        <v>0.08214201562295601</v>
+        <v>0.07986029296676279</v>
       </c>
       <c r="W37">
-        <v>0.1988364726066243</v>
+        <v>0.199330764416628</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>0.328568062491824</v>
+        <v>0.3194411718670511</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1613803510341884</v>
+        <v>0.163088660811856</v>
       </c>
       <c r="C38">
-        <v>17202.23754644084</v>
+        <v>15574.01135676777</v>
       </c>
       <c r="D38">
-        <v>48320.17394651356</v>
+        <v>47616.39043462029</v>
       </c>
       <c r="E38">
-        <v>27043.46862209294</v>
+        <v>27967.91129987274</v>
       </c>
       <c r="F38">
-        <v>33279.93640007272</v>
+        <v>34204.37907785252</v>
       </c>
       <c r="G38">
         <v>2162</v>
@@ -4403,37 +4403,37 @@
         <v>2303</v>
       </c>
       <c r="M38">
-        <v>7209.46516236326</v>
+        <v>7409.728083540018</v>
       </c>
       <c r="N38">
-        <v>-4906.46516236326</v>
+        <v>-5106.728083540018</v>
       </c>
       <c r="O38">
-        <v>-1226.616290590815</v>
+        <v>-1276.682020885004</v>
       </c>
       <c r="P38">
-        <v>-3679.848871772445</v>
+        <v>-3830.046062655013</v>
       </c>
       <c r="Q38">
-        <v>-3079.848871772445</v>
+        <v>-3230.046062655013</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1400332435065661</v>
+        <v>0.1415290092765116</v>
       </c>
       <c r="T38">
-        <v>1.45775830728387</v>
+        <v>1.480897328034408</v>
       </c>
       <c r="U38">
         <v>0.2166309777667576</v>
       </c>
       <c r="V38">
-        <v>0.07986029296676279</v>
+        <v>0.07770190667036379</v>
       </c>
       <c r="W38">
-        <v>0.199330764416628</v>
+        <v>0.1997983377504153</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>0.3194411718670511</v>
+        <v>0.3108076266814551</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.163088660811856</v>
+        <v>0.1647969705895236</v>
       </c>
       <c r="C39">
-        <v>15574.01135676777</v>
+        <v>13965.99207234231</v>
       </c>
       <c r="D39">
-        <v>47616.39043462029</v>
+        <v>46932.81382797462</v>
       </c>
       <c r="E39">
-        <v>27967.91129987274</v>
+        <v>28892.35397765254</v>
       </c>
       <c r="F39">
-        <v>34204.37907785252</v>
+        <v>35128.82175563231</v>
       </c>
       <c r="G39">
         <v>2162</v>
@@ -4485,37 +4485,37 @@
         <v>2303</v>
       </c>
       <c r="M39">
-        <v>7409.728083540018</v>
+        <v>7609.991004716774</v>
       </c>
       <c r="N39">
-        <v>-5106.728083540018</v>
+        <v>-5306.991004716774</v>
       </c>
       <c r="O39">
-        <v>-1276.682020885004</v>
+        <v>-1326.747751179194</v>
       </c>
       <c r="P39">
-        <v>-3830.046062655013</v>
+        <v>-3980.243253537581</v>
       </c>
       <c r="Q39">
-        <v>-3230.046062655013</v>
+        <v>-3380.243253537581</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1415290092765116</v>
+        <v>0.143073025555165</v>
       </c>
       <c r="T39">
-        <v>1.480897328034408</v>
+        <v>1.504782768809156</v>
       </c>
       <c r="U39">
         <v>0.2166309777667576</v>
       </c>
       <c r="V39">
-        <v>0.07770190667036379</v>
+        <v>0.07565711965272265</v>
       </c>
       <c r="W39">
-        <v>0.1997983377504153</v>
+        <v>0.2002413019613717</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>0.3108076266814551</v>
+        <v>0.3026284786108906</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1647969705895236</v>
+        <v>0.1665052803671911</v>
       </c>
       <c r="C40">
-        <v>13965.99207234231</v>
+        <v>12377.32174427345</v>
       </c>
       <c r="D40">
-        <v>46932.81382797462</v>
+        <v>46268.58617768557</v>
       </c>
       <c r="E40">
-        <v>28892.35397765254</v>
+        <v>29816.79665543234</v>
       </c>
       <c r="F40">
-        <v>35128.82175563231</v>
+        <v>36053.26443341211</v>
       </c>
       <c r="G40">
         <v>2162</v>
@@ -4567,37 +4567,37 @@
         <v>2303</v>
       </c>
       <c r="M40">
-        <v>7609.991004716774</v>
+        <v>7810.253925893531</v>
       </c>
       <c r="N40">
-        <v>-5306.991004716774</v>
+        <v>-5507.253925893531</v>
       </c>
       <c r="O40">
-        <v>-1326.747751179194</v>
+        <v>-1376.813481473383</v>
       </c>
       <c r="P40">
-        <v>-3980.243253537581</v>
+        <v>-4130.440444420148</v>
       </c>
       <c r="Q40">
-        <v>-3380.243253537581</v>
+        <v>-3530.440444420148</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.143073025555165</v>
+        <v>0.1446676653183645</v>
       </c>
       <c r="T40">
-        <v>1.504782768809156</v>
+        <v>1.529451338789634</v>
       </c>
       <c r="U40">
         <v>0.2166309777667576</v>
       </c>
       <c r="V40">
-        <v>0.07565711965272265</v>
+        <v>0.07371719350778104</v>
       </c>
       <c r="W40">
-        <v>0.2002413019613717</v>
+        <v>0.2006615500589457</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.3026284786108906</v>
+        <v>0.2948687740311242</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1665052803671911</v>
+        <v>0.1682135901448587</v>
       </c>
       <c r="C41">
-        <v>12377.32174427345</v>
+        <v>10807.1903151658</v>
       </c>
       <c r="D41">
-        <v>46268.58617768557</v>
+        <v>45622.89742635772</v>
       </c>
       <c r="E41">
-        <v>29816.79665543234</v>
+        <v>30741.23933321214</v>
       </c>
       <c r="F41">
-        <v>36053.26443341211</v>
+        <v>36977.70711119191</v>
       </c>
       <c r="G41">
         <v>2162</v>
@@ -4649,37 +4649,37 @@
         <v>2303</v>
       </c>
       <c r="M41">
-        <v>7810.253925893531</v>
+        <v>8010.516847070289</v>
       </c>
       <c r="N41">
-        <v>-5507.253925893531</v>
+        <v>-5707.516847070289</v>
       </c>
       <c r="O41">
-        <v>-1376.813481473383</v>
+        <v>-1426.879211767572</v>
       </c>
       <c r="P41">
-        <v>-4130.440444420148</v>
+        <v>-4280.637635302717</v>
       </c>
       <c r="Q41">
-        <v>-3530.440444420148</v>
+        <v>-3680.637635302717</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1446676653183645</v>
+        <v>0.1463154597403372</v>
       </c>
       <c r="T41">
-        <v>1.529451338789634</v>
+        <v>1.554942194436128</v>
       </c>
       <c r="U41">
         <v>0.2166309777667576</v>
       </c>
       <c r="V41">
-        <v>0.07371719350778104</v>
+        <v>0.07187426367008651</v>
       </c>
       <c r="W41">
-        <v>0.2006615500589457</v>
+        <v>0.201060785751641</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.2948687740311242</v>
+        <v>0.287497054680346</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1682135901448587</v>
+        <v>0.1699218999225263</v>
       </c>
       <c r="C42">
-        <v>10807.1903151658</v>
+        <v>9254.832323427552</v>
       </c>
       <c r="D42">
-        <v>45622.89742635772</v>
+        <v>44994.98211239927</v>
       </c>
       <c r="E42">
-        <v>30741.23933321214</v>
+        <v>31665.68201099194</v>
       </c>
       <c r="F42">
-        <v>36977.70711119191</v>
+        <v>37902.14978897171</v>
       </c>
       <c r="G42">
         <v>2162</v>
@@ -4731,37 +4731,37 @@
         <v>2303</v>
       </c>
       <c r="M42">
-        <v>8010.516847070289</v>
+        <v>8210.779768247046</v>
       </c>
       <c r="N42">
-        <v>-5707.516847070289</v>
+        <v>-5907.779768247046</v>
       </c>
       <c r="O42">
-        <v>-1426.879211767572</v>
+        <v>-1476.944942061762</v>
       </c>
       <c r="P42">
-        <v>-4280.637635302717</v>
+        <v>-4430.834826185284</v>
       </c>
       <c r="Q42">
-        <v>-3680.637635302717</v>
+        <v>-3830.834826185284</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1463154597403372</v>
+        <v>0.1480191116003429</v>
       </c>
       <c r="T42">
-        <v>1.554942194436128</v>
+        <v>1.581297146884198</v>
       </c>
       <c r="U42">
         <v>0.2166309777667576</v>
       </c>
       <c r="V42">
-        <v>0.07187426367008651</v>
+        <v>0.07012123284886489</v>
       </c>
       <c r="W42">
-        <v>0.201060785751641</v>
+        <v>0.2014405465324975</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.287497054680346</v>
+        <v>0.2804849313954595</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1699218999225263</v>
+        <v>0.1716302097001939</v>
       </c>
       <c r="C43">
-        <v>9254.832323427552</v>
+        <v>7719.523876038606</v>
       </c>
       <c r="D43">
-        <v>44994.98211239927</v>
+        <v>44384.11634279012</v>
       </c>
       <c r="E43">
-        <v>31665.68201099194</v>
+        <v>32590.12468877174</v>
       </c>
       <c r="F43">
-        <v>37902.14978897171</v>
+        <v>38826.59246675151</v>
       </c>
       <c r="G43">
         <v>2162</v>
@@ -4813,37 +4813,37 @@
         <v>2303</v>
       </c>
       <c r="M43">
-        <v>8210.779768247046</v>
+        <v>8411.042689423804</v>
       </c>
       <c r="N43">
-        <v>-5907.779768247046</v>
+        <v>-6108.042689423804</v>
       </c>
       <c r="O43">
-        <v>-1476.944942061762</v>
+        <v>-1527.010672355951</v>
       </c>
       <c r="P43">
-        <v>-4430.834826185284</v>
+        <v>-4581.032017067853</v>
       </c>
       <c r="Q43">
-        <v>-3830.834826185284</v>
+        <v>-3981.032017067853</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1480191116003429</v>
+        <v>0.1497815100762109</v>
       </c>
       <c r="T43">
-        <v>1.581297146884198</v>
+        <v>1.608560890795995</v>
       </c>
       <c r="U43">
         <v>0.2166309777667576</v>
       </c>
       <c r="V43">
-        <v>0.07012123284886489</v>
+        <v>0.06845167968579667</v>
       </c>
       <c r="W43">
-        <v>0.2014405465324975</v>
+        <v>0.2018022234666465</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.2804849313954595</v>
+        <v>0.2738067187431866</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1716302097001939</v>
+        <v>0.1733385194778614</v>
       </c>
       <c r="C44">
-        <v>7719.523876038613</v>
+        <v>6200.579864607331</v>
       </c>
       <c r="D44">
-        <v>44384.11634279012</v>
+        <v>43789.61500913864</v>
       </c>
       <c r="E44">
-        <v>32590.12468877173</v>
+        <v>33514.56736655153</v>
       </c>
       <c r="F44">
-        <v>38826.59246675151</v>
+        <v>39751.03514453131</v>
       </c>
       <c r="G44">
         <v>2162</v>
@@ -4895,37 +4895,37 @@
         <v>2303</v>
       </c>
       <c r="M44">
-        <v>8411.042689423803</v>
+        <v>8611.305610600561</v>
       </c>
       <c r="N44">
-        <v>-6108.042689423803</v>
+        <v>-6308.305610600561</v>
       </c>
       <c r="O44">
-        <v>-1527.010672355951</v>
+        <v>-1577.07640265014</v>
       </c>
       <c r="P44">
-        <v>-4581.032017067851</v>
+        <v>-4731.22920795042</v>
       </c>
       <c r="Q44">
-        <v>-3981.032017067851</v>
+        <v>-4131.22920795042</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1497815100762109</v>
+        <v>0.1516057470950918</v>
       </c>
       <c r="T44">
-        <v>1.608560890795995</v>
+        <v>1.636781257301187</v>
       </c>
       <c r="U44">
         <v>0.2166309777667576</v>
       </c>
       <c r="V44">
-        <v>0.06845167968579668</v>
+        <v>0.06685978015822001</v>
       </c>
       <c r="W44">
-        <v>0.2018022234666465</v>
+        <v>0.2021470782178119</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.2738067187431867</v>
+        <v>0.26743912063288</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1733385194778614</v>
+        <v>0.175046829255529</v>
       </c>
       <c r="C45">
-        <v>6200.579864607331</v>
+        <v>4697.351402206747</v>
       </c>
       <c r="D45">
-        <v>43789.61500913864</v>
+        <v>43210.82922451785</v>
       </c>
       <c r="E45">
-        <v>33514.56736655153</v>
+        <v>34439.01004433133</v>
       </c>
       <c r="F45">
-        <v>39751.03514453131</v>
+        <v>40675.47782231111</v>
       </c>
       <c r="G45">
         <v>2162</v>
@@ -4977,37 +4977,37 @@
         <v>2303</v>
       </c>
       <c r="M45">
-        <v>8611.305610600561</v>
+        <v>8811.568531777319</v>
       </c>
       <c r="N45">
-        <v>-6308.305610600561</v>
+        <v>-6508.568531777319</v>
       </c>
       <c r="O45">
-        <v>-1577.07640265014</v>
+        <v>-1627.14213294433</v>
       </c>
       <c r="P45">
-        <v>-4731.22920795042</v>
+        <v>-4881.426398832989</v>
       </c>
       <c r="Q45">
-        <v>-4131.22920795042</v>
+        <v>-4281.426398832989</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1516057470950918</v>
+        <v>0.1534951354360756</v>
       </c>
       <c r="T45">
-        <v>1.636781257301187</v>
+        <v>1.666009494038709</v>
       </c>
       <c r="U45">
         <v>0.2166309777667576</v>
       </c>
       <c r="V45">
-        <v>0.06685978015822001</v>
+        <v>0.06534023970007864</v>
       </c>
       <c r="W45">
-        <v>0.2021470782178119</v>
+        <v>0.2024762577530152</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.26743912063288</v>
+        <v>0.2613609588003145</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.175046829255529</v>
+        <v>0.1767551390331966</v>
       </c>
       <c r="C46">
-        <v>4697.351402206747</v>
+        <v>3209.223460829489</v>
       </c>
       <c r="D46">
-        <v>43210.82922451785</v>
+        <v>42647.1439609204</v>
       </c>
       <c r="E46">
-        <v>34439.01004433133</v>
+        <v>35363.45272211113</v>
       </c>
       <c r="F46">
-        <v>40675.47782231111</v>
+        <v>41599.92050009091</v>
       </c>
       <c r="G46">
         <v>2162</v>
@@ -5059,37 +5059,37 @@
         <v>2303</v>
       </c>
       <c r="M46">
-        <v>8811.568531777319</v>
+        <v>9011.831452954077</v>
       </c>
       <c r="N46">
-        <v>-6508.568531777319</v>
+        <v>-6708.831452954077</v>
       </c>
       <c r="O46">
-        <v>-1627.14213294433</v>
+        <v>-1677.207863238519</v>
       </c>
       <c r="P46">
-        <v>-4881.426398832989</v>
+        <v>-5031.623589715558</v>
       </c>
       <c r="Q46">
-        <v>-4281.426398832989</v>
+        <v>-4431.623589715558</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1534951354360756</v>
+        <v>0.1554532288076406</v>
       </c>
       <c r="T46">
-        <v>1.666009494038709</v>
+        <v>1.696300575748503</v>
       </c>
       <c r="U46">
         <v>0.2166309777667576</v>
       </c>
       <c r="V46">
-        <v>0.06534023970007864</v>
+        <v>0.06388823437341022</v>
       </c>
       <c r="W46">
-        <v>0.2024762577530152</v>
+        <v>0.202790807086654</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.2613609588003145</v>
+        <v>0.2555529374936408</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1767551390331966</v>
+        <v>0.1784634488108642</v>
       </c>
       <c r="C47">
-        <v>3209.223460829489</v>
+        <v>1735.61269137809</v>
       </c>
       <c r="D47">
-        <v>42647.1439609204</v>
+        <v>42097.97586924879</v>
       </c>
       <c r="E47">
-        <v>35363.45272211113</v>
+        <v>36287.89539989092</v>
       </c>
       <c r="F47">
-        <v>41599.92050009091</v>
+        <v>42524.3631778707</v>
       </c>
       <c r="G47">
         <v>2162</v>
@@ -5141,37 +5141,37 @@
         <v>2303</v>
       </c>
       <c r="M47">
-        <v>9011.831452954077</v>
+        <v>9212.094374130831</v>
       </c>
       <c r="N47">
-        <v>-6708.831452954077</v>
+        <v>-6909.094374130831</v>
       </c>
       <c r="O47">
-        <v>-1677.207863238519</v>
+        <v>-1727.273593532708</v>
       </c>
       <c r="P47">
-        <v>-5031.623589715558</v>
+        <v>-5181.820780598124</v>
       </c>
       <c r="Q47">
-        <v>-4431.623589715558</v>
+        <v>-4581.820780598124</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1554532288076406</v>
+        <v>0.1574838441559302</v>
       </c>
       <c r="T47">
-        <v>1.696300575748503</v>
+        <v>1.727713549373475</v>
       </c>
       <c r="U47">
         <v>0.2166309777667576</v>
       </c>
       <c r="V47">
-        <v>0.06388823437341022</v>
+        <v>0.06249935971311871</v>
       </c>
       <c r="W47">
-        <v>0.202790807086654</v>
+        <v>0.2030916803623084</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.2555529374936408</v>
+        <v>0.2499974388524748</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1784634488108642</v>
+        <v>0.1801717585885318</v>
       </c>
       <c r="C48">
-        <v>1735.61269137809</v>
+        <v>275.9654099458858</v>
       </c>
       <c r="D48">
-        <v>42097.97586924879</v>
+        <v>41562.77126559638</v>
       </c>
       <c r="E48">
-        <v>36287.89539989092</v>
+        <v>37212.33807767072</v>
       </c>
       <c r="F48">
-        <v>42524.3631778707</v>
+        <v>43448.8058556505</v>
       </c>
       <c r="G48">
         <v>2162</v>
@@ -5223,37 +5223,37 @@
         <v>2303</v>
       </c>
       <c r="M48">
-        <v>9212.094374130831</v>
+        <v>9412.357295307589</v>
       </c>
       <c r="N48">
-        <v>-6909.094374130831</v>
+        <v>-7109.357295307589</v>
       </c>
       <c r="O48">
-        <v>-1727.273593532708</v>
+        <v>-1777.339323826897</v>
       </c>
       <c r="P48">
-        <v>-5181.820780598124</v>
+        <v>-5332.017971480692</v>
       </c>
       <c r="Q48">
-        <v>-4581.820780598124</v>
+        <v>-4732.017971480692</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1574838441559302</v>
+        <v>0.159591086498495</v>
       </c>
       <c r="T48">
-        <v>1.727713549373475</v>
+        <v>1.760311918229579</v>
       </c>
       <c r="U48">
         <v>0.2166309777667576</v>
       </c>
       <c r="V48">
-        <v>0.06249935971311871</v>
+        <v>0.06116958610220129</v>
       </c>
       <c r="W48">
-        <v>0.2030916803623084</v>
+        <v>0.2033797505198499</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.2499974388524748</v>
+        <v>0.2446783444088052</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1801717585885318</v>
+        <v>0.1818800683661994</v>
       </c>
       <c r="C49">
-        <v>275.9654099458858</v>
+        <v>-1170.244264223933</v>
       </c>
       <c r="D49">
-        <v>41562.77126559638</v>
+        <v>41041.00426920637</v>
       </c>
       <c r="E49">
-        <v>37212.33807767072</v>
+        <v>38136.78075545052</v>
       </c>
       <c r="F49">
-        <v>43448.8058556505</v>
+        <v>44373.2485334303</v>
       </c>
       <c r="G49">
         <v>2162</v>
@@ -5305,37 +5305,37 @@
         <v>2303</v>
       </c>
       <c r="M49">
-        <v>9412.357295307589</v>
+        <v>9612.620216484347</v>
       </c>
       <c r="N49">
-        <v>-7109.357295307589</v>
+        <v>-7309.620216484347</v>
       </c>
       <c r="O49">
-        <v>-1777.339323826897</v>
+        <v>-1827.405054121087</v>
       </c>
       <c r="P49">
-        <v>-5332.017971480692</v>
+        <v>-5482.21516236326</v>
       </c>
       <c r="Q49">
-        <v>-4732.017971480692</v>
+        <v>-4882.21516236326</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.159591086498495</v>
+        <v>0.161779376623466</v>
       </c>
       <c r="T49">
-        <v>1.760311918229579</v>
+        <v>1.794164070503225</v>
       </c>
       <c r="U49">
         <v>0.2166309777667576</v>
       </c>
       <c r="V49">
-        <v>0.06116958610220129</v>
+        <v>0.05989521972507209</v>
       </c>
       <c r="W49">
-        <v>0.2033797505198499</v>
+        <v>0.2036558177541604</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.2446783444088052</v>
+        <v>0.2395808789002883</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1818800683661993</v>
+        <v>0.1835883781438669</v>
       </c>
       <c r="C50">
-        <v>-1170.244264223918</v>
+        <v>-2603.516132265155</v>
       </c>
       <c r="D50">
-        <v>41041.00426920637</v>
+        <v>40532.17507894494</v>
       </c>
       <c r="E50">
-        <v>38136.78075545051</v>
+        <v>39061.22343323031</v>
       </c>
       <c r="F50">
-        <v>44373.24853343029</v>
+        <v>45297.69121121009</v>
       </c>
       <c r="G50">
         <v>2162</v>
@@ -5387,37 +5387,37 @@
         <v>2303</v>
       </c>
       <c r="M50">
-        <v>9612.620216484345</v>
+        <v>9812.883137661103</v>
       </c>
       <c r="N50">
-        <v>-7309.620216484345</v>
+        <v>-7509.883137661103</v>
       </c>
       <c r="O50">
-        <v>-1827.405054121086</v>
+        <v>-1877.470784415276</v>
       </c>
       <c r="P50">
-        <v>-5482.215162363259</v>
+        <v>-5632.412353245827</v>
       </c>
       <c r="Q50">
-        <v>-4882.215162363259</v>
+        <v>-5032.412353245827</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.161779376623466</v>
+        <v>0.1640534820474555</v>
       </c>
       <c r="T50">
-        <v>1.794164070503225</v>
+        <v>1.82934375816015</v>
       </c>
       <c r="U50">
         <v>0.2166309777667576</v>
       </c>
       <c r="V50">
-        <v>0.0598952197250721</v>
+        <v>0.05867286830211144</v>
       </c>
       <c r="W50">
-        <v>0.2036558177541604</v>
+        <v>0.203920616938091</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.2395808789002885</v>
+        <v>0.2346914732084457</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1835883781438669</v>
+        <v>0.1852966879215345</v>
       </c>
       <c r="C51">
-        <v>-2603.516132265155</v>
+        <v>-4024.325512575153</v>
       </c>
       <c r="D51">
-        <v>40532.17507894494</v>
+        <v>40035.80837641474</v>
       </c>
       <c r="E51">
-        <v>39061.22343323031</v>
+        <v>39985.66611101011</v>
       </c>
       <c r="F51">
-        <v>45297.69121121009</v>
+        <v>46222.13388898989</v>
       </c>
       <c r="G51">
         <v>2162</v>
@@ -5469,37 +5469,37 @@
         <v>2303</v>
       </c>
       <c r="M51">
-        <v>9812.883137661103</v>
+        <v>10013.14605883786</v>
       </c>
       <c r="N51">
-        <v>-7509.883137661103</v>
+        <v>-7710.146058837861</v>
       </c>
       <c r="O51">
-        <v>-1877.470784415276</v>
+        <v>-1927.536514709465</v>
       </c>
       <c r="P51">
-        <v>-5632.412353245827</v>
+        <v>-5782.609544128396</v>
       </c>
       <c r="Q51">
-        <v>-5032.412353245827</v>
+        <v>-5182.609544128396</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1640534820474555</v>
+        <v>0.1664185516884046</v>
       </c>
       <c r="T51">
-        <v>1.82934375816015</v>
+        <v>1.865930633323354</v>
       </c>
       <c r="U51">
         <v>0.2166309777667576</v>
       </c>
       <c r="V51">
-        <v>0.05867286830211144</v>
+        <v>0.05749941093606921</v>
       </c>
       <c r="W51">
-        <v>0.203920616938091</v>
+        <v>0.2041748241546643</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.2346914732084457</v>
+        <v>0.2299976437442768</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1852966879215345</v>
+        <v>0.187004997699202</v>
       </c>
       <c r="C52">
-        <v>-4024.325512575153</v>
+        <v>-5433.124721785571</v>
       </c>
       <c r="D52">
-        <v>40035.80837641474</v>
+        <v>39551.45184498412</v>
       </c>
       <c r="E52">
-        <v>39985.66611101011</v>
+        <v>40910.10878878991</v>
       </c>
       <c r="F52">
-        <v>46222.13388898989</v>
+        <v>47146.57656676969</v>
       </c>
       <c r="G52">
         <v>2162</v>
@@ -5551,37 +5551,37 @@
         <v>2303</v>
       </c>
       <c r="M52">
-        <v>10013.14605883786</v>
+        <v>10213.40898001462</v>
       </c>
       <c r="N52">
-        <v>-7710.146058837861</v>
+        <v>-7910.408980014619</v>
       </c>
       <c r="O52">
-        <v>-1927.536514709465</v>
+        <v>-1977.602245003655</v>
       </c>
       <c r="P52">
-        <v>-5782.609544128396</v>
+        <v>-5932.806735010965</v>
       </c>
       <c r="Q52">
-        <v>-5182.609544128396</v>
+        <v>-5332.806735010965</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1664185516884046</v>
+        <v>0.1688801547840864</v>
       </c>
       <c r="T52">
-        <v>1.865930633323354</v>
+        <v>1.904010850329953</v>
       </c>
       <c r="U52">
         <v>0.2166309777667576</v>
       </c>
       <c r="V52">
-        <v>0.05749941093606921</v>
+        <v>0.0563719715059502</v>
       </c>
       <c r="W52">
-        <v>0.2041748241546643</v>
+        <v>0.2044190624607838</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.2299976437442768</v>
+        <v>0.2254878860238008</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.187004997699202</v>
+        <v>0.1887133074768696</v>
       </c>
       <c r="C53">
-        <v>-5433.124721785571</v>
+        <v>-6830.344449516931</v>
       </c>
       <c r="D53">
-        <v>39551.45184498412</v>
+        <v>39078.67479503256</v>
       </c>
       <c r="E53">
-        <v>40910.10878878991</v>
+        <v>41834.55146656971</v>
       </c>
       <c r="F53">
-        <v>47146.57656676969</v>
+        <v>48071.01924454949</v>
       </c>
       <c r="G53">
         <v>2162</v>
@@ -5633,37 +5633,37 @@
         <v>2303</v>
       </c>
       <c r="M53">
-        <v>10213.40898001462</v>
+        <v>10413.67190119138</v>
       </c>
       <c r="N53">
-        <v>-7910.408980014619</v>
+        <v>-8110.671901191376</v>
       </c>
       <c r="O53">
-        <v>-1977.602245003655</v>
+        <v>-2027.667975297844</v>
       </c>
       <c r="P53">
-        <v>-5932.806735010965</v>
+        <v>-6083.003925893532</v>
       </c>
       <c r="Q53">
-        <v>-5332.806735010965</v>
+        <v>-5483.003925893532</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1688801547840864</v>
+        <v>0.1714443246754215</v>
       </c>
       <c r="T53">
-        <v>1.904010850329953</v>
+        <v>1.94367774304516</v>
       </c>
       <c r="U53">
         <v>0.2166309777667576</v>
       </c>
       <c r="V53">
-        <v>0.0563719715059502</v>
+        <v>0.05528789513083578</v>
       </c>
       <c r="W53">
-        <v>0.2044190624607838</v>
+        <v>0.2046539069858987</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.2254878860238008</v>
+        <v>0.2211515805233432</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1887133074768696</v>
+        <v>0.1904216172545372</v>
       </c>
       <c r="C54">
-        <v>-6830.344449516931</v>
+        <v>-8216.395035699177</v>
       </c>
       <c r="D54">
-        <v>39078.67479503256</v>
+        <v>38617.06688663011</v>
       </c>
       <c r="E54">
-        <v>41834.55146656971</v>
+        <v>42758.9941443495</v>
       </c>
       <c r="F54">
-        <v>48071.01924454949</v>
+        <v>48995.46192232928</v>
       </c>
       <c r="G54">
         <v>2162</v>
@@ -5715,37 +5715,37 @@
         <v>2303</v>
       </c>
       <c r="M54">
-        <v>10413.67190119138</v>
+        <v>10613.93482236813</v>
       </c>
       <c r="N54">
-        <v>-8110.671901191376</v>
+        <v>-8310.934822368132</v>
       </c>
       <c r="O54">
-        <v>-2027.667975297844</v>
+        <v>-2077.733705592033</v>
       </c>
       <c r="P54">
-        <v>-6083.003925893532</v>
+        <v>-6233.201116776099</v>
       </c>
       <c r="Q54">
-        <v>-5483.003925893532</v>
+        <v>-5633.201116776099</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1714443246754215</v>
+        <v>0.1741176081791539</v>
       </c>
       <c r="T54">
-        <v>1.94367774304516</v>
+        <v>1.985032588641866</v>
       </c>
       <c r="U54">
         <v>0.2166309777667576</v>
       </c>
       <c r="V54">
-        <v>0.05528789513083578</v>
+        <v>0.0542447272981785</v>
       </c>
       <c r="W54">
-        <v>0.2046539069858987</v>
+        <v>0.204879889453462</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.2211515805233432</v>
+        <v>0.216978909192714</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1904216172545372</v>
+        <v>0.1921299270322048</v>
       </c>
       <c r="C55">
-        <v>-8216.395035699177</v>
+        <v>-9591.667658420811</v>
       </c>
       <c r="D55">
-        <v>38617.06688663011</v>
+        <v>38166.23694168827</v>
       </c>
       <c r="E55">
-        <v>42758.9941443495</v>
+        <v>43683.4368221293</v>
       </c>
       <c r="F55">
-        <v>48995.46192232928</v>
+        <v>49919.90460010908</v>
       </c>
       <c r="G55">
         <v>2162</v>
@@ -5797,37 +5797,37 @@
         <v>2303</v>
       </c>
       <c r="M55">
-        <v>10613.93482236813</v>
+        <v>10814.19774354489</v>
       </c>
       <c r="N55">
-        <v>-8310.934822368132</v>
+        <v>-8511.19774354489</v>
       </c>
       <c r="O55">
-        <v>-2077.733705592033</v>
+        <v>-2127.799435886222</v>
       </c>
       <c r="P55">
-        <v>-6233.201116776099</v>
+        <v>-6383.398307658667</v>
       </c>
       <c r="Q55">
-        <v>-5633.201116776099</v>
+        <v>-5783.398307658667</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1741176081791539</v>
+        <v>0.1769071214004398</v>
       </c>
       <c r="T55">
-        <v>1.985032588641866</v>
+        <v>2.028185471003645</v>
       </c>
       <c r="U55">
         <v>0.2166309777667576</v>
       </c>
       <c r="V55">
-        <v>0.0542447272981785</v>
+        <v>0.05324019531117519</v>
       </c>
       <c r="W55">
-        <v>0.204879889453462</v>
+        <v>0.2050975022000046</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.216978909192714</v>
+        <v>0.2129607812447007</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1921299270322048</v>
+        <v>0.1938382368098724</v>
       </c>
       <c r="C56">
-        <v>-9591.667658420811</v>
+        <v>-10956.53543953389</v>
       </c>
       <c r="D56">
-        <v>38166.23694168827</v>
+        <v>37725.81183835499</v>
       </c>
       <c r="E56">
-        <v>43683.4368221293</v>
+        <v>44607.8794999091</v>
       </c>
       <c r="F56">
-        <v>49919.90460010908</v>
+        <v>50844.34727788888</v>
       </c>
       <c r="G56">
         <v>2162</v>
@@ -5879,37 +5879,37 @@
         <v>2303</v>
       </c>
       <c r="M56">
-        <v>10814.19774354489</v>
+        <v>11014.46066472165</v>
       </c>
       <c r="N56">
-        <v>-8511.19774354489</v>
+        <v>-8711.460664721648</v>
       </c>
       <c r="O56">
-        <v>-2127.799435886222</v>
+        <v>-2177.865166180412</v>
       </c>
       <c r="P56">
-        <v>-6383.398307658667</v>
+        <v>-6533.595498541235</v>
       </c>
       <c r="Q56">
-        <v>-5783.398307658667</v>
+        <v>-5933.595498541235</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1769071214004398</v>
+        <v>0.1798206129871163</v>
       </c>
       <c r="T56">
-        <v>2.028185471003645</v>
+        <v>2.073256259248171</v>
       </c>
       <c r="U56">
         <v>0.2166309777667576</v>
       </c>
       <c r="V56">
-        <v>0.05324019531117519</v>
+        <v>0.05227219176006291</v>
       </c>
       <c r="W56">
-        <v>0.2050975022000046</v>
+        <v>0.2053072017557637</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.2129607812447007</v>
+        <v>0.2090887670402517</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1938382368098724</v>
+        <v>0.1955465465875399</v>
       </c>
       <c r="C57">
-        <v>-10956.53543953389</v>
+        <v>-12311.35447458236</v>
       </c>
       <c r="D57">
-        <v>37725.81183835499</v>
+        <v>37295.43548108632</v>
       </c>
       <c r="E57">
-        <v>44607.8794999091</v>
+        <v>45532.3221776889</v>
       </c>
       <c r="F57">
-        <v>50844.34727788888</v>
+        <v>51768.78995566868</v>
       </c>
       <c r="G57">
         <v>2162</v>
@@ -5961,37 +5961,37 @@
         <v>2303</v>
       </c>
       <c r="M57">
-        <v>11014.46066472165</v>
+        <v>11214.72358589841</v>
       </c>
       <c r="N57">
-        <v>-8711.460664721648</v>
+        <v>-8911.723585898406</v>
       </c>
       <c r="O57">
-        <v>-2177.865166180412</v>
+        <v>-2227.930896474601</v>
       </c>
       <c r="P57">
-        <v>-6533.595498541235</v>
+        <v>-6683.792689423804</v>
       </c>
       <c r="Q57">
-        <v>-5933.595498541235</v>
+        <v>-6083.792689423804</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1798206129871163</v>
+        <v>0.1828665360095507</v>
       </c>
       <c r="T57">
-        <v>2.073256259248171</v>
+        <v>2.120375719685629</v>
       </c>
       <c r="U57">
         <v>0.2166309777667576</v>
       </c>
       <c r="V57">
-        <v>0.05227219176006291</v>
+        <v>0.0513387597643475</v>
       </c>
       <c r="W57">
-        <v>0.2053072017557637</v>
+        <v>0.2055094120416743</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.2090887670402517</v>
+        <v>0.2053550390573901</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1955465465875399</v>
+        <v>0.1972548563652075</v>
       </c>
       <c r="C58">
-        <v>-12311.35447458236</v>
+        <v>-13656.46479302916</v>
       </c>
       <c r="D58">
-        <v>37295.43548108632</v>
+        <v>36874.76784041932</v>
       </c>
       <c r="E58">
-        <v>45532.3221776889</v>
+        <v>46456.7648554687</v>
       </c>
       <c r="F58">
-        <v>51768.78995566868</v>
+        <v>52693.23263344848</v>
       </c>
       <c r="G58">
         <v>2162</v>
@@ -6043,37 +6043,37 @@
         <v>2303</v>
       </c>
       <c r="M58">
-        <v>11214.72358589841</v>
+        <v>11414.98650707516</v>
       </c>
       <c r="N58">
-        <v>-8911.723585898406</v>
+        <v>-9111.986507075162</v>
       </c>
       <c r="O58">
-        <v>-2227.930896474601</v>
+        <v>-2277.996626768791</v>
       </c>
       <c r="P58">
-        <v>-6683.792689423804</v>
+        <v>-6833.989880306372</v>
       </c>
       <c r="Q58">
-        <v>-6083.792689423804</v>
+        <v>-6233.989880306372</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1828665360095507</v>
+        <v>0.186054129870238</v>
       </c>
       <c r="T58">
-        <v>2.120375719685629</v>
+        <v>2.169686782934132</v>
       </c>
       <c r="U58">
         <v>0.2166309777667576</v>
       </c>
       <c r="V58">
-        <v>0.0513387597643475</v>
+        <v>0.05043807976848176</v>
       </c>
       <c r="W58">
-        <v>0.2055094120416743</v>
+        <v>0.2057045272298337</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.2053550390573901</v>
+        <v>0.201752319073927</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1972548563652075</v>
+        <v>0.2195114739012451</v>
       </c>
       <c r="C59">
-        <v>-13656.46479302916</v>
+        <v>-19305.45206261273</v>
       </c>
       <c r="D59">
-        <v>36874.76784041932</v>
+        <v>32150.22324861555</v>
       </c>
       <c r="E59">
-        <v>46456.7648554687</v>
+        <v>47381.2075332485</v>
       </c>
       <c r="F59">
-        <v>52693.23263344848</v>
+        <v>53617.67531122828</v>
       </c>
       <c r="G59">
         <v>2162</v>
@@ -6125,45 +6125,45 @@
         <v>2303</v>
       </c>
       <c r="M59">
-        <v>11414.98650707516</v>
+        <v>13491.86806414491</v>
       </c>
       <c r="N59">
-        <v>-9111.986507075162</v>
+        <v>-11188.86806414491</v>
       </c>
       <c r="O59">
-        <v>-2277.996626768791</v>
+        <v>-2797.217016036228</v>
       </c>
       <c r="P59">
-        <v>-6833.989880306372</v>
+        <v>-8391.651048108683</v>
       </c>
       <c r="Q59">
-        <v>-6233.989880306372</v>
+        <v>-7791.651048108683</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.186054129870238</v>
+        <v>0.1899847228632674</v>
       </c>
       <c r="T59">
-        <v>2.169686782934132</v>
+        <v>2.230491806457929</v>
       </c>
       <c r="U59">
-        <v>0.2166309777667576</v>
+        <v>0.2516309777667576</v>
       </c>
       <c r="V59">
-        <v>0.05043807976848176</v>
+        <v>0.04267385341026828</v>
       </c>
       <c r="W59">
-        <v>0.2057045272298337</v>
+        <v>0.2408929143080565</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y59">
-        <v>0.201752319073927</v>
+        <v>0.1706954136410731</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.219511473901245</v>
+        <v>0.2215697836789126</v>
       </c>
       <c r="C60">
-        <v>-19305.45206261271</v>
+        <v>-20606.38219734761</v>
       </c>
       <c r="D60">
-        <v>32150.22324861556</v>
+        <v>31773.73579166046</v>
       </c>
       <c r="E60">
-        <v>47381.20753324849</v>
+        <v>48305.65021102829</v>
       </c>
       <c r="F60">
-        <v>53617.67531122827</v>
+        <v>54542.11798900807</v>
       </c>
       <c r="G60">
         <v>2162</v>
@@ -6207,37 +6207,37 @@
         <v>2303</v>
       </c>
       <c r="M60">
-        <v>13491.86806414491</v>
+        <v>13724.48647904396</v>
       </c>
       <c r="N60">
-        <v>-11188.86806414491</v>
+        <v>-11421.48647904396</v>
       </c>
       <c r="O60">
-        <v>-2797.217016036227</v>
+        <v>-2855.371619760989</v>
       </c>
       <c r="P60">
-        <v>-8391.651048108681</v>
+        <v>-8566.114859282967</v>
       </c>
       <c r="Q60">
-        <v>-7791.651048108681</v>
+        <v>-7966.114859282967</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1899847228632673</v>
+        <v>0.193501423420908</v>
       </c>
       <c r="T60">
-        <v>2.230491806457928</v>
+        <v>2.284894045639829</v>
       </c>
       <c r="U60">
         <v>0.2516309777667576</v>
       </c>
       <c r="V60">
-        <v>0.0426738534102683</v>
+        <v>0.0419505677592468</v>
       </c>
       <c r="W60">
-        <v>0.2408929143080565</v>
+        <v>0.2410749153836277</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.1706954136410732</v>
+        <v>0.1678022710369872</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.2215697836789126</v>
+        <v>0.2236280934565802</v>
       </c>
       <c r="C61">
-        <v>-20606.38219734761</v>
+        <v>-21898.59686087931</v>
       </c>
       <c r="D61">
-        <v>31773.73579166046</v>
+        <v>31405.96380590856</v>
       </c>
       <c r="E61">
-        <v>48305.65021102829</v>
+        <v>49230.09288880809</v>
       </c>
       <c r="F61">
-        <v>54542.11798900807</v>
+        <v>55466.56066678787</v>
       </c>
       <c r="G61">
         <v>2162</v>
@@ -6289,37 +6289,37 @@
         <v>2303</v>
       </c>
       <c r="M61">
-        <v>13724.48647904396</v>
+        <v>13957.10489394301</v>
       </c>
       <c r="N61">
-        <v>-11421.48647904396</v>
+        <v>-11654.10489394301</v>
       </c>
       <c r="O61">
-        <v>-2855.371619760989</v>
+        <v>-2913.526223485752</v>
       </c>
       <c r="P61">
-        <v>-8566.114859282967</v>
+        <v>-8740.578670457257</v>
       </c>
       <c r="Q61">
-        <v>-7966.114859282967</v>
+        <v>-8140.578670457257</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.193501423420908</v>
+        <v>0.1971939590064307</v>
       </c>
       <c r="T61">
-        <v>2.284894045639829</v>
+        <v>2.342016396780825</v>
       </c>
       <c r="U61">
         <v>0.2516309777667576</v>
       </c>
       <c r="V61">
-        <v>0.0419505677592468</v>
+        <v>0.04125139162992601</v>
       </c>
       <c r="W61">
-        <v>0.2410749153836277</v>
+        <v>0.2412508497566799</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.1678022710369872</v>
+        <v>0.1650055665197041</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.2236280934565802</v>
+        <v>0.2256864032342478</v>
       </c>
       <c r="C62">
-        <v>-21898.59686087931</v>
+        <v>-23182.39522767469</v>
       </c>
       <c r="D62">
-        <v>31405.96380590856</v>
+        <v>31046.60811689298</v>
       </c>
       <c r="E62">
-        <v>49230.09288880809</v>
+        <v>50154.53556658789</v>
       </c>
       <c r="F62">
-        <v>55466.56066678787</v>
+        <v>56391.00334456767</v>
       </c>
       <c r="G62">
         <v>2162</v>
@@ -6371,37 +6371,37 @@
         <v>2303</v>
       </c>
       <c r="M62">
-        <v>13957.10489394301</v>
+        <v>14189.72330884206</v>
       </c>
       <c r="N62">
-        <v>-11654.10489394301</v>
+        <v>-11886.72330884206</v>
       </c>
       <c r="O62">
-        <v>-2913.526223485752</v>
+        <v>-2971.680827210515</v>
       </c>
       <c r="P62">
-        <v>-8740.578670457257</v>
+        <v>-8915.042481631544</v>
       </c>
       <c r="Q62">
-        <v>-8140.578670457257</v>
+        <v>-8315.042481631544</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1971939590064307</v>
+        <v>0.201075855391211</v>
       </c>
       <c r="T62">
-        <v>2.342016396780825</v>
+        <v>2.402068099262385</v>
       </c>
       <c r="U62">
         <v>0.2516309777667576</v>
       </c>
       <c r="V62">
-        <v>0.04125139162992601</v>
+        <v>0.04057513930812395</v>
       </c>
       <c r="W62">
-        <v>0.2412508497566799</v>
+        <v>0.241421015789632</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.1650055665197041</v>
+        <v>0.1623005572324958</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.2256864032342478</v>
+        <v>0.2277447130119154</v>
       </c>
       <c r="C63">
-        <v>-23182.39522767469</v>
+        <v>-24458.06293415993</v>
       </c>
       <c r="D63">
-        <v>31046.60811689298</v>
+        <v>30695.38308818754</v>
       </c>
       <c r="E63">
-        <v>50154.53556658789</v>
+        <v>51078.97824436769</v>
       </c>
       <c r="F63">
-        <v>56391.00334456767</v>
+        <v>57315.44602234747</v>
       </c>
       <c r="G63">
         <v>2162</v>
@@ -6453,37 +6453,37 @@
         <v>2303</v>
       </c>
       <c r="M63">
-        <v>14189.72330884206</v>
+        <v>14422.34172374111</v>
       </c>
       <c r="N63">
-        <v>-11886.72330884206</v>
+        <v>-12119.34172374111</v>
       </c>
       <c r="O63">
-        <v>-2971.680827210515</v>
+        <v>-3029.835430935278</v>
       </c>
       <c r="P63">
-        <v>-8915.042481631544</v>
+        <v>-9089.506292805832</v>
       </c>
       <c r="Q63">
-        <v>-8315.042481631544</v>
+        <v>-8489.506292805832</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.201075855391211</v>
+        <v>0.2051620621120324</v>
       </c>
       <c r="T63">
-        <v>2.402068099262385</v>
+        <v>2.465280417664026</v>
       </c>
       <c r="U63">
         <v>0.2516309777667576</v>
       </c>
       <c r="V63">
-        <v>0.04057513930812395</v>
+        <v>0.03992070157734775</v>
       </c>
       <c r="W63">
-        <v>0.241421015789632</v>
+        <v>0.2415856925957146</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.1623005572324958</v>
+        <v>0.159682806309391</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.2277447130119154</v>
+        <v>0.2298030227895829</v>
       </c>
       <c r="C64">
-        <v>-24458.06293415993</v>
+        <v>-25725.87283592234</v>
       </c>
       <c r="D64">
-        <v>30695.38308818754</v>
+        <v>30352.01586420492</v>
       </c>
       <c r="E64">
-        <v>51078.97824436769</v>
+        <v>52003.42092214748</v>
       </c>
       <c r="F64">
-        <v>57315.44602234747</v>
+        <v>58239.88870012726</v>
       </c>
       <c r="G64">
         <v>2162</v>
@@ -6535,37 +6535,37 @@
         <v>2303</v>
       </c>
       <c r="M64">
-        <v>14422.34172374111</v>
+        <v>14654.96013864016</v>
       </c>
       <c r="N64">
-        <v>-12119.34172374111</v>
+        <v>-12351.96013864016</v>
       </c>
       <c r="O64">
-        <v>-3029.835430935278</v>
+        <v>-3087.99003466004</v>
       </c>
       <c r="P64">
-        <v>-9089.506292805832</v>
+        <v>-9263.970103980118</v>
       </c>
       <c r="Q64">
-        <v>-8489.506292805832</v>
+        <v>-8663.970103980118</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.2051620621120324</v>
+        <v>0.209469144871817</v>
       </c>
       <c r="T64">
-        <v>2.465280417664026</v>
+        <v>2.531909618141433</v>
       </c>
       <c r="U64">
         <v>0.2516309777667576</v>
       </c>
       <c r="V64">
-        <v>0.03992070157734775</v>
+        <v>0.03928703964754858</v>
       </c>
       <c r="W64">
-        <v>0.2415856925957146</v>
+        <v>0.2417451415666836</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.159682806309391</v>
+        <v>0.1571481585901944</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.2298030227895829</v>
+        <v>0.2318613325672506</v>
       </c>
       <c r="C65">
-        <v>-25725.87283592234</v>
+        <v>-26986.08571465259</v>
       </c>
       <c r="D65">
-        <v>30352.01586420492</v>
+        <v>30016.24566325447</v>
       </c>
       <c r="E65">
-        <v>52003.42092214748</v>
+        <v>52927.86359992728</v>
       </c>
       <c r="F65">
-        <v>58239.88870012726</v>
+        <v>59164.33137790706</v>
       </c>
       <c r="G65">
         <v>2162</v>
@@ -6617,37 +6617,37 @@
         <v>2303</v>
       </c>
       <c r="M65">
-        <v>14654.96013864016</v>
+        <v>14887.57855353921</v>
       </c>
       <c r="N65">
-        <v>-12351.96013864016</v>
+        <v>-12584.57855353921</v>
       </c>
       <c r="O65">
-        <v>-3087.99003466004</v>
+        <v>-3146.144638384802</v>
       </c>
       <c r="P65">
-        <v>-9263.970103980118</v>
+        <v>-9438.433915154408</v>
       </c>
       <c r="Q65">
-        <v>-8663.970103980118</v>
+        <v>-8838.433915154408</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.209469144871817</v>
+        <v>0.2140155100071453</v>
       </c>
       <c r="T65">
-        <v>2.531909618141433</v>
+        <v>2.602240440867584</v>
       </c>
       <c r="U65">
         <v>0.2516309777667576</v>
       </c>
       <c r="V65">
-        <v>0.03928703964754858</v>
+        <v>0.03867317965305563</v>
       </c>
       <c r="W65">
-        <v>0.2417451415666836</v>
+        <v>0.2418996077573097</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.1571481585901944</v>
+        <v>0.1546927186122226</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.2318613325672506</v>
+        <v>0.2339196423449181</v>
       </c>
       <c r="C66">
-        <v>-26986.08571465259</v>
+        <v>-28238.95093867702</v>
       </c>
       <c r="D66">
-        <v>30016.24566325447</v>
+        <v>29687.82311700984</v>
       </c>
       <c r="E66">
-        <v>52927.86359992728</v>
+        <v>53852.30627770708</v>
       </c>
       <c r="F66">
-        <v>59164.33137790706</v>
+        <v>60088.77405568686</v>
       </c>
       <c r="G66">
         <v>2162</v>
@@ -6699,37 +6699,37 @@
         <v>2303</v>
       </c>
       <c r="M66">
-        <v>14887.57855353921</v>
+        <v>15120.19696843826</v>
       </c>
       <c r="N66">
-        <v>-12584.57855353921</v>
+        <v>-12817.19696843826</v>
       </c>
       <c r="O66">
-        <v>-3146.144638384802</v>
+        <v>-3204.299242109565</v>
       </c>
       <c r="P66">
-        <v>-9438.433915154408</v>
+        <v>-9612.897726328694</v>
       </c>
       <c r="Q66">
-        <v>-8838.433915154408</v>
+        <v>-9012.897726328694</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.2140155100071453</v>
+        <v>0.2188216674359209</v>
       </c>
       <c r="T66">
-        <v>2.602240440867584</v>
+        <v>2.676590167749515</v>
       </c>
       <c r="U66">
         <v>0.2516309777667576</v>
       </c>
       <c r="V66">
-        <v>0.03867317965305563</v>
+        <v>0.03807820765839324</v>
       </c>
       <c r="W66">
-        <v>0.2418996077573097</v>
+        <v>0.2420493211420705</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.1546927186122226</v>
+        <v>0.1523128306335729</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.2339196423449181</v>
+        <v>0.2359779521225857</v>
       </c>
       <c r="C67">
-        <v>-28238.95093867702</v>
+        <v>-29484.70708059602</v>
       </c>
       <c r="D67">
-        <v>29687.82311700984</v>
+        <v>29366.50965287063</v>
       </c>
       <c r="E67">
-        <v>53852.30627770708</v>
+        <v>54776.74895548688</v>
       </c>
       <c r="F67">
-        <v>60088.77405568686</v>
+        <v>61013.21673346666</v>
       </c>
       <c r="G67">
         <v>2162</v>
@@ -6781,37 +6781,37 @@
         <v>2303</v>
       </c>
       <c r="M67">
-        <v>15120.19696843826</v>
+        <v>15352.81538333731</v>
       </c>
       <c r="N67">
-        <v>-12817.19696843826</v>
+        <v>-13049.81538333731</v>
       </c>
       <c r="O67">
-        <v>-3204.299242109565</v>
+        <v>-3262.453845834328</v>
       </c>
       <c r="P67">
-        <v>-9612.897726328694</v>
+        <v>-9787.361537502984</v>
       </c>
       <c r="Q67">
-        <v>-9012.897726328694</v>
+        <v>-9187.361537502984</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.2188216674359209</v>
+        <v>0.2239105400075656</v>
       </c>
       <c r="T67">
-        <v>2.676590167749515</v>
+        <v>2.755313407977441</v>
       </c>
       <c r="U67">
         <v>0.2516309777667576</v>
       </c>
       <c r="V67">
-        <v>0.03807820765839324</v>
+        <v>0.03750126511811455</v>
       </c>
       <c r="W67">
-        <v>0.2420493211420705</v>
+        <v>0.242194497757596</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.1523128306335729</v>
+        <v>0.1500050604724582</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.2359779521225857</v>
+        <v>0.2380362619002532</v>
       </c>
       <c r="C68">
-        <v>-29484.70708059602</v>
+        <v>-30723.58249524332</v>
       </c>
       <c r="D68">
-        <v>29366.50965287063</v>
+        <v>29052.07691600314</v>
       </c>
       <c r="E68">
-        <v>54776.74895548688</v>
+        <v>55701.19163326668</v>
       </c>
       <c r="F68">
-        <v>61013.21673346666</v>
+        <v>61937.65941124646</v>
       </c>
       <c r="G68">
         <v>2162</v>
@@ -6863,37 +6863,37 @@
         <v>2303</v>
       </c>
       <c r="M68">
-        <v>15352.81538333731</v>
+        <v>15585.43379823636</v>
       </c>
       <c r="N68">
-        <v>-13049.81538333731</v>
+        <v>-13282.43379823636</v>
       </c>
       <c r="O68">
-        <v>-3262.453845834328</v>
+        <v>-3320.60844955909</v>
       </c>
       <c r="P68">
-        <v>-9787.361537502984</v>
+        <v>-9961.82534867727</v>
       </c>
       <c r="Q68">
-        <v>-9187.361537502984</v>
+        <v>-9361.82534867727</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2239105400075656</v>
+        <v>0.229307829098704</v>
       </c>
       <c r="T68">
-        <v>2.755313407977441</v>
+        <v>2.838807753673728</v>
       </c>
       <c r="U68">
         <v>0.2516309777667576</v>
       </c>
       <c r="V68">
-        <v>0.03750126511811455</v>
+        <v>0.03694154474321732</v>
       </c>
       <c r="W68">
-        <v>0.242194497757596</v>
+        <v>0.2423353407428074</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.1500050604724582</v>
+        <v>0.1477661789728693</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.2380362619002532</v>
+        <v>0.2400945716779208</v>
       </c>
       <c r="C69">
-        <v>-30723.58249524332</v>
+        <v>-31955.79586090875</v>
       </c>
       <c r="D69">
-        <v>29052.07691600314</v>
+        <v>28744.30622811751</v>
       </c>
       <c r="E69">
-        <v>55701.19163326668</v>
+        <v>56625.63431104648</v>
       </c>
       <c r="F69">
-        <v>61937.65941124646</v>
+        <v>62862.10208902626</v>
       </c>
       <c r="G69">
         <v>2162</v>
@@ -6945,37 +6945,37 @@
         <v>2303</v>
       </c>
       <c r="M69">
-        <v>15585.43379823636</v>
+        <v>15818.05221313541</v>
       </c>
       <c r="N69">
-        <v>-13282.43379823636</v>
+        <v>-13515.05221313541</v>
       </c>
       <c r="O69">
-        <v>-3320.60844955909</v>
+        <v>-3378.763053283853</v>
       </c>
       <c r="P69">
-        <v>-9961.82534867727</v>
+        <v>-10136.28915985156</v>
       </c>
       <c r="Q69">
-        <v>-9361.82534867727</v>
+        <v>-9536.28915985156</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.229307829098704</v>
+        <v>0.2350424487580385</v>
       </c>
       <c r="T69">
-        <v>2.838807753673728</v>
+        <v>2.927520495976032</v>
       </c>
       <c r="U69">
         <v>0.2516309777667576</v>
       </c>
       <c r="V69">
-        <v>0.03694154474321732</v>
+        <v>0.03639828673228765</v>
       </c>
       <c r="W69">
-        <v>0.2423353407428074</v>
+        <v>0.2424720412872773</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.1477661789728693</v>
+        <v>0.1455931469291506</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2400945716779208</v>
+        <v>0.2421528814555884</v>
       </c>
       <c r="C70">
-        <v>-31955.79586090875</v>
+        <v>-33181.5566865202</v>
       </c>
       <c r="D70">
-        <v>28744.30622811751</v>
+        <v>28442.98808028585</v>
       </c>
       <c r="E70">
-        <v>56625.63431104648</v>
+        <v>57550.07698882627</v>
       </c>
       <c r="F70">
-        <v>62862.10208902626</v>
+        <v>63786.54476680605</v>
       </c>
       <c r="G70">
         <v>2162</v>
@@ -7027,37 +7027,37 @@
         <v>2303</v>
       </c>
       <c r="M70">
-        <v>15818.05221313541</v>
+        <v>16050.67062803446</v>
       </c>
       <c r="N70">
-        <v>-13515.05221313541</v>
+        <v>-13747.67062803446</v>
       </c>
       <c r="O70">
-        <v>-3378.763053283853</v>
+        <v>-3436.917657008615</v>
       </c>
       <c r="P70">
-        <v>-10136.28915985156</v>
+        <v>-10310.75297102585</v>
       </c>
       <c r="Q70">
-        <v>-9536.28915985156</v>
+        <v>-9710.752971025846</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2350424487580385</v>
+        <v>0.2411470438792655</v>
       </c>
       <c r="T70">
-        <v>2.927520495976032</v>
+        <v>3.021956641007517</v>
       </c>
       <c r="U70">
         <v>0.2516309777667576</v>
       </c>
       <c r="V70">
-        <v>0.03639828673228765</v>
+        <v>0.03587077533037044</v>
       </c>
       <c r="W70">
-        <v>0.2424720412872773</v>
+        <v>0.2426047794971248</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.1455931469291506</v>
+        <v>0.1434831013214818</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2421528814555884</v>
+        <v>0.244211191233256</v>
       </c>
       <c r="C71">
-        <v>-33181.5566865202</v>
+        <v>-34401.06578725649</v>
       </c>
       <c r="D71">
-        <v>28442.98808028585</v>
+        <v>28147.92165732936</v>
       </c>
       <c r="E71">
-        <v>57550.07698882627</v>
+        <v>58474.51966660607</v>
       </c>
       <c r="F71">
-        <v>63786.54476680605</v>
+        <v>64710.98744458585</v>
       </c>
       <c r="G71">
         <v>2162</v>
@@ -7109,37 +7109,37 @@
         <v>2303</v>
       </c>
       <c r="M71">
-        <v>16050.67062803446</v>
+        <v>16283.28904293351</v>
       </c>
       <c r="N71">
-        <v>-13747.67062803446</v>
+        <v>-13980.28904293351</v>
       </c>
       <c r="O71">
-        <v>-3436.917657008615</v>
+        <v>-3495.072260733378</v>
       </c>
       <c r="P71">
-        <v>-10310.75297102585</v>
+        <v>-10485.21678220013</v>
       </c>
       <c r="Q71">
-        <v>-9710.752971025846</v>
+        <v>-9885.216782200134</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2411470438792655</v>
+        <v>0.2476586120085744</v>
       </c>
       <c r="T71">
-        <v>3.021956641007517</v>
+        <v>3.122688529041101</v>
       </c>
       <c r="U71">
         <v>0.2516309777667576</v>
       </c>
       <c r="V71">
-        <v>0.03587077533037044</v>
+        <v>0.03535833568279372</v>
       </c>
       <c r="W71">
-        <v>0.2426047794971248</v>
+        <v>0.242733725186691</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.1434831013214818</v>
+        <v>0.1414333427311749</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.244211191233256</v>
+        <v>0.2462695010109235</v>
       </c>
       <c r="C72">
-        <v>-34401.06578725649</v>
+        <v>-35614.51573086047</v>
       </c>
       <c r="D72">
-        <v>28147.92165732936</v>
+        <v>27858.91439150518</v>
       </c>
       <c r="E72">
-        <v>58474.51966660607</v>
+        <v>59398.96234438587</v>
       </c>
       <c r="F72">
-        <v>64710.98744458585</v>
+        <v>65635.43012236565</v>
       </c>
       <c r="G72">
         <v>2162</v>
@@ -7191,37 +7191,37 @@
         <v>2303</v>
       </c>
       <c r="M72">
-        <v>16283.28904293351</v>
+        <v>16515.90745783256</v>
       </c>
       <c r="N72">
-        <v>-13980.28904293351</v>
+        <v>-14212.90745783256</v>
       </c>
       <c r="O72">
-        <v>-3495.072260733378</v>
+        <v>-3553.226864458141</v>
       </c>
       <c r="P72">
-        <v>-10485.21678220013</v>
+        <v>-10659.68059337442</v>
       </c>
       <c r="Q72">
-        <v>-9885.216782200134</v>
+        <v>-10059.68059337442</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2476586120085744</v>
+        <v>0.2546192538019735</v>
       </c>
       <c r="T72">
-        <v>3.122688529041101</v>
+        <v>3.230367443835622</v>
       </c>
       <c r="U72">
         <v>0.2516309777667576</v>
       </c>
       <c r="V72">
-        <v>0.03535833568279372</v>
+        <v>0.03486033095486705</v>
       </c>
       <c r="W72">
-        <v>0.242733725186691</v>
+        <v>0.2428590386033116</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.1414333427311749</v>
+        <v>0.1394413238194682</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2462695010109235</v>
+        <v>0.2483278107885911</v>
       </c>
       <c r="C73">
-        <v>-35614.51573086045</v>
+        <v>-36822.09125673635</v>
       </c>
       <c r="D73">
-        <v>27858.91439150518</v>
+        <v>27575.7815434091</v>
       </c>
       <c r="E73">
-        <v>59398.96234438586</v>
+        <v>60323.40502216567</v>
       </c>
       <c r="F73">
-        <v>65635.43012236564</v>
+        <v>66559.87280014544</v>
       </c>
       <c r="G73">
         <v>2162</v>
@@ -7273,37 +7273,37 @@
         <v>2303</v>
       </c>
       <c r="M73">
-        <v>16515.90745783256</v>
+        <v>16748.52587273161</v>
       </c>
       <c r="N73">
-        <v>-14212.90745783256</v>
+        <v>-14445.52587273161</v>
       </c>
       <c r="O73">
-        <v>-3553.22686445814</v>
+        <v>-3611.381468182903</v>
       </c>
       <c r="P73">
-        <v>-10659.68059337442</v>
+        <v>-10834.14440454871</v>
       </c>
       <c r="Q73">
-        <v>-10059.68059337442</v>
+        <v>-10234.14440454871</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2546192538019734</v>
+        <v>0.2620770842949011</v>
       </c>
       <c r="T73">
-        <v>3.23036744383562</v>
+        <v>3.345737709686893</v>
       </c>
       <c r="U73">
         <v>0.2516309777667576</v>
       </c>
       <c r="V73">
-        <v>0.03486033095486706</v>
+        <v>0.03437615969160501</v>
       </c>
       <c r="W73">
-        <v>0.2428590386033116</v>
+        <v>0.2429808710916928</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.1394413238194682</v>
+        <v>0.1375046387664201</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2483278107885911</v>
+        <v>0.2503861205662587</v>
       </c>
       <c r="C74">
-        <v>-36822.09125673635</v>
+        <v>-38023.96966974844</v>
       </c>
       <c r="D74">
-        <v>27575.7815434091</v>
+        <v>27298.3458081768</v>
       </c>
       <c r="E74">
-        <v>60323.40502216567</v>
+        <v>61247.84769994546</v>
       </c>
       <c r="F74">
-        <v>66559.87280014544</v>
+        <v>67484.31547792524</v>
       </c>
       <c r="G74">
         <v>2162</v>
@@ -7355,37 +7355,37 @@
         <v>2303</v>
       </c>
       <c r="M74">
-        <v>16748.52587273161</v>
+        <v>16981.14428763066</v>
       </c>
       <c r="N74">
-        <v>-14445.52587273161</v>
+        <v>-14678.14428763066</v>
       </c>
       <c r="O74">
-        <v>-3611.381468182903</v>
+        <v>-3669.536071907665</v>
       </c>
       <c r="P74">
-        <v>-10834.14440454871</v>
+        <v>-11008.608215723</v>
       </c>
       <c r="Q74">
-        <v>-10234.14440454871</v>
+        <v>-10408.608215723</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2620770842949011</v>
+        <v>0.2700873466761937</v>
       </c>
       <c r="T74">
-        <v>3.345737709686893</v>
+        <v>3.469653921156778</v>
       </c>
       <c r="U74">
         <v>0.2516309777667576</v>
       </c>
       <c r="V74">
-        <v>0.03437615969160501</v>
+        <v>0.03390525339445973</v>
       </c>
       <c r="W74">
-        <v>0.2429808710916928</v>
+        <v>0.24309936570368</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.1375046387664201</v>
+        <v>0.135621013577839</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2503861205662587</v>
+        <v>0.2524444303439263</v>
       </c>
       <c r="C75">
-        <v>-38023.96966974844</v>
+        <v>-39220.32121048479</v>
       </c>
       <c r="D75">
-        <v>27298.3458081768</v>
+        <v>27026.43694522025</v>
       </c>
       <c r="E75">
-        <v>61247.84769994546</v>
+        <v>62172.29037772526</v>
       </c>
       <c r="F75">
-        <v>67484.31547792524</v>
+        <v>68408.75815570504</v>
       </c>
       <c r="G75">
         <v>2162</v>
@@ -7437,37 +7437,37 @@
         <v>2303</v>
       </c>
       <c r="M75">
-        <v>16981.14428763066</v>
+        <v>17213.76270252971</v>
       </c>
       <c r="N75">
-        <v>-14678.14428763066</v>
+        <v>-14910.76270252971</v>
       </c>
       <c r="O75">
-        <v>-3669.536071907665</v>
+        <v>-3727.690675632428</v>
       </c>
       <c r="P75">
-        <v>-11008.608215723</v>
+        <v>-11183.07202689728</v>
       </c>
       <c r="Q75">
-        <v>-10408.608215723</v>
+        <v>-10583.07202689728</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2700873466761937</v>
+        <v>0.2787137830868165</v>
       </c>
       <c r="T75">
-        <v>3.469653921156778</v>
+        <v>3.603102148893577</v>
       </c>
       <c r="U75">
         <v>0.2516309777667576</v>
       </c>
       <c r="V75">
-        <v>0.03390525339445973</v>
+        <v>0.03344707429453461</v>
       </c>
       <c r="W75">
-        <v>0.24309936570368</v>
+        <v>0.2432146577585864</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.135621013577839</v>
+        <v>0.1337882971781384</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2524444303439263</v>
+        <v>0.2545027401215939</v>
       </c>
       <c r="C76">
-        <v>-39220.32121048479</v>
+        <v>-40411.30940361074</v>
       </c>
       <c r="D76">
-        <v>27026.43694522025</v>
+        <v>26759.8914298741</v>
       </c>
       <c r="E76">
-        <v>62172.29037772526</v>
+        <v>63096.73305550506</v>
       </c>
       <c r="F76">
-        <v>68408.75815570504</v>
+        <v>69333.20083348484</v>
       </c>
       <c r="G76">
         <v>2162</v>
@@ -7519,37 +7519,37 @@
         <v>2303</v>
       </c>
       <c r="M76">
-        <v>17213.76270252971</v>
+        <v>17446.38111742876</v>
       </c>
       <c r="N76">
-        <v>-14910.76270252971</v>
+        <v>-15143.38111742876</v>
       </c>
       <c r="O76">
-        <v>-3727.690675632428</v>
+        <v>-3785.845279357191</v>
       </c>
       <c r="P76">
-        <v>-11183.07202689728</v>
+        <v>-11357.53583807157</v>
       </c>
       <c r="Q76">
-        <v>-10583.07202689728</v>
+        <v>-10757.53583807157</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2787137830868165</v>
+        <v>0.2880303344102892</v>
       </c>
       <c r="T76">
-        <v>3.603102148893577</v>
+        <v>3.74722623484932</v>
       </c>
       <c r="U76">
         <v>0.2516309777667576</v>
       </c>
       <c r="V76">
-        <v>0.03344707429453461</v>
+        <v>0.03300111330394081</v>
       </c>
       <c r="W76">
-        <v>0.2432146577585864</v>
+        <v>0.2433268753586954</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.1337882971781384</v>
+        <v>0.1320044532157633</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2545027401215939</v>
+        <v>0.2565610498992614</v>
       </c>
       <c r="C77">
-        <v>-40411.30940361074</v>
+        <v>-41597.0913858102</v>
       </c>
       <c r="D77">
-        <v>26759.8914298741</v>
+        <v>26498.55212545443</v>
       </c>
       <c r="E77">
-        <v>63096.73305550506</v>
+        <v>64021.17573328485</v>
       </c>
       <c r="F77">
-        <v>69333.20083348484</v>
+        <v>70257.64351126463</v>
       </c>
       <c r="G77">
         <v>2162</v>
@@ -7601,37 +7601,37 @@
         <v>2303</v>
       </c>
       <c r="M77">
-        <v>17446.38111742876</v>
+        <v>17678.99953232781</v>
       </c>
       <c r="N77">
-        <v>-15143.38111742876</v>
+        <v>-15375.99953232781</v>
       </c>
       <c r="O77">
-        <v>-3785.845279357191</v>
+        <v>-3843.999883081952</v>
       </c>
       <c r="P77">
-        <v>-11357.53583807157</v>
+        <v>-11531.99964924586</v>
       </c>
       <c r="Q77">
-        <v>-10757.53583807157</v>
+        <v>-10931.99964924586</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2880303344102892</v>
+        <v>0.2981232650107179</v>
       </c>
       <c r="T77">
-        <v>3.74722623484932</v>
+        <v>3.903360661301375</v>
       </c>
       <c r="U77">
         <v>0.2516309777667576</v>
       </c>
       <c r="V77">
-        <v>0.03300111330394081</v>
+        <v>0.03256688812888896</v>
       </c>
       <c r="W77">
-        <v>0.2433268753586954</v>
+        <v>0.2434361398640646</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.1320044532157633</v>
+        <v>0.1302675525155559</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2565610498992614</v>
+        <v>0.258619359676929</v>
       </c>
       <c r="C78">
-        <v>-41597.0913858102</v>
+        <v>-42777.81821469663</v>
       </c>
       <c r="D78">
-        <v>26498.55212545443</v>
+        <v>26242.26797434781</v>
       </c>
       <c r="E78">
-        <v>64021.17573328485</v>
+        <v>64945.61841106466</v>
       </c>
       <c r="F78">
-        <v>70257.64351126463</v>
+        <v>71182.08618904444</v>
       </c>
       <c r="G78">
         <v>2162</v>
@@ -7683,37 +7683,37 @@
         <v>2303</v>
       </c>
       <c r="M78">
-        <v>17678.99953232781</v>
+        <v>17911.61794722686</v>
       </c>
       <c r="N78">
-        <v>-15375.99953232781</v>
+        <v>-15608.61794722686</v>
       </c>
       <c r="O78">
-        <v>-3843.999883081952</v>
+        <v>-3902.154486806716</v>
       </c>
       <c r="P78">
-        <v>-11531.99964924586</v>
+        <v>-11706.46346042015</v>
       </c>
       <c r="Q78">
-        <v>-10931.99964924586</v>
+        <v>-11106.46346042015</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2981232650107179</v>
+        <v>0.3090938417503143</v>
       </c>
       <c r="T78">
-        <v>3.903360661301375</v>
+        <v>4.073071994401436</v>
       </c>
       <c r="U78">
         <v>0.2516309777667576</v>
       </c>
       <c r="V78">
-        <v>0.03256688812888896</v>
+        <v>0.03214394152981247</v>
       </c>
       <c r="W78">
-        <v>0.2434361398640646</v>
+        <v>0.2435425663303334</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.1302675525155559</v>
+        <v>0.1285757661192499</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.258619359676929</v>
+        <v>0.2606776694545966</v>
       </c>
       <c r="C79">
-        <v>-42777.81821469663</v>
+        <v>-43953.63515996952</v>
       </c>
       <c r="D79">
-        <v>26242.26797434781</v>
+        <v>25990.89370685471</v>
       </c>
       <c r="E79">
-        <v>64945.61841106466</v>
+        <v>65870.06108884445</v>
       </c>
       <c r="F79">
-        <v>71182.08618904444</v>
+        <v>72106.52886682423</v>
       </c>
       <c r="G79">
         <v>2162</v>
@@ -7765,37 +7765,37 @@
         <v>2303</v>
       </c>
       <c r="M79">
-        <v>17911.61794722686</v>
+        <v>18144.23636212591</v>
       </c>
       <c r="N79">
-        <v>-15608.61794722686</v>
+        <v>-15841.23636212591</v>
       </c>
       <c r="O79">
-        <v>-3902.154486806716</v>
+        <v>-3960.309090531478</v>
       </c>
       <c r="P79">
-        <v>-11706.46346042015</v>
+        <v>-11880.92727159443</v>
       </c>
       <c r="Q79">
-        <v>-11106.46346042015</v>
+        <v>-11280.92727159443</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.3090938417503143</v>
+        <v>0.3210617436480559</v>
       </c>
       <c r="T79">
-        <v>4.073071994401436</v>
+        <v>4.258211630510591</v>
       </c>
       <c r="U79">
         <v>0.2516309777667576</v>
       </c>
       <c r="V79">
-        <v>0.03214394152981247</v>
+        <v>0.0317318397153277</v>
       </c>
       <c r="W79">
-        <v>0.2435425663303334</v>
+        <v>0.2436462639128517</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.1285757661192499</v>
+        <v>0.1269273588613108</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2606776694545966</v>
+        <v>0.2627359792322642</v>
       </c>
       <c r="C80">
-        <v>-43953.63515996952</v>
+        <v>-45124.68197799598</v>
       </c>
       <c r="D80">
-        <v>25990.89370685471</v>
+        <v>25744.28956660806</v>
       </c>
       <c r="E80">
-        <v>65870.06108884445</v>
+        <v>66794.50376662426</v>
       </c>
       <c r="F80">
-        <v>72106.52886682423</v>
+        <v>73030.97154460404</v>
       </c>
       <c r="G80">
         <v>2162</v>
@@ -7847,37 +7847,37 @@
         <v>2303</v>
       </c>
       <c r="M80">
-        <v>18144.23636212591</v>
+        <v>18376.85477702496</v>
       </c>
       <c r="N80">
-        <v>-15841.23636212591</v>
+        <v>-16073.85477702496</v>
       </c>
       <c r="O80">
-        <v>-3960.309090531478</v>
+        <v>-4018.463694256241</v>
       </c>
       <c r="P80">
-        <v>-11880.92727159443</v>
+        <v>-12055.39108276872</v>
       </c>
       <c r="Q80">
-        <v>-11280.92727159443</v>
+        <v>-11455.39108276872</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.3210617436480559</v>
+        <v>0.3341694457265348</v>
       </c>
       <c r="T80">
-        <v>4.258211630510591</v>
+        <v>4.460983612915858</v>
       </c>
       <c r="U80">
         <v>0.2516309777667576</v>
       </c>
       <c r="V80">
-        <v>0.0317318397153277</v>
+        <v>0.03133017085817165</v>
       </c>
       <c r="W80">
-        <v>0.2436462639128517</v>
+        <v>0.2437473362401163</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.1269273588613108</v>
+        <v>0.1253206834326867</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2627359792322642</v>
+        <v>0.2647942890099317</v>
       </c>
       <c r="C81">
-        <v>-45124.68197799598</v>
+        <v>-46291.09317090746</v>
       </c>
       <c r="D81">
-        <v>25744.28956660806</v>
+        <v>25502.32105147636</v>
       </c>
       <c r="E81">
-        <v>66794.50376662426</v>
+        <v>67718.94644440405</v>
       </c>
       <c r="F81">
-        <v>73030.97154460404</v>
+        <v>73955.41422238383</v>
       </c>
       <c r="G81">
         <v>2162</v>
@@ -7929,37 +7929,37 @@
         <v>2303</v>
       </c>
       <c r="M81">
-        <v>18376.85477702496</v>
+        <v>18609.47319192401</v>
       </c>
       <c r="N81">
-        <v>-16073.85477702496</v>
+        <v>-16306.47319192401</v>
       </c>
       <c r="O81">
-        <v>-4018.463694256241</v>
+        <v>-4076.618297981003</v>
       </c>
       <c r="P81">
-        <v>-12055.39108276872</v>
+        <v>-12229.85489394301</v>
       </c>
       <c r="Q81">
-        <v>-11455.39108276872</v>
+        <v>-11629.85489394301</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.3341694457265348</v>
+        <v>0.3485879180128615</v>
       </c>
       <c r="T81">
-        <v>4.460983612915858</v>
+        <v>4.684032793561651</v>
       </c>
       <c r="U81">
         <v>0.2516309777667576</v>
       </c>
       <c r="V81">
-        <v>0.03133017085817165</v>
+        <v>0.03093854372244451</v>
       </c>
       <c r="W81">
-        <v>0.2437473362401163</v>
+        <v>0.2438458817591993</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.1253206834326867</v>
+        <v>0.123754174889778</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2647942890099317</v>
+        <v>0.2668525987875993</v>
       </c>
       <c r="C82">
-        <v>-46291.09317090746</v>
+        <v>-47452.99823122143</v>
       </c>
       <c r="D82">
-        <v>25502.32105147636</v>
+        <v>25264.8586689422</v>
       </c>
       <c r="E82">
-        <v>67718.94644440405</v>
+        <v>68643.38912218384</v>
       </c>
       <c r="F82">
-        <v>73955.41422238383</v>
+        <v>74879.85690016362</v>
       </c>
       <c r="G82">
         <v>2162</v>
@@ -8011,37 +8011,37 @@
         <v>2303</v>
       </c>
       <c r="M82">
-        <v>18609.47319192401</v>
+        <v>18842.09160682306</v>
       </c>
       <c r="N82">
-        <v>-16306.47319192401</v>
+        <v>-16539.09160682306</v>
       </c>
       <c r="O82">
-        <v>-4076.618297981003</v>
+        <v>-4134.772901705765</v>
       </c>
       <c r="P82">
-        <v>-12229.85489394301</v>
+        <v>-12404.3187051173</v>
       </c>
       <c r="Q82">
-        <v>-11629.85489394301</v>
+        <v>-11804.3187051173</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.3485879180128615</v>
+        <v>0.3645241242240648</v>
       </c>
       <c r="T82">
-        <v>4.684032793561651</v>
+        <v>4.930560835328055</v>
       </c>
       <c r="U82">
         <v>0.2516309777667576</v>
       </c>
       <c r="V82">
-        <v>0.03093854372244451</v>
+        <v>0.03055658639253779</v>
       </c>
       <c r="W82">
-        <v>0.2438458817591993</v>
+        <v>0.2439419940555889</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.123754174889778</v>
+        <v>0.1222263455701511</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2668525987875993</v>
+        <v>0.2689109085652669</v>
       </c>
       <c r="C83">
-        <v>-47452.99823122143</v>
+        <v>-48610.52187292218</v>
       </c>
       <c r="D83">
-        <v>25264.8586689422</v>
+        <v>25031.77770502124</v>
       </c>
       <c r="E83">
-        <v>68643.38912218384</v>
+        <v>69567.83179996365</v>
       </c>
       <c r="F83">
-        <v>74879.85690016362</v>
+        <v>75804.29957794343</v>
       </c>
       <c r="G83">
         <v>2162</v>
@@ -8093,37 +8093,37 @@
         <v>2303</v>
       </c>
       <c r="M83">
-        <v>18842.09160682306</v>
+        <v>19074.71002172211</v>
       </c>
       <c r="N83">
-        <v>-16539.09160682306</v>
+        <v>-16771.71002172211</v>
       </c>
       <c r="O83">
-        <v>-4134.772901705765</v>
+        <v>-4192.927505430528</v>
       </c>
       <c r="P83">
-        <v>-12404.3187051173</v>
+        <v>-12578.78251629158</v>
       </c>
       <c r="Q83">
-        <v>-11804.3187051173</v>
+        <v>-11978.78251629158</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.3645241242240648</v>
+        <v>0.3822310200142907</v>
       </c>
       <c r="T83">
-        <v>4.930560835328055</v>
+        <v>5.204480881735169</v>
       </c>
       <c r="U83">
         <v>0.2516309777667576</v>
       </c>
       <c r="V83">
-        <v>0.03055658639253779</v>
+        <v>0.03018394509506781</v>
       </c>
       <c r="W83">
-        <v>0.2439419940555889</v>
+        <v>0.2440357621496275</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.1222263455701511</v>
+        <v>0.1207357803802712</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2689109085652669</v>
+        <v>0.2709692183429345</v>
       </c>
       <c r="C84">
-        <v>-48610.52187292218</v>
+        <v>-49763.78424986786</v>
       </c>
       <c r="D84">
-        <v>25031.77770502124</v>
+        <v>24802.95800585536</v>
       </c>
       <c r="E84">
-        <v>69567.83179996365</v>
+        <v>70492.27447774344</v>
       </c>
       <c r="F84">
-        <v>75804.29957794343</v>
+        <v>76728.74225572322</v>
       </c>
       <c r="G84">
         <v>2162</v>
@@ -8175,37 +8175,37 @@
         <v>2303</v>
       </c>
       <c r="M84">
-        <v>19074.71002172211</v>
+        <v>19307.32843662116</v>
       </c>
       <c r="N84">
-        <v>-16771.71002172211</v>
+        <v>-17004.32843662116</v>
       </c>
       <c r="O84">
-        <v>-4192.927505430528</v>
+        <v>-4251.082109155291</v>
       </c>
       <c r="P84">
-        <v>-12578.78251629158</v>
+        <v>-12753.24632746587</v>
       </c>
       <c r="Q84">
-        <v>-11978.78251629158</v>
+        <v>-12153.24632746587</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3822310200142907</v>
+        <v>0.4020210800151313</v>
       </c>
       <c r="T84">
-        <v>5.204480881735169</v>
+        <v>5.510626815954885</v>
       </c>
       <c r="U84">
         <v>0.2516309777667576</v>
       </c>
       <c r="V84">
-        <v>0.03018394509506781</v>
+        <v>0.02982028310597061</v>
       </c>
       <c r="W84">
-        <v>0.2440357621496275</v>
+        <v>0.2441272707715207</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.1207357803802712</v>
+        <v>0.1192811324238824</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2709692183429345</v>
+        <v>0.273027528120602</v>
       </c>
       <c r="C85">
-        <v>-49763.78424986786</v>
+        <v>-50912.90116232681</v>
       </c>
       <c r="D85">
-        <v>24802.95800585536</v>
+        <v>24578.28377117622</v>
       </c>
       <c r="E85">
-        <v>70492.27447774344</v>
+        <v>71416.71715552325</v>
       </c>
       <c r="F85">
-        <v>76728.74225572322</v>
+        <v>77653.18493350303</v>
       </c>
       <c r="G85">
         <v>2162</v>
@@ -8257,37 +8257,37 @@
         <v>2303</v>
       </c>
       <c r="M85">
-        <v>19307.32843662116</v>
+        <v>19539.94685152021</v>
       </c>
       <c r="N85">
-        <v>-17004.32843662116</v>
+        <v>-17236.94685152021</v>
       </c>
       <c r="O85">
-        <v>-4251.082109155291</v>
+        <v>-4309.236712880053</v>
       </c>
       <c r="P85">
-        <v>-12753.24632746587</v>
+        <v>-12927.71013864016</v>
       </c>
       <c r="Q85">
-        <v>-12153.24632746587</v>
+        <v>-12327.71013864016</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.4020210800151313</v>
+        <v>0.4242848975160771</v>
       </c>
       <c r="T85">
-        <v>5.510626815954885</v>
+        <v>5.855040991952066</v>
       </c>
       <c r="U85">
         <v>0.2516309777667576</v>
       </c>
       <c r="V85">
-        <v>0.02982028310597061</v>
+        <v>0.02946527973566144</v>
       </c>
       <c r="W85">
-        <v>0.2441272707715207</v>
+        <v>0.2442166006167021</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.1192811324238824</v>
+        <v>0.1178611189426457</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.273027528120602</v>
+        <v>0.2750858378982696</v>
       </c>
       <c r="C86">
-        <v>-50912.90116232679</v>
+        <v>-52057.98425238947</v>
       </c>
       <c r="D86">
-        <v>24578.28377117622</v>
+        <v>24357.64335889334</v>
       </c>
       <c r="E86">
-        <v>71416.71715552323</v>
+        <v>72341.15983330303</v>
       </c>
       <c r="F86">
-        <v>77653.18493350301</v>
+        <v>78577.62761128281</v>
       </c>
       <c r="G86">
         <v>2162</v>
@@ -8339,37 +8339,37 @@
         <v>2303</v>
       </c>
       <c r="M86">
-        <v>19539.94685152021</v>
+        <v>19772.56526641926</v>
       </c>
       <c r="N86">
-        <v>-17236.94685152021</v>
+        <v>-17469.56526641926</v>
       </c>
       <c r="O86">
-        <v>-4309.236712880052</v>
+        <v>-4367.391316604815</v>
       </c>
       <c r="P86">
-        <v>-12927.71013864016</v>
+        <v>-13102.17394981445</v>
       </c>
       <c r="Q86">
-        <v>-12327.71013864016</v>
+        <v>-12502.17394981445</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.4242848975160768</v>
+        <v>0.4495172240171486</v>
       </c>
       <c r="T86">
-        <v>5.855040991952062</v>
+        <v>6.2453770580822</v>
       </c>
       <c r="U86">
         <v>0.2516309777667576</v>
       </c>
       <c r="V86">
-        <v>0.02946527973566144</v>
+        <v>0.02911862938583013</v>
       </c>
       <c r="W86">
-        <v>0.2442166006167021</v>
+        <v>0.2443038285831733</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.1178611189426457</v>
+        <v>0.1164745175433205</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2750858378982696</v>
+        <v>0.2771441476759372</v>
       </c>
       <c r="C87">
-        <v>-52057.98425238947</v>
+        <v>-53199.14118894871</v>
       </c>
       <c r="D87">
-        <v>24357.64335889334</v>
+        <v>24140.92910011391</v>
       </c>
       <c r="E87">
-        <v>72341.15983330303</v>
+        <v>73265.60251108283</v>
       </c>
       <c r="F87">
-        <v>78577.62761128281</v>
+        <v>79502.07028906261</v>
       </c>
       <c r="G87">
         <v>2162</v>
@@ -8421,37 +8421,37 @@
         <v>2303</v>
       </c>
       <c r="M87">
-        <v>19772.56526641926</v>
+        <v>20005.18368131831</v>
       </c>
       <c r="N87">
-        <v>-17469.56526641926</v>
+        <v>-17702.18368131831</v>
       </c>
       <c r="O87">
-        <v>-4367.391316604815</v>
+        <v>-4425.545920329578</v>
       </c>
       <c r="P87">
-        <v>-13102.17394981445</v>
+        <v>-13276.63776098873</v>
       </c>
       <c r="Q87">
-        <v>-12502.17394981445</v>
+        <v>-12676.63776098873</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.4495172240171486</v>
+        <v>0.4783541685898021</v>
       </c>
       <c r="T87">
-        <v>6.2453770580822</v>
+        <v>6.691475419373785</v>
       </c>
       <c r="U87">
         <v>0.2516309777667576</v>
       </c>
       <c r="V87">
-        <v>0.02911862938583013</v>
+        <v>0.0287800406720414</v>
       </c>
       <c r="W87">
-        <v>0.2443038285831733</v>
+        <v>0.2443890279922847</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.1164745175433205</v>
+        <v>0.1151201626881656</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2771441476759372</v>
+        <v>0.2792024574536048</v>
       </c>
       <c r="C88">
-        <v>-53199.14118894871</v>
+        <v>-54336.47584289213</v>
       </c>
       <c r="D88">
-        <v>24140.92910011391</v>
+        <v>23928.03712395028</v>
       </c>
       <c r="E88">
-        <v>73265.60251108283</v>
+        <v>74190.04518886263</v>
       </c>
       <c r="F88">
-        <v>79502.07028906261</v>
+        <v>80426.51296684241</v>
       </c>
       <c r="G88">
         <v>2162</v>
@@ -8503,37 +8503,37 @@
         <v>2303</v>
       </c>
       <c r="M88">
-        <v>20005.18368131831</v>
+        <v>20237.80209621736</v>
       </c>
       <c r="N88">
-        <v>-17702.18368131831</v>
+        <v>-17934.80209621736</v>
       </c>
       <c r="O88">
-        <v>-4425.545920329578</v>
+        <v>-4483.70052405434</v>
       </c>
       <c r="P88">
-        <v>-13276.63776098873</v>
+        <v>-13451.10157216302</v>
       </c>
       <c r="Q88">
-        <v>-12676.63776098873</v>
+        <v>-12851.10157216302</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.4783541685898021</v>
+        <v>0.511627566173633</v>
       </c>
       <c r="T88">
-        <v>6.691475419373785</v>
+        <v>7.206204297787154</v>
       </c>
       <c r="U88">
         <v>0.2516309777667576</v>
       </c>
       <c r="V88">
-        <v>0.0287800406720414</v>
+        <v>0.02844923560684553</v>
       </c>
       <c r="W88">
-        <v>0.2443890279922847</v>
+        <v>0.2444722687942902</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.1151201626881656</v>
+        <v>0.1137969424273821</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2792024574536048</v>
+        <v>0.2812607672312724</v>
       </c>
       <c r="C89">
-        <v>-54336.47584289213</v>
+        <v>-55470.08845310591</v>
       </c>
       <c r="D89">
-        <v>23928.03712395028</v>
+        <v>23718.8671915163</v>
       </c>
       <c r="E89">
-        <v>74190.04518886263</v>
+        <v>75114.48786664243</v>
       </c>
       <c r="F89">
-        <v>80426.51296684241</v>
+        <v>81350.95564462221</v>
       </c>
       <c r="G89">
         <v>2162</v>
@@ -8585,37 +8585,37 @@
         <v>2303</v>
       </c>
       <c r="M89">
-        <v>20237.80209621736</v>
+        <v>20470.42051111642</v>
       </c>
       <c r="N89">
-        <v>-17934.80209621736</v>
+        <v>-18167.42051111642</v>
       </c>
       <c r="O89">
-        <v>-4483.70052405434</v>
+        <v>-4541.855127779104</v>
       </c>
       <c r="P89">
-        <v>-13451.10157216302</v>
+        <v>-13625.56538333731</v>
       </c>
       <c r="Q89">
-        <v>-12851.10157216302</v>
+        <v>-13025.56538333731</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.511627566173633</v>
+        <v>0.5504465300214358</v>
       </c>
       <c r="T89">
-        <v>7.206204297787154</v>
+        <v>7.806721322602752</v>
       </c>
       <c r="U89">
         <v>0.2516309777667576</v>
       </c>
       <c r="V89">
-        <v>0.02844923560684553</v>
+        <v>0.02812594883858591</v>
       </c>
       <c r="W89">
-        <v>0.2444722687942902</v>
+        <v>0.2445536177598864</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.1137969424273821</v>
+        <v>0.1125037953543436</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2812607672312724</v>
+        <v>0.2833190770089399</v>
       </c>
       <c r="C90">
-        <v>-55470.08845310591</v>
+        <v>-56600.07578384703</v>
       </c>
       <c r="D90">
-        <v>23718.8671915163</v>
+        <v>23513.32253855497</v>
       </c>
       <c r="E90">
-        <v>75114.48786664243</v>
+        <v>76038.93054442223</v>
       </c>
       <c r="F90">
-        <v>81350.95564462221</v>
+        <v>82275.398322402</v>
       </c>
       <c r="G90">
         <v>2162</v>
@@ -8667,37 +8667,37 @@
         <v>2303</v>
       </c>
       <c r="M90">
-        <v>20470.42051111642</v>
+        <v>20703.03892601546</v>
       </c>
       <c r="N90">
-        <v>-18167.42051111642</v>
+        <v>-18400.03892601546</v>
       </c>
       <c r="O90">
-        <v>-4541.855127779104</v>
+        <v>-4600.009731503866</v>
       </c>
       <c r="P90">
-        <v>-13625.56538333731</v>
+        <v>-13800.0291945116</v>
       </c>
       <c r="Q90">
-        <v>-13025.56538333731</v>
+        <v>-13200.0291945116</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.5504465300214358</v>
+        <v>0.5963234872961117</v>
       </c>
       <c r="T90">
-        <v>7.806721322602752</v>
+        <v>8.516423261021183</v>
       </c>
       <c r="U90">
         <v>0.2516309777667576</v>
       </c>
       <c r="V90">
-        <v>0.02812594883858591</v>
+        <v>0.02780992694152315</v>
       </c>
       <c r="W90">
-        <v>0.2445536177598864</v>
+        <v>0.24463313865884</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.1125037953543436</v>
+        <v>0.1112397077660926</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2833190770089399</v>
+        <v>0.2853773867866075</v>
       </c>
       <c r="C91">
-        <v>-56600.07578384703</v>
+        <v>-57726.53127400327</v>
       </c>
       <c r="D91">
-        <v>23513.32253855497</v>
+        <v>23311.30972617854</v>
       </c>
       <c r="E91">
-        <v>76038.93054442223</v>
+        <v>76963.37322220203</v>
       </c>
       <c r="F91">
-        <v>82275.398322402</v>
+        <v>83199.84100018181</v>
       </c>
       <c r="G91">
         <v>2162</v>
@@ -8749,37 +8749,37 @@
         <v>2303</v>
       </c>
       <c r="M91">
-        <v>20703.03892601546</v>
+        <v>20935.65734091452</v>
       </c>
       <c r="N91">
-        <v>-18400.03892601546</v>
+        <v>-18632.65734091452</v>
       </c>
       <c r="O91">
-        <v>-4600.009731503866</v>
+        <v>-4658.164335228629</v>
       </c>
       <c r="P91">
-        <v>-13800.0291945116</v>
+        <v>-13974.49300568589</v>
       </c>
       <c r="Q91">
-        <v>-13200.0291945116</v>
+        <v>-13374.49300568589</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.5963234872961117</v>
+        <v>0.651375836025723</v>
       </c>
       <c r="T91">
-        <v>8.516423261021183</v>
+        <v>9.368065587123303</v>
       </c>
       <c r="U91">
         <v>0.2516309777667576</v>
       </c>
       <c r="V91">
-        <v>0.02780992694152315</v>
+        <v>0.027500927753284</v>
       </c>
       <c r="W91">
-        <v>0.24463313865884</v>
+        <v>0.2447108924267057</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.1112397077660926</v>
+        <v>0.110003711013136</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2853773867866075</v>
+        <v>0.2874356965642751</v>
       </c>
       <c r="C92">
-        <v>-57726.53127400327</v>
+        <v>-58849.54517872455</v>
       </c>
       <c r="D92">
-        <v>23311.30972617854</v>
+        <v>23112.73849923705</v>
       </c>
       <c r="E92">
-        <v>76963.37322220203</v>
+        <v>77887.81589998183</v>
       </c>
       <c r="F92">
-        <v>83199.84100018181</v>
+        <v>84124.2836779616</v>
       </c>
       <c r="G92">
         <v>2162</v>
@@ -8831,37 +8831,37 @@
         <v>2303</v>
       </c>
       <c r="M92">
-        <v>20935.65734091452</v>
+        <v>21168.27575581356</v>
       </c>
       <c r="N92">
-        <v>-18632.65734091452</v>
+        <v>-18865.27575581356</v>
       </c>
       <c r="O92">
-        <v>-4658.164335228629</v>
+        <v>-4716.318938953391</v>
       </c>
       <c r="P92">
-        <v>-13974.49300568589</v>
+        <v>-14148.95681686017</v>
       </c>
       <c r="Q92">
-        <v>-13374.49300568589</v>
+        <v>-13548.95681686017</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.651375836025723</v>
+        <v>0.7186620400285813</v>
       </c>
       <c r="T92">
-        <v>9.368065587123303</v>
+        <v>10.40896176347034</v>
       </c>
       <c r="U92">
         <v>0.2516309777667576</v>
       </c>
       <c r="V92">
-        <v>0.027500927753284</v>
+        <v>0.02719871975599517</v>
       </c>
       <c r="W92">
-        <v>0.2447108924267057</v>
+        <v>0.2447869373205525</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.110003711013136</v>
+        <v>0.1087948790239807</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2874356965642751</v>
+        <v>0.2894940063419427</v>
       </c>
       <c r="C93">
-        <v>-58849.54517872455</v>
+        <v>-59969.20470387687</v>
       </c>
       <c r="D93">
-        <v>23112.73849923705</v>
+        <v>22917.52165186452</v>
       </c>
       <c r="E93">
-        <v>77887.81589998183</v>
+        <v>78812.25857776162</v>
       </c>
       <c r="F93">
-        <v>84124.2836779616</v>
+        <v>85048.7263557414</v>
       </c>
       <c r="G93">
         <v>2162</v>
@@ -8913,37 +8913,37 @@
         <v>2303</v>
       </c>
       <c r="M93">
-        <v>21168.27575581356</v>
+        <v>21400.89417071261</v>
       </c>
       <c r="N93">
-        <v>-18865.27575581356</v>
+        <v>-19097.89417071261</v>
       </c>
       <c r="O93">
-        <v>-4716.318938953391</v>
+        <v>-4774.473542678154</v>
       </c>
       <c r="P93">
-        <v>-14148.95681686017</v>
+        <v>-14323.42062803446</v>
       </c>
       <c r="Q93">
-        <v>-13548.95681686017</v>
+        <v>-13723.42062803446</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.7186620400285813</v>
+        <v>0.8027697950321541</v>
       </c>
       <c r="T93">
-        <v>10.40896176347034</v>
+        <v>11.71008198390413</v>
       </c>
       <c r="U93">
         <v>0.2516309777667576</v>
       </c>
       <c r="V93">
-        <v>0.02719871975599517</v>
+        <v>0.02690308149777783</v>
       </c>
       <c r="W93">
-        <v>0.2447869373205525</v>
+        <v>0.244861329064533</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.1087948790239807</v>
+        <v>0.1076123259911114</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2894940063419427</v>
+        <v>0.2915523161196102</v>
       </c>
       <c r="C94">
-        <v>-59969.20470387687</v>
+        <v>-61085.5941337393</v>
       </c>
       <c r="D94">
-        <v>22917.52165186452</v>
+        <v>22725.57489978191</v>
       </c>
       <c r="E94">
-        <v>78812.25857776162</v>
+        <v>79736.70125554143</v>
       </c>
       <c r="F94">
-        <v>85048.7263557414</v>
+        <v>85973.1690335212</v>
       </c>
       <c r="G94">
         <v>2162</v>
@@ -8995,37 +8995,37 @@
         <v>2303</v>
       </c>
       <c r="M94">
-        <v>21400.89417071261</v>
+        <v>21633.51258561166</v>
       </c>
       <c r="N94">
-        <v>-19097.89417071261</v>
+        <v>-19330.51258561166</v>
       </c>
       <c r="O94">
-        <v>-4774.473542678154</v>
+        <v>-4832.628146402916</v>
       </c>
       <c r="P94">
-        <v>-14323.42062803446</v>
+        <v>-14497.88443920875</v>
       </c>
       <c r="Q94">
-        <v>-13723.42062803446</v>
+        <v>-13897.88443920875</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.8027697950321541</v>
+        <v>0.9109083371796047</v>
       </c>
       <c r="T94">
-        <v>11.71008198390413</v>
+        <v>13.38295083874758</v>
       </c>
       <c r="U94">
         <v>0.2516309777667576</v>
       </c>
       <c r="V94">
-        <v>0.02690308149777783</v>
+        <v>0.02661380105156517</v>
       </c>
       <c r="W94">
-        <v>0.244861329064533</v>
+        <v>0.2449341209860623</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.1076123259911114</v>
+        <v>0.1064552042062606</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2915523161196102</v>
+        <v>0.2936106258972778</v>
       </c>
       <c r="C95">
-        <v>-61085.5941337393</v>
+        <v>-62198.79495233719</v>
       </c>
       <c r="D95">
-        <v>22725.57489978191</v>
+        <v>22536.8167589638</v>
       </c>
       <c r="E95">
-        <v>79736.70125554143</v>
+        <v>80661.14393332122</v>
       </c>
       <c r="F95">
-        <v>85973.1690335212</v>
+        <v>86897.611711301</v>
       </c>
       <c r="G95">
         <v>2162</v>
@@ -9077,37 +9077,37 @@
         <v>2303</v>
       </c>
       <c r="M95">
-        <v>21633.51258561166</v>
+        <v>21866.13100051072</v>
       </c>
       <c r="N95">
-        <v>-19330.51258561166</v>
+        <v>-19563.13100051072</v>
       </c>
       <c r="O95">
-        <v>-4832.628146402916</v>
+        <v>-4890.782750127679</v>
       </c>
       <c r="P95">
-        <v>-14497.88443920875</v>
+        <v>-14672.34825038304</v>
       </c>
       <c r="Q95">
-        <v>-13897.88443920875</v>
+        <v>-14072.34825038304</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.9109083371796047</v>
+        <v>1.055093060042873</v>
       </c>
       <c r="T95">
-        <v>13.38295083874758</v>
+        <v>15.61344264520552</v>
       </c>
       <c r="U95">
         <v>0.2516309777667576</v>
       </c>
       <c r="V95">
-        <v>0.02661380105156517</v>
+        <v>0.02633067550846341</v>
       </c>
       <c r="W95">
-        <v>0.2449341209860623</v>
+        <v>0.2450053641433037</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.1064552042062606</v>
+        <v>0.1053227020338536</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2936106258972778</v>
+        <v>0.2956689356749454</v>
       </c>
       <c r="C96">
-        <v>-62198.79495233719</v>
+        <v>-63308.88595877848</v>
       </c>
       <c r="D96">
-        <v>22536.8167589638</v>
+        <v>22351.16843030232</v>
       </c>
       <c r="E96">
-        <v>80661.14393332122</v>
+        <v>81585.58661110103</v>
       </c>
       <c r="F96">
-        <v>86897.611711301</v>
+        <v>87822.0543890808</v>
       </c>
       <c r="G96">
         <v>2162</v>
@@ -9159,37 +9159,37 @@
         <v>2303</v>
       </c>
       <c r="M96">
-        <v>21866.13100051072</v>
+        <v>22098.74941540977</v>
       </c>
       <c r="N96">
-        <v>-19563.13100051072</v>
+        <v>-19795.74941540977</v>
       </c>
       <c r="O96">
-        <v>-4890.782750127679</v>
+        <v>-4948.937353852441</v>
       </c>
       <c r="P96">
-        <v>-14672.34825038304</v>
+        <v>-14846.81206155732</v>
       </c>
       <c r="Q96">
-        <v>-14072.34825038304</v>
+        <v>-14246.81206155732</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.055093060042873</v>
+        <v>1.256951672051448</v>
       </c>
       <c r="T96">
-        <v>15.61344264520552</v>
+        <v>18.73613117424663</v>
       </c>
       <c r="U96">
         <v>0.2516309777667576</v>
       </c>
       <c r="V96">
-        <v>0.02633067550846341</v>
+        <v>0.02605351050311116</v>
       </c>
       <c r="W96">
-        <v>0.2450053641433037</v>
+        <v>0.2450751074446032</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.1053227020338536</v>
+        <v>0.1042140420124447</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2956689356749454</v>
+        <v>0.297727245452613</v>
       </c>
       <c r="C97">
-        <v>-63308.88595877848</v>
+        <v>-64415.94337693593</v>
       </c>
       <c r="D97">
-        <v>22351.16843030232</v>
+        <v>22168.55368992467</v>
       </c>
       <c r="E97">
-        <v>81585.58661110103</v>
+        <v>82510.02928888082</v>
       </c>
       <c r="F97">
-        <v>87822.0543890808</v>
+        <v>88746.4970668606</v>
       </c>
       <c r="G97">
         <v>2162</v>
@@ -9241,37 +9241,37 @@
         <v>2303</v>
       </c>
       <c r="M97">
-        <v>22098.74941540977</v>
+        <v>22331.36783030882</v>
       </c>
       <c r="N97">
-        <v>-19795.74941540977</v>
+        <v>-20028.36783030882</v>
       </c>
       <c r="O97">
-        <v>-4948.937353852441</v>
+        <v>-5007.091957577204</v>
       </c>
       <c r="P97">
-        <v>-14846.81206155732</v>
+        <v>-15021.27587273161</v>
       </c>
       <c r="Q97">
-        <v>-14246.81206155732</v>
+        <v>-14421.27587273161</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.256951672051448</v>
+        <v>1.55973959006431</v>
       </c>
       <c r="T97">
-        <v>18.73613117424663</v>
+        <v>23.4201639678083</v>
       </c>
       <c r="U97">
         <v>0.2516309777667576</v>
       </c>
       <c r="V97">
-        <v>0.02605351050311116</v>
+        <v>0.02578211976870375</v>
       </c>
       <c r="W97">
-        <v>0.2450751074446032</v>
+        <v>0.245143397760459</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.1042140420124447</v>
+        <v>0.103128479074815</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2977272454526129</v>
+        <v>0.2997855552302805</v>
       </c>
       <c r="C98">
-        <v>-64415.94337693592</v>
+        <v>-65520.04095979624</v>
       </c>
       <c r="D98">
-        <v>22168.55368992467</v>
+        <v>21988.89878484415</v>
       </c>
       <c r="E98">
-        <v>82510.0292888808</v>
+        <v>83434.47196666061</v>
       </c>
       <c r="F98">
-        <v>88746.49706686058</v>
+        <v>89670.93974464039</v>
       </c>
       <c r="G98">
         <v>2162</v>
@@ -9323,37 +9323,37 @@
         <v>2303</v>
       </c>
       <c r="M98">
-        <v>22331.36783030881</v>
+        <v>22563.98624520786</v>
       </c>
       <c r="N98">
-        <v>-20028.36783030881</v>
+        <v>-20260.98624520786</v>
       </c>
       <c r="O98">
-        <v>-5007.091957577203</v>
+        <v>-5065.246561301966</v>
       </c>
       <c r="P98">
-        <v>-15021.27587273161</v>
+        <v>-15195.7396839059</v>
       </c>
       <c r="Q98">
-        <v>-14421.27587273161</v>
+        <v>-14595.7396839059</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.559739590064306</v>
+        <v>2.064386120085741</v>
       </c>
       <c r="T98">
-        <v>23.42016396780823</v>
+        <v>31.22688529041098</v>
       </c>
       <c r="U98">
         <v>0.2516309777667576</v>
       </c>
       <c r="V98">
-        <v>0.02578211976870376</v>
+        <v>0.02551632471954186</v>
       </c>
       <c r="W98">
-        <v>0.245143397760459</v>
+        <v>0.2452102800285652</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.103128479074815</v>
+        <v>0.1020652988781675</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2997855552302805</v>
+        <v>0.3018438650079481</v>
       </c>
       <c r="C99">
-        <v>-65520.04095979624</v>
+        <v>-66621.25008877604</v>
       </c>
       <c r="D99">
-        <v>21988.89878484415</v>
+        <v>21812.13233364415</v>
       </c>
       <c r="E99">
-        <v>83434.47196666061</v>
+        <v>84358.9146444404</v>
       </c>
       <c r="F99">
-        <v>89670.93974464039</v>
+        <v>90595.38242242018</v>
       </c>
       <c r="G99">
         <v>2162</v>
@@ -9405,37 +9405,37 @@
         <v>2303</v>
       </c>
       <c r="M99">
-        <v>22563.98624520786</v>
+        <v>22796.60466010691</v>
       </c>
       <c r="N99">
-        <v>-20260.98624520786</v>
+        <v>-20493.60466010691</v>
       </c>
       <c r="O99">
-        <v>-5065.246561301966</v>
+        <v>-5123.401165026728</v>
       </c>
       <c r="P99">
-        <v>-15195.7396839059</v>
+        <v>-15370.20349508019</v>
       </c>
       <c r="Q99">
-        <v>-14595.7396839059</v>
+        <v>-14770.20349508019</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>2.064386120085741</v>
+        <v>3.073679180128612</v>
       </c>
       <c r="T99">
-        <v>31.22688529041098</v>
+        <v>46.84032793561646</v>
       </c>
       <c r="U99">
         <v>0.2516309777667576</v>
       </c>
       <c r="V99">
-        <v>0.02551632471954186</v>
+        <v>0.02525595405913838</v>
       </c>
       <c r="W99">
-        <v>0.2452102800285652</v>
+        <v>0.2452757973524243</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.1020652988781675</v>
+        <v>0.1010238162365535</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.3018438650079481</v>
+        <v>0.3039021747856157</v>
       </c>
       <c r="C100">
-        <v>-66621.25008877604</v>
+        <v>-67719.63986828565</v>
       </c>
       <c r="D100">
-        <v>21812.13233364415</v>
+        <v>21638.18523191434</v>
       </c>
       <c r="E100">
-        <v>84358.9146444404</v>
+        <v>85283.35732222021</v>
       </c>
       <c r="F100">
-        <v>90595.38242242018</v>
+        <v>91519.82510019999</v>
       </c>
       <c r="G100">
         <v>2162</v>
@@ -9487,37 +9487,37 @@
         <v>2303</v>
       </c>
       <c r="M100">
-        <v>22796.60466010691</v>
+        <v>23029.22307500596</v>
       </c>
       <c r="N100">
-        <v>-20493.60466010691</v>
+        <v>-20726.22307500596</v>
       </c>
       <c r="O100">
-        <v>-5123.401165026728</v>
+        <v>-5181.555768751491</v>
       </c>
       <c r="P100">
-        <v>-15370.20349508019</v>
+        <v>-15544.66730625447</v>
       </c>
       <c r="Q100">
-        <v>-14770.20349508019</v>
+        <v>-14944.66730625447</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>3.073679180128612</v>
+        <v>6.101558360257224</v>
       </c>
       <c r="T100">
-        <v>46.84032793561646</v>
+        <v>93.68065587123291</v>
       </c>
       <c r="U100">
         <v>0.2516309777667576</v>
       </c>
       <c r="V100">
-        <v>0.02525595405913838</v>
+        <v>0.02500084341207637</v>
       </c>
       <c r="W100">
-        <v>0.2452757973524243</v>
+        <v>0.2453399910939832</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.1010238162365535</v>
+        <v>0.1000033736483055</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.3039021747856157</v>
-      </c>
-      <c r="C101">
-        <v>-67719.63986828565</v>
-      </c>
-      <c r="D101">
-        <v>21638.18523191434</v>
-      </c>
-      <c r="E101">
-        <v>85283.35732222021</v>
-      </c>
-      <c r="F101">
-        <v>91519.82510019999</v>
-      </c>
-      <c r="G101">
-        <v>2162</v>
-      </c>
-      <c r="H101">
-        <v>86207.8</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>2903</v>
-      </c>
-      <c r="K101">
-        <v>600</v>
-      </c>
-      <c r="L101">
-        <v>2303</v>
-      </c>
-      <c r="M101">
-        <v>23029.22307500596</v>
-      </c>
-      <c r="N101">
-        <v>-20726.22307500596</v>
-      </c>
-      <c r="O101">
-        <v>-5181.555768751491</v>
-      </c>
-      <c r="P101">
-        <v>-15544.66730625447</v>
-      </c>
-      <c r="Q101">
-        <v>-14944.66730625447</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>6.101558360257224</v>
-      </c>
-      <c r="T101">
-        <v>93.68065587123291</v>
-      </c>
-      <c r="U101">
-        <v>0.2516309777667576</v>
-      </c>
-      <c r="V101">
-        <v>0.02500084341207637</v>
-      </c>
-      <c r="W101">
-        <v>0.2453399910939832</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.1000033736483055</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
